--- a/sensitivity_results/legacy/mobilenet_v3_small_beforecorrelation_matrices.xlsx
+++ b/sensitivity_results/legacy/mobilenet_v3_small_beforecorrelation_matrices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\temp\ToGIT\Legacy\pearson_corelation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F929F95C-3F4E-4046-9710-F41AF77F1E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7837051-866E-4E2F-B938-92A3D633C502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="60">
   <si>
     <t>features.0.0</t>
   </si>
@@ -214,12 +214,18 @@
   <si>
     <t/>
   </si>
+  <si>
+    <t>Layer Number</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -231,14 +237,34 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -268,17 +294,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -296,13 +354,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -611,8 +662,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71F22ED4-C7AC-41CF-8A93-E6DE23EDFDBC}">
-  <dimension ref="A1:BA64"/>
+  <dimension ref="A1:BY79"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="24" max="24" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="19.36328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:53" x14ac:dyDescent="0.35">
       <c r="B1" t="str">
@@ -1463,417 +1518,417 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6">
         <f>MIN(B2:B4)</f>
         <v>-4.8587059485559601E-2</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6">
         <f t="shared" ref="C6:R6" si="0">MIN(C2:C4)</f>
         <v>4.2116191186550669E-4</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6">
         <f t="shared" si="0"/>
         <v>-0.122908404287476</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6">
         <f t="shared" si="0"/>
         <v>-1.112564254048028E-2</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6">
         <f t="shared" si="0"/>
         <v>-7.3830407358991346E-3</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6">
         <f t="shared" si="0"/>
         <v>-4.4877845328920737E-2</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6">
         <f t="shared" si="0"/>
         <v>-0.1814170971556317</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6">
         <f t="shared" si="0"/>
         <v>-0.1081727279359343</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6">
         <f t="shared" si="0"/>
         <v>-5.9473538099599363E-2</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6">
         <f t="shared" si="0"/>
         <v>-0.15347827777765929</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6">
         <f t="shared" si="0"/>
         <v>-0.2252474346248946</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6">
         <f t="shared" si="0"/>
         <v>-0.19157511620157161</v>
       </c>
-      <c r="O6" s="2">
+      <c r="O6">
         <f t="shared" si="0"/>
         <v>-1.590499553657693E-2</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6">
         <f t="shared" si="0"/>
         <v>-0.2217890721860255</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6">
         <f t="shared" si="0"/>
         <v>-6.6432306251082582E-2</v>
       </c>
-      <c r="R6" s="2">
+      <c r="R6">
         <f t="shared" si="0"/>
         <v>1.582327991513794E-2</v>
       </c>
-      <c r="S6" s="2">
+      <c r="S6">
         <f t="shared" ref="S6:AZ6" si="1">MIN(S2:S4)</f>
         <v>-1.799368890890491E-2</v>
       </c>
-      <c r="T6" s="2">
+      <c r="T6">
         <f t="shared" si="1"/>
         <v>-7.7579799858527643E-2</v>
       </c>
-      <c r="U6" s="2">
+      <c r="U6">
         <f t="shared" si="1"/>
         <v>-5.2705866379122703E-2</v>
       </c>
-      <c r="V6" s="2">
+      <c r="V6">
         <f t="shared" si="1"/>
         <v>5.1934390584396098E-2</v>
       </c>
-      <c r="W6" s="2">
+      <c r="W6">
         <f t="shared" si="1"/>
         <v>-0.17067477104912859</v>
       </c>
-      <c r="X6" s="2">
+      <c r="X6">
         <f t="shared" si="1"/>
         <v>-9.7960855386681631E-2</v>
       </c>
-      <c r="Y6" s="2">
+      <c r="Y6">
         <f t="shared" si="1"/>
         <v>-5.4213993915080083E-2</v>
       </c>
-      <c r="Z6" s="2">
+      <c r="Z6">
         <f t="shared" si="1"/>
         <v>-0.115615423932769</v>
       </c>
-      <c r="AA6" s="2">
+      <c r="AA6">
         <f t="shared" si="1"/>
         <v>1.328320411295162E-2</v>
       </c>
-      <c r="AB6" s="2">
+      <c r="AB6">
         <f t="shared" si="1"/>
         <v>-6.3615870139065778E-2</v>
       </c>
-      <c r="AC6" s="2">
+      <c r="AC6">
         <f t="shared" si="1"/>
         <v>-4.3211284844837258E-2</v>
       </c>
-      <c r="AD6" s="2">
+      <c r="AD6">
         <f t="shared" si="1"/>
         <v>-0.13339506874455501</v>
       </c>
-      <c r="AE6" s="2">
+      <c r="AE6">
         <f t="shared" si="1"/>
         <v>-0.15505926707260631</v>
       </c>
-      <c r="AF6" s="2">
+      <c r="AF6">
         <f t="shared" si="1"/>
         <v>3.4978000999223317E-2</v>
       </c>
-      <c r="AG6" s="2">
+      <c r="AG6">
         <f t="shared" si="1"/>
         <v>1.1876681947670139E-3</v>
       </c>
-      <c r="AH6" s="2">
+      <c r="AH6">
         <f t="shared" si="1"/>
         <v>-2.0180075978273929E-2</v>
       </c>
-      <c r="AI6" s="2">
+      <c r="AI6">
         <f t="shared" si="1"/>
         <v>6.2361502728391277E-2</v>
       </c>
-      <c r="AJ6" s="2">
+      <c r="AJ6">
         <f t="shared" si="1"/>
         <v>8.1943705279893374E-3</v>
       </c>
-      <c r="AK6" s="2">
+      <c r="AK6">
         <f t="shared" si="1"/>
         <v>1.8792838181911551E-2</v>
       </c>
-      <c r="AL6" s="2">
+      <c r="AL6">
         <f t="shared" si="1"/>
         <v>-1.2870830995980031E-2</v>
       </c>
-      <c r="AM6" s="2">
+      <c r="AM6">
         <f t="shared" si="1"/>
         <v>9.659843726364814E-2</v>
       </c>
-      <c r="AN6" s="2">
+      <c r="AN6">
         <f t="shared" si="1"/>
         <v>4.4795997694640939E-2</v>
       </c>
-      <c r="AO6" s="2">
+      <c r="AO6">
         <f t="shared" si="1"/>
         <v>-1.1472447249154329E-2</v>
       </c>
-      <c r="AP6" s="2">
+      <c r="AP6">
         <f t="shared" si="1"/>
         <v>7.2819799999499168E-2</v>
       </c>
-      <c r="AQ6" s="2">
+      <c r="AQ6">
         <f t="shared" si="1"/>
         <v>-5.960278212353802E-2</v>
       </c>
-      <c r="AR6" s="2">
+      <c r="AR6">
         <f t="shared" si="1"/>
         <v>-9.4200917726437933E-2</v>
       </c>
-      <c r="AS6" s="2">
+      <c r="AS6">
         <f t="shared" si="1"/>
         <v>-0.16755433489613319</v>
       </c>
-      <c r="AT6" s="2">
+      <c r="AT6">
         <f t="shared" si="1"/>
         <v>-4.6638144116081262E-2</v>
       </c>
-      <c r="AU6" s="2">
+      <c r="AU6">
         <f t="shared" si="1"/>
         <v>7.3195438611299679E-2</v>
       </c>
-      <c r="AV6" s="2">
+      <c r="AV6">
         <f t="shared" si="1"/>
         <v>-8.8108167075657134E-2</v>
       </c>
-      <c r="AW6" s="2">
+      <c r="AW6">
         <f t="shared" si="1"/>
         <v>-0.10950002353724871</v>
       </c>
-      <c r="AX6" s="2">
+      <c r="AX6">
         <f t="shared" si="1"/>
         <v>-0.1500093788951973</v>
       </c>
-      <c r="AY6" s="2">
+      <c r="AY6">
         <f t="shared" si="1"/>
         <v>-0.2176444454547318</v>
       </c>
-      <c r="AZ6" s="2">
+      <c r="AZ6">
         <f t="shared" si="1"/>
         <v>0.23543717196231551</v>
       </c>
     </row>
     <row r="7" spans="1:53" x14ac:dyDescent="0.35">
-      <c r="B7" s="2" t="b">
+      <c r="B7" t="b">
         <f t="shared" ref="B7:R7" si="2">IF(AND(B2&gt;0,B3&gt;0,B4&gt;0),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="2" t="b">
+      <c r="C7" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="D7" s="2" t="b">
+      <c r="D7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E7" s="2" t="b">
+      <c r="E7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F7" s="2" t="b">
+      <c r="F7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G7" s="2" t="b">
+      <c r="G7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H7" s="2" t="b">
+      <c r="H7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I7" s="2" t="b">
+      <c r="I7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J7" s="2" t="b">
+      <c r="J7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K7" s="2" t="b">
+      <c r="K7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L7" s="2" t="b">
+      <c r="L7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M7" s="2" t="b">
+      <c r="M7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N7" s="2" t="b">
+      <c r="N7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O7" s="2" t="b">
+      <c r="O7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P7" s="2" t="b">
+      <c r="P7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q7" s="2" t="b">
+      <c r="Q7" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R7" s="2" t="b">
+      <c r="R7" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="S7" s="2" t="b">
+      <c r="S7" t="b">
         <f t="shared" ref="S7:AZ7" si="3">IF(AND(S2&gt;0,S3&gt;0,S4&gt;0),TRUE,FALSE)</f>
         <v>0</v>
       </c>
-      <c r="T7" s="2" t="b">
+      <c r="T7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U7" s="2" t="b">
+      <c r="U7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V7" s="2" t="b">
+      <c r="V7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="W7" s="2" t="b">
+      <c r="W7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X7" s="2" t="b">
+      <c r="X7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y7" s="2" t="b">
+      <c r="Y7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z7" s="2" t="b">
+      <c r="Z7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA7" s="2" t="b">
+      <c r="AA7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AB7" s="2" t="b">
+      <c r="AB7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AC7" s="2" t="b">
+      <c r="AC7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AD7" s="2" t="b">
+      <c r="AD7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE7" s="2" t="b">
+      <c r="AE7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AF7" s="2" t="b">
+      <c r="AF7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AG7" s="2" t="b">
+      <c r="AG7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AH7" s="2" t="b">
+      <c r="AH7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI7" s="2" t="b">
+      <c r="AI7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AJ7" s="2" t="b">
+      <c r="AJ7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AK7" s="2" t="b">
+      <c r="AK7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AL7" s="2" t="b">
+      <c r="AL7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AM7" s="2" t="b">
+      <c r="AM7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AN7" s="2" t="b">
+      <c r="AN7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AO7" s="2" t="b">
+      <c r="AO7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AP7" s="2" t="b">
+      <c r="AP7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AQ7" s="2" t="b">
+      <c r="AQ7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AR7" s="2" t="b">
+      <c r="AR7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AS7" s="2" t="b">
+      <c r="AS7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AT7" s="2" t="b">
+      <c r="AT7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AU7" s="2" t="b">
+      <c r="AU7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="AV7" s="2" t="b">
+      <c r="AV7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AW7" s="2" t="b">
+      <c r="AW7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AX7" s="2" t="b">
+      <c r="AX7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AY7" s="2" t="b">
+      <c r="AY7" t="b">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AZ7" s="2" t="b">
+      <c r="AZ7" t="b">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -1887,217 +1942,214 @@
         <v>0.40955026609037631</v>
       </c>
     </row>
-    <row r="9" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="2" t="b">
+      <c r="B9" t="b">
         <f>IF(OR(AND(B2&gt;0,B3&gt;0), AND(B2&gt;0,B4&gt;0), AND(B3&gt;0,B4&gt;0)), TRUE, FALSE)</f>
         <v>1</v>
       </c>
-      <c r="C9" s="2" t="b">
-        <f t="shared" ref="C9:S9" si="4">IF(OR(AND(C2&gt;0,C3&gt;0), AND(C2&gt;0,C4&gt;0), AND(C3&gt;0,C4&gt;0)), TRUE, FALSE)</f>
+      <c r="C9" t="b">
+        <f t="shared" ref="C9:R9" si="4">IF(OR(AND(C2&gt;0,C3&gt;0), AND(C2&gt;0,C4&gt;0), AND(C3&gt;0,C4&gt;0)), TRUE, FALSE)</f>
         <v>1</v>
       </c>
-      <c r="D9" s="2" t="b">
+      <c r="D9" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E9" s="2" t="b">
+      <c r="E9" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F9" s="2" t="b">
+      <c r="F9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="G9" s="2" t="b">
+      <c r="G9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="H9" s="2" t="b">
+      <c r="H9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="I9" s="2" t="b">
+      <c r="I9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="J9" s="2" t="b">
+      <c r="J9" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K9" s="2" t="b">
+      <c r="K9" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="L9" s="2" t="b">
+      <c r="L9" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M9" s="2" t="b">
+      <c r="M9" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N9" s="2" t="b">
+      <c r="N9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="O9" s="2" t="b">
+      <c r="O9" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="P9" s="2" t="b">
+      <c r="P9" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Q9" s="2" t="b">
+      <c r="Q9" t="b">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R9" s="2" t="b">
+      <c r="R9" t="b">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="S9" s="2" t="b">
+      <c r="S9" t="b">
         <f t="shared" ref="S9:AZ9" si="5">IF(OR(AND(S2&gt;0,S3&gt;0), AND(S2&gt;0,S4&gt;0), AND(S3&gt;0,S4&gt;0)), TRUE, FALSE)</f>
         <v>1</v>
       </c>
-      <c r="T9" s="2" t="b">
+      <c r="T9" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U9" s="2" t="b">
+      <c r="U9" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="V9" s="2" t="b">
+      <c r="V9" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="W9" s="2" t="b">
+      <c r="W9" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="X9" s="2" t="b">
+      <c r="X9" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Y9" s="2" t="b">
+      <c r="Y9" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Z9" s="2" t="b">
+      <c r="Z9" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA9" s="2" t="b">
+      <c r="AA9" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AB9" s="2" t="b">
+      <c r="AB9" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AC9" s="2" t="b">
+      <c r="AC9" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AD9" s="2" t="b">
+      <c r="AD9" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AE9" s="2" t="b">
+      <c r="AE9" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AF9" s="2" t="b">
+      <c r="AF9" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AG9" s="2" t="b">
+      <c r="AG9" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AH9" s="2" t="b">
+      <c r="AH9" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AI9" s="2" t="b">
+      <c r="AI9" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AJ9" s="2" t="b">
+      <c r="AJ9" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AK9" s="2" t="b">
+      <c r="AK9" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AL9" s="2" t="b">
+      <c r="AL9" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AM9" s="2" t="b">
+      <c r="AM9" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AN9" s="2" t="b">
+      <c r="AN9" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AO9" s="2" t="b">
+      <c r="AO9" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AP9" s="2" t="b">
+      <c r="AP9" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AQ9" s="2" t="b">
+      <c r="AQ9" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AR9" s="2" t="b">
+      <c r="AR9" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AS9" s="2" t="b">
+      <c r="AS9" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AT9" s="2" t="b">
+      <c r="AT9" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AU9" s="2" t="b">
+      <c r="AU9" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AV9" s="2" t="b">
+      <c r="AV9" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AW9" s="2" t="b">
+      <c r="AW9" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AX9" s="2" t="b">
+      <c r="AX9" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AY9" s="2" t="b">
+      <c r="AY9" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="AZ9" s="2" t="b">
+      <c r="AZ9" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.35">
-      <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:53" x14ac:dyDescent="0.35">
       <c r="B11" t="str">
@@ -2315,180 +2367,7664 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>40</v>
       </c>
+      <c r="X27" s="2"/>
+      <c r="Y27" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z27" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="2">
+        <f>Z27+1</f>
+        <v>1</v>
+      </c>
+      <c r="AB27" s="2">
+        <f>AA27+1</f>
+        <v>2</v>
+      </c>
+      <c r="AC27" s="2">
+        <f>AB27+1</f>
+        <v>3</v>
+      </c>
+      <c r="AD27" s="2">
+        <f>AC27+1</f>
+        <v>4</v>
+      </c>
+      <c r="AE27" s="2">
+        <f>AD27+1</f>
+        <v>5</v>
+      </c>
+      <c r="AF27" s="2">
+        <f>AE27+1</f>
+        <v>6</v>
+      </c>
+      <c r="AG27" s="2">
+        <f>AF27+1</f>
+        <v>7</v>
+      </c>
+      <c r="AH27" s="2">
+        <f>AG27+1</f>
+        <v>8</v>
+      </c>
+      <c r="AI27" s="2">
+        <f>AH27+1</f>
+        <v>9</v>
+      </c>
+      <c r="AJ27" s="2">
+        <f>AI27+1</f>
+        <v>10</v>
+      </c>
+      <c r="AK27" s="2">
+        <f>AJ27+1</f>
+        <v>11</v>
+      </c>
+      <c r="AL27" s="2">
+        <f>AK27+1</f>
+        <v>12</v>
+      </c>
+      <c r="AM27" s="2">
+        <f>AL27+1</f>
+        <v>13</v>
+      </c>
+      <c r="AN27" s="2">
+        <f>AM27+1</f>
+        <v>14</v>
+      </c>
+      <c r="AO27" s="2">
+        <f>AN27+1</f>
+        <v>15</v>
+      </c>
+      <c r="AP27" s="2">
+        <f>AO27+1</f>
+        <v>16</v>
+      </c>
+      <c r="AQ27" s="2">
+        <f>AP27+1</f>
+        <v>17</v>
+      </c>
+      <c r="AR27" s="2">
+        <f>AQ27+1</f>
+        <v>18</v>
+      </c>
+      <c r="AS27" s="2">
+        <f>AR27+1</f>
+        <v>19</v>
+      </c>
+      <c r="AT27" s="2">
+        <f>AS27+1</f>
+        <v>20</v>
+      </c>
+      <c r="AU27" s="2">
+        <f>AT27+1</f>
+        <v>21</v>
+      </c>
+      <c r="AV27" s="2">
+        <f>AU27+1</f>
+        <v>22</v>
+      </c>
+      <c r="AW27" s="2">
+        <f>AV27+1</f>
+        <v>23</v>
+      </c>
+      <c r="AX27" s="2">
+        <f>AW27+1</f>
+        <v>24</v>
+      </c>
+      <c r="AY27" s="2">
+        <f>AX27+1</f>
+        <v>25</v>
+      </c>
+      <c r="AZ27" s="2">
+        <f>AY27+1</f>
+        <v>26</v>
+      </c>
+      <c r="BA27" s="2">
+        <f>AZ27+1</f>
+        <v>27</v>
+      </c>
+      <c r="BB27" s="2">
+        <f>BA27+1</f>
+        <v>28</v>
+      </c>
+      <c r="BC27" s="2">
+        <f>BB27+1</f>
+        <v>29</v>
+      </c>
+      <c r="BD27" s="2">
+        <f>BC27+1</f>
+        <v>30</v>
+      </c>
+      <c r="BE27" s="2">
+        <f>BD27+1</f>
+        <v>31</v>
+      </c>
+      <c r="BF27" s="2">
+        <f>BE27+1</f>
+        <v>32</v>
+      </c>
+      <c r="BG27" s="2">
+        <f>BF27+1</f>
+        <v>33</v>
+      </c>
+      <c r="BH27" s="2">
+        <f>BG27+1</f>
+        <v>34</v>
+      </c>
+      <c r="BI27" s="2">
+        <f>BH27+1</f>
+        <v>35</v>
+      </c>
+      <c r="BJ27" s="2">
+        <f>BI27+1</f>
+        <v>36</v>
+      </c>
+      <c r="BK27" s="2">
+        <f>BJ27+1</f>
+        <v>37</v>
+      </c>
+      <c r="BL27" s="2">
+        <f>BK27+1</f>
+        <v>38</v>
+      </c>
+      <c r="BM27" s="2">
+        <f>BL27+1</f>
+        <v>39</v>
+      </c>
+      <c r="BN27" s="2">
+        <f>BM27+1</f>
+        <v>40</v>
+      </c>
+      <c r="BO27" s="2">
+        <f>BN27+1</f>
+        <v>41</v>
+      </c>
+      <c r="BP27" s="2">
+        <f>BO27+1</f>
+        <v>42</v>
+      </c>
+      <c r="BQ27" s="2">
+        <f>BP27+1</f>
+        <v>43</v>
+      </c>
+      <c r="BR27" s="2">
+        <f>BQ27+1</f>
+        <v>44</v>
+      </c>
+      <c r="BS27" s="2">
+        <f>BR27+1</f>
+        <v>45</v>
+      </c>
+      <c r="BT27" s="2">
+        <f>BS27+1</f>
+        <v>46</v>
+      </c>
+      <c r="BU27" s="2">
+        <f>BT27+1</f>
+        <v>47</v>
+      </c>
+      <c r="BV27" s="2">
+        <f>BU27+1</f>
+        <v>48</v>
+      </c>
+      <c r="BW27" s="2">
+        <f>BV27+1</f>
+        <v>49</v>
+      </c>
+      <c r="BX27" s="2">
+        <f>BW27+1</f>
+        <v>50</v>
+      </c>
+      <c r="BY27" s="2">
+        <f>BX27+1</f>
+        <v>51</v>
+      </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>45</v>
       </c>
+      <c r="X28" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="5" t="str">
+        <f>IF(MIN(Class_0!B2,Class_1!B2,Class_2!B2)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA28" s="4"/>
+      <c r="AB28" s="4"/>
+      <c r="AC28" s="4"/>
+      <c r="AD28" s="4"/>
+      <c r="AE28" s="4"/>
+      <c r="AF28" s="4"/>
+      <c r="AG28" s="4"/>
+      <c r="AH28" s="4"/>
+      <c r="AI28" s="4"/>
+      <c r="AJ28" s="4"/>
+      <c r="AK28" s="4"/>
+      <c r="AL28" s="4"/>
+      <c r="AM28" s="4"/>
+      <c r="AN28" s="4"/>
+      <c r="AO28" s="4"/>
+      <c r="AP28" s="4"/>
+      <c r="AQ28" s="4"/>
+      <c r="AR28" s="4"/>
+      <c r="AS28" s="4"/>
+      <c r="AT28" s="4"/>
+      <c r="AU28" s="4"/>
+      <c r="AV28" s="4"/>
+      <c r="AW28" s="4"/>
+      <c r="AX28" s="4"/>
+      <c r="AY28" s="4"/>
+      <c r="AZ28" s="4"/>
+      <c r="BA28" s="4"/>
+      <c r="BB28" s="4"/>
+      <c r="BC28" s="4"/>
+      <c r="BD28" s="4"/>
+      <c r="BE28" s="4"/>
+      <c r="BF28" s="4"/>
+      <c r="BG28" s="4"/>
+      <c r="BH28" s="4"/>
+      <c r="BI28" s="4"/>
+      <c r="BJ28" s="4"/>
+      <c r="BK28" s="4"/>
+      <c r="BL28" s="4"/>
+      <c r="BM28" s="4"/>
+      <c r="BN28" s="4"/>
+      <c r="BO28" s="4"/>
+      <c r="BP28" s="4"/>
+      <c r="BQ28" s="4"/>
+      <c r="BR28" s="4"/>
+      <c r="BS28" s="4"/>
+      <c r="BT28" s="4"/>
+      <c r="BU28" s="4"/>
+      <c r="BV28" s="4"/>
+      <c r="BW28" s="4"/>
+      <c r="BX28" s="4"/>
+      <c r="BY28" s="4"/>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>50</v>
       </c>
+      <c r="X29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="2">
+        <f>Y28+1</f>
+        <v>1</v>
+      </c>
+      <c r="Z29" s="4" t="str">
+        <f>IF(MIN(Class_0!B3,Class_1!B3,Class_2!B3)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA29" s="5" t="str">
+        <f>IF(MIN(Class_0!C3,Class_1!C3,Class_2!C3)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB29" s="4"/>
+      <c r="AC29" s="4"/>
+      <c r="AD29" s="4"/>
+      <c r="AE29" s="4"/>
+      <c r="AF29" s="4"/>
+      <c r="AG29" s="4"/>
+      <c r="AH29" s="4"/>
+      <c r="AI29" s="4"/>
+      <c r="AJ29" s="4"/>
+      <c r="AK29" s="4"/>
+      <c r="AL29" s="4"/>
+      <c r="AM29" s="4"/>
+      <c r="AN29" s="4"/>
+      <c r="AO29" s="4"/>
+      <c r="AP29" s="4"/>
+      <c r="AQ29" s="4"/>
+      <c r="AR29" s="4"/>
+      <c r="AS29" s="4"/>
+      <c r="AT29" s="4"/>
+      <c r="AU29" s="4"/>
+      <c r="AV29" s="4"/>
+      <c r="AW29" s="4"/>
+      <c r="AX29" s="4"/>
+      <c r="AY29" s="4"/>
+      <c r="AZ29" s="4"/>
+      <c r="BA29" s="4"/>
+      <c r="BB29" s="4"/>
+      <c r="BC29" s="4"/>
+      <c r="BD29" s="4"/>
+      <c r="BE29" s="4"/>
+      <c r="BF29" s="4"/>
+      <c r="BG29" s="4"/>
+      <c r="BH29" s="4"/>
+      <c r="BI29" s="4"/>
+      <c r="BJ29" s="4"/>
+      <c r="BK29" s="4"/>
+      <c r="BL29" s="4"/>
+      <c r="BM29" s="4"/>
+      <c r="BN29" s="4"/>
+      <c r="BO29" s="4"/>
+      <c r="BP29" s="4"/>
+      <c r="BQ29" s="4"/>
+      <c r="BR29" s="4"/>
+      <c r="BS29" s="4"/>
+      <c r="BT29" s="4"/>
+      <c r="BU29" s="4"/>
+      <c r="BV29" s="4"/>
+      <c r="BW29" s="4"/>
+      <c r="BX29" s="4"/>
+      <c r="BY29" s="4"/>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>58</v>
       </c>
+      <c r="X30" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y30" s="2">
+        <f t="shared" ref="Y30:Y79" si="7">Y29+1</f>
+        <v>2</v>
+      </c>
+      <c r="Z30" s="4" t="str">
+        <f>IF(MIN(Class_0!B4,Class_1!B4,Class_2!B4)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA30" s="4" t="str">
+        <f>IF(MIN(Class_0!C4,Class_1!C4,Class_2!C4)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB30" s="5" t="str">
+        <f>IF(MIN(Class_0!D4,Class_1!D4,Class_2!D4)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC30" s="4"/>
+      <c r="AD30" s="4"/>
+      <c r="AE30" s="4"/>
+      <c r="AF30" s="4"/>
+      <c r="AG30" s="4"/>
+      <c r="AH30" s="4"/>
+      <c r="AI30" s="4"/>
+      <c r="AJ30" s="4"/>
+      <c r="AK30" s="4"/>
+      <c r="AL30" s="4"/>
+      <c r="AM30" s="4"/>
+      <c r="AN30" s="4"/>
+      <c r="AO30" s="4"/>
+      <c r="AP30" s="4"/>
+      <c r="AQ30" s="4"/>
+      <c r="AR30" s="4"/>
+      <c r="AS30" s="4"/>
+      <c r="AT30" s="4"/>
+      <c r="AU30" s="4"/>
+      <c r="AV30" s="4"/>
+      <c r="AW30" s="4"/>
+      <c r="AX30" s="4"/>
+      <c r="AY30" s="4"/>
+      <c r="AZ30" s="4"/>
+      <c r="BA30" s="4"/>
+      <c r="BB30" s="4"/>
+      <c r="BC30" s="4"/>
+      <c r="BD30" s="4"/>
+      <c r="BE30" s="4"/>
+      <c r="BF30" s="4"/>
+      <c r="BG30" s="4"/>
+      <c r="BH30" s="4"/>
+      <c r="BI30" s="4"/>
+      <c r="BJ30" s="4"/>
+      <c r="BK30" s="4"/>
+      <c r="BL30" s="4"/>
+      <c r="BM30" s="4"/>
+      <c r="BN30" s="4"/>
+      <c r="BO30" s="4"/>
+      <c r="BP30" s="4"/>
+      <c r="BQ30" s="4"/>
+      <c r="BR30" s="4"/>
+      <c r="BS30" s="4"/>
+      <c r="BT30" s="4"/>
+      <c r="BU30" s="4"/>
+      <c r="BV30" s="4"/>
+      <c r="BW30" s="4"/>
+      <c r="BX30" s="4"/>
+      <c r="BY30" s="4"/>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:77" x14ac:dyDescent="0.35">
+      <c r="X31" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y31" s="2">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="Z31" s="4" t="str">
+        <f>IF(MIN(Class_0!B5,Class_1!B5,Class_2!B5)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA31" s="4" t="str">
+        <f>IF(MIN(Class_0!C5,Class_1!C5,Class_2!C5)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB31" s="4" t="str">
+        <f>IF(MIN(Class_0!D5,Class_1!D5,Class_2!D5)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC31" s="5" t="str">
+        <f>IF(MIN(Class_0!E5,Class_1!E5,Class_2!E5)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD31" s="4"/>
+      <c r="AE31" s="4"/>
+      <c r="AF31" s="4"/>
+      <c r="AG31" s="4"/>
+      <c r="AH31" s="4"/>
+      <c r="AI31" s="4"/>
+      <c r="AJ31" s="4"/>
+      <c r="AK31" s="4"/>
+      <c r="AL31" s="4"/>
+      <c r="AM31" s="4"/>
+      <c r="AN31" s="4"/>
+      <c r="AO31" s="4"/>
+      <c r="AP31" s="4"/>
+      <c r="AQ31" s="4"/>
+      <c r="AR31" s="4"/>
+      <c r="AS31" s="4"/>
+      <c r="AT31" s="4"/>
+      <c r="AU31" s="4"/>
+      <c r="AV31" s="4"/>
+      <c r="AW31" s="4"/>
+      <c r="AX31" s="4"/>
+      <c r="AY31" s="4"/>
+      <c r="AZ31" s="4"/>
+      <c r="BA31" s="4"/>
+      <c r="BB31" s="4"/>
+      <c r="BC31" s="4"/>
+      <c r="BD31" s="4"/>
+      <c r="BE31" s="4"/>
+      <c r="BF31" s="4"/>
+      <c r="BG31" s="4"/>
+      <c r="BH31" s="4"/>
+      <c r="BI31" s="4"/>
+      <c r="BJ31" s="4"/>
+      <c r="BK31" s="4"/>
+      <c r="BL31" s="4"/>
+      <c r="BM31" s="4"/>
+      <c r="BN31" s="4"/>
+      <c r="BO31" s="4"/>
+      <c r="BP31" s="4"/>
+      <c r="BQ31" s="4"/>
+      <c r="BR31" s="4"/>
+      <c r="BS31" s="4"/>
+      <c r="BT31" s="4"/>
+      <c r="BU31" s="4"/>
+      <c r="BV31" s="4"/>
+      <c r="BW31" s="4"/>
+      <c r="BX31" s="4"/>
+      <c r="BY31" s="4"/>
+    </row>
+    <row r="32" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>58</v>
       </c>
+      <c r="X32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y32" s="2">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="Z32" s="4" t="str">
+        <f>IF(MIN(Class_0!B6,Class_1!B6,Class_2!B6)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA32" s="4" t="str">
+        <f>IF(MIN(Class_0!C6,Class_1!C6,Class_2!C6)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB32" s="4" t="str">
+        <f>IF(MIN(Class_0!D6,Class_1!D6,Class_2!D6)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC32" s="4" t="str">
+        <f>IF(MIN(Class_0!E6,Class_1!E6,Class_2!E6)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD32" s="5" t="str">
+        <f>IF(MIN(Class_0!F6,Class_1!F6,Class_2!F6)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE32" s="4"/>
+      <c r="AF32" s="4"/>
+      <c r="AG32" s="4"/>
+      <c r="AH32" s="4"/>
+      <c r="AI32" s="4"/>
+      <c r="AJ32" s="4"/>
+      <c r="AK32" s="4"/>
+      <c r="AL32" s="4"/>
+      <c r="AM32" s="4"/>
+      <c r="AN32" s="4"/>
+      <c r="AO32" s="4"/>
+      <c r="AP32" s="4"/>
+      <c r="AQ32" s="4"/>
+      <c r="AR32" s="4"/>
+      <c r="AS32" s="4"/>
+      <c r="AT32" s="4"/>
+      <c r="AU32" s="4"/>
+      <c r="AV32" s="4"/>
+      <c r="AW32" s="4"/>
+      <c r="AX32" s="4"/>
+      <c r="AY32" s="4"/>
+      <c r="AZ32" s="4"/>
+      <c r="BA32" s="4"/>
+      <c r="BB32" s="4"/>
+      <c r="BC32" s="4"/>
+      <c r="BD32" s="4"/>
+      <c r="BE32" s="4"/>
+      <c r="BF32" s="4"/>
+      <c r="BG32" s="4"/>
+      <c r="BH32" s="4"/>
+      <c r="BI32" s="4"/>
+      <c r="BJ32" s="4"/>
+      <c r="BK32" s="4"/>
+      <c r="BL32" s="4"/>
+      <c r="BM32" s="4"/>
+      <c r="BN32" s="4"/>
+      <c r="BO32" s="4"/>
+      <c r="BP32" s="4"/>
+      <c r="BQ32" s="4"/>
+      <c r="BR32" s="4"/>
+      <c r="BS32" s="4"/>
+      <c r="BT32" s="4"/>
+      <c r="BU32" s="4"/>
+      <c r="BV32" s="4"/>
+      <c r="BW32" s="4"/>
+      <c r="BX32" s="4"/>
+      <c r="BY32" s="4"/>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>58</v>
       </c>
+      <c r="X33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y33" s="2">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="Z33" s="4" t="str">
+        <f>IF(MIN(Class_0!B7,Class_1!B7,Class_2!B7)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA33" s="4" t="str">
+        <f>IF(MIN(Class_0!C7,Class_1!C7,Class_2!C7)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB33" s="4" t="str">
+        <f>IF(MIN(Class_0!D7,Class_1!D7,Class_2!D7)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC33" s="4" t="str">
+        <f>IF(MIN(Class_0!E7,Class_1!E7,Class_2!E7)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD33" s="4" t="str">
+        <f>IF(MIN(Class_0!F7,Class_1!F7,Class_2!F7)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE33" s="5" t="str">
+        <f>IF(MIN(Class_0!G7,Class_1!G7,Class_2!G7)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF33" s="4"/>
+      <c r="AG33" s="4"/>
+      <c r="AH33" s="4"/>
+      <c r="AI33" s="4"/>
+      <c r="AJ33" s="4"/>
+      <c r="AK33" s="4"/>
+      <c r="AL33" s="4"/>
+      <c r="AM33" s="4"/>
+      <c r="AN33" s="4"/>
+      <c r="AO33" s="4"/>
+      <c r="AP33" s="4"/>
+      <c r="AQ33" s="4"/>
+      <c r="AR33" s="4"/>
+      <c r="AS33" s="4"/>
+      <c r="AT33" s="4"/>
+      <c r="AU33" s="4"/>
+      <c r="AV33" s="4"/>
+      <c r="AW33" s="4"/>
+      <c r="AX33" s="4"/>
+      <c r="AY33" s="4"/>
+      <c r="AZ33" s="4"/>
+      <c r="BA33" s="4"/>
+      <c r="BB33" s="4"/>
+      <c r="BC33" s="4"/>
+      <c r="BD33" s="4"/>
+      <c r="BE33" s="4"/>
+      <c r="BF33" s="4"/>
+      <c r="BG33" s="4"/>
+      <c r="BH33" s="4"/>
+      <c r="BI33" s="4"/>
+      <c r="BJ33" s="4"/>
+      <c r="BK33" s="4"/>
+      <c r="BL33" s="4"/>
+      <c r="BM33" s="4"/>
+      <c r="BN33" s="4"/>
+      <c r="BO33" s="4"/>
+      <c r="BP33" s="4"/>
+      <c r="BQ33" s="4"/>
+      <c r="BR33" s="4"/>
+      <c r="BS33" s="4"/>
+      <c r="BT33" s="4"/>
+      <c r="BU33" s="4"/>
+      <c r="BV33" s="4"/>
+      <c r="BW33" s="4"/>
+      <c r="BX33" s="4"/>
+      <c r="BY33" s="4"/>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:77" x14ac:dyDescent="0.35">
+      <c r="X34" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y34" s="2">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="Z34" s="4" t="str">
+        <f>IF(MIN(Class_0!B8,Class_1!B8,Class_2!B8)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA34" s="4" t="str">
+        <f>IF(MIN(Class_0!C8,Class_1!C8,Class_2!C8)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB34" s="4" t="str">
+        <f>IF(MIN(Class_0!D8,Class_1!D8,Class_2!D8)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC34" s="4" t="str">
+        <f>IF(MIN(Class_0!E8,Class_1!E8,Class_2!E8)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD34" s="4" t="str">
+        <f>IF(MIN(Class_0!F8,Class_1!F8,Class_2!F8)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE34" s="4" t="str">
+        <f>IF(MIN(Class_0!G8,Class_1!G8,Class_2!G8)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF34" s="5" t="str">
+        <f>IF(MIN(Class_0!H8,Class_1!H8,Class_2!H8)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG34" s="4"/>
+      <c r="AH34" s="4"/>
+      <c r="AI34" s="4"/>
+      <c r="AJ34" s="4"/>
+      <c r="AK34" s="4"/>
+      <c r="AL34" s="4"/>
+      <c r="AM34" s="4"/>
+      <c r="AN34" s="4"/>
+      <c r="AO34" s="4"/>
+      <c r="AP34" s="4"/>
+      <c r="AQ34" s="4"/>
+      <c r="AR34" s="4"/>
+      <c r="AS34" s="4"/>
+      <c r="AT34" s="4"/>
+      <c r="AU34" s="4"/>
+      <c r="AV34" s="4"/>
+      <c r="AW34" s="4"/>
+      <c r="AX34" s="4"/>
+      <c r="AY34" s="4"/>
+      <c r="AZ34" s="4"/>
+      <c r="BA34" s="4"/>
+      <c r="BB34" s="4"/>
+      <c r="BC34" s="4"/>
+      <c r="BD34" s="4"/>
+      <c r="BE34" s="4"/>
+      <c r="BF34" s="4"/>
+      <c r="BG34" s="4"/>
+      <c r="BH34" s="4"/>
+      <c r="BI34" s="4"/>
+      <c r="BJ34" s="4"/>
+      <c r="BK34" s="4"/>
+      <c r="BL34" s="4"/>
+      <c r="BM34" s="4"/>
+      <c r="BN34" s="4"/>
+      <c r="BO34" s="4"/>
+      <c r="BP34" s="4"/>
+      <c r="BQ34" s="4"/>
+      <c r="BR34" s="4"/>
+      <c r="BS34" s="4"/>
+      <c r="BT34" s="4"/>
+      <c r="BU34" s="4"/>
+      <c r="BV34" s="4"/>
+      <c r="BW34" s="4"/>
+      <c r="BX34" s="4"/>
+      <c r="BY34" s="4"/>
+    </row>
+    <row r="35" spans="2:77" x14ac:dyDescent="0.35">
+      <c r="X35" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y35" s="2">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Z35" s="4" t="str">
+        <f>IF(MIN(Class_0!B9,Class_1!B9,Class_2!B9)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA35" s="4" t="str">
+        <f>IF(MIN(Class_0!C9,Class_1!C9,Class_2!C9)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB35" s="4" t="str">
+        <f>IF(MIN(Class_0!D9,Class_1!D9,Class_2!D9)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC35" s="4" t="str">
+        <f>IF(MIN(Class_0!E9,Class_1!E9,Class_2!E9)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD35" s="4" t="str">
+        <f>IF(MIN(Class_0!F9,Class_1!F9,Class_2!F9)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE35" s="4" t="str">
+        <f>IF(MIN(Class_0!G9,Class_1!G9,Class_2!G9)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF35" s="4" t="str">
+        <f>IF(MIN(Class_0!H9,Class_1!H9,Class_2!H9)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG35" s="5" t="str">
+        <f>IF(MIN(Class_0!I9,Class_1!I9,Class_2!I9)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH35" s="4"/>
+      <c r="AI35" s="4"/>
+      <c r="AJ35" s="4"/>
+      <c r="AK35" s="4"/>
+      <c r="AL35" s="4"/>
+      <c r="AM35" s="4"/>
+      <c r="AN35" s="4"/>
+      <c r="AO35" s="4"/>
+      <c r="AP35" s="4"/>
+      <c r="AQ35" s="4"/>
+      <c r="AR35" s="4"/>
+      <c r="AS35" s="4"/>
+      <c r="AT35" s="4"/>
+      <c r="AU35" s="4"/>
+      <c r="AV35" s="4"/>
+      <c r="AW35" s="4"/>
+      <c r="AX35" s="4"/>
+      <c r="AY35" s="4"/>
+      <c r="AZ35" s="4"/>
+      <c r="BA35" s="4"/>
+      <c r="BB35" s="4"/>
+      <c r="BC35" s="4"/>
+      <c r="BD35" s="4"/>
+      <c r="BE35" s="4"/>
+      <c r="BF35" s="4"/>
+      <c r="BG35" s="4"/>
+      <c r="BH35" s="4"/>
+      <c r="BI35" s="4"/>
+      <c r="BJ35" s="4"/>
+      <c r="BK35" s="4"/>
+      <c r="BL35" s="4"/>
+      <c r="BM35" s="4"/>
+      <c r="BN35" s="4"/>
+      <c r="BO35" s="4"/>
+      <c r="BP35" s="4"/>
+      <c r="BQ35" s="4"/>
+      <c r="BR35" s="4"/>
+      <c r="BS35" s="4"/>
+      <c r="BT35" s="4"/>
+      <c r="BU35" s="4"/>
+      <c r="BV35" s="4"/>
+      <c r="BW35" s="4"/>
+      <c r="BX35" s="4"/>
+      <c r="BY35" s="4"/>
+    </row>
+    <row r="36" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>58</v>
       </c>
+      <c r="X36" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y36" s="2">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="Z36" s="4" t="str">
+        <f>IF(MIN(Class_0!B10,Class_1!B10,Class_2!B10)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA36" s="4" t="str">
+        <f>IF(MIN(Class_0!C10,Class_1!C10,Class_2!C10)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB36" s="4" t="str">
+        <f>IF(MIN(Class_0!D10,Class_1!D10,Class_2!D10)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC36" s="4" t="str">
+        <f>IF(MIN(Class_0!E10,Class_1!E10,Class_2!E10)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD36" s="4" t="str">
+        <f>IF(MIN(Class_0!F10,Class_1!F10,Class_2!F10)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE36" s="4" t="str">
+        <f>IF(MIN(Class_0!G10,Class_1!G10,Class_2!G10)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF36" s="4" t="str">
+        <f>IF(MIN(Class_0!H10,Class_1!H10,Class_2!H10)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG36" s="4" t="str">
+        <f>IF(MIN(Class_0!I10,Class_1!I10,Class_2!I10)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH36" s="5" t="str">
+        <f>IF(MIN(Class_0!J10,Class_1!J10,Class_2!J10)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI36" s="4"/>
+      <c r="AJ36" s="4"/>
+      <c r="AK36" s="4"/>
+      <c r="AL36" s="4"/>
+      <c r="AM36" s="4"/>
+      <c r="AN36" s="4"/>
+      <c r="AO36" s="4"/>
+      <c r="AP36" s="4"/>
+      <c r="AQ36" s="4"/>
+      <c r="AR36" s="4"/>
+      <c r="AS36" s="4"/>
+      <c r="AT36" s="4"/>
+      <c r="AU36" s="4"/>
+      <c r="AV36" s="4"/>
+      <c r="AW36" s="4"/>
+      <c r="AX36" s="4"/>
+      <c r="AY36" s="4"/>
+      <c r="AZ36" s="4"/>
+      <c r="BA36" s="4"/>
+      <c r="BB36" s="4"/>
+      <c r="BC36" s="4"/>
+      <c r="BD36" s="4"/>
+      <c r="BE36" s="4"/>
+      <c r="BF36" s="4"/>
+      <c r="BG36" s="4"/>
+      <c r="BH36" s="4"/>
+      <c r="BI36" s="4"/>
+      <c r="BJ36" s="4"/>
+      <c r="BK36" s="4"/>
+      <c r="BL36" s="4"/>
+      <c r="BM36" s="4"/>
+      <c r="BN36" s="4"/>
+      <c r="BO36" s="4"/>
+      <c r="BP36" s="4"/>
+      <c r="BQ36" s="4"/>
+      <c r="BR36" s="4"/>
+      <c r="BS36" s="4"/>
+      <c r="BT36" s="4"/>
+      <c r="BU36" s="4"/>
+      <c r="BV36" s="4"/>
+      <c r="BW36" s="4"/>
+      <c r="BX36" s="4"/>
+      <c r="BY36" s="4"/>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>58</v>
       </c>
+      <c r="X37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y37" s="2">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="Z37" s="4" t="str">
+        <f>IF(MIN(Class_0!B11,Class_1!B11,Class_2!B11)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA37" s="4" t="str">
+        <f>IF(MIN(Class_0!C11,Class_1!C11,Class_2!C11)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB37" s="4" t="str">
+        <f>IF(MIN(Class_0!D11,Class_1!D11,Class_2!D11)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC37" s="4" t="str">
+        <f>IF(MIN(Class_0!E11,Class_1!E11,Class_2!E11)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD37" s="4" t="str">
+        <f>IF(MIN(Class_0!F11,Class_1!F11,Class_2!F11)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE37" s="4" t="str">
+        <f>IF(MIN(Class_0!G11,Class_1!G11,Class_2!G11)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF37" s="4" t="str">
+        <f>IF(MIN(Class_0!H11,Class_1!H11,Class_2!H11)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG37" s="4" t="str">
+        <f>IF(MIN(Class_0!I11,Class_1!I11,Class_2!I11)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH37" s="4" t="str">
+        <f>IF(MIN(Class_0!J11,Class_1!J11,Class_2!J11)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI37" s="5" t="str">
+        <f>IF(MIN(Class_0!K11,Class_1!K11,Class_2!K11)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ37" s="4"/>
+      <c r="AK37" s="4"/>
+      <c r="AL37" s="4"/>
+      <c r="AM37" s="4"/>
+      <c r="AN37" s="4"/>
+      <c r="AO37" s="4"/>
+      <c r="AP37" s="4"/>
+      <c r="AQ37" s="4"/>
+      <c r="AR37" s="4"/>
+      <c r="AS37" s="4"/>
+      <c r="AT37" s="4"/>
+      <c r="AU37" s="4"/>
+      <c r="AV37" s="4"/>
+      <c r="AW37" s="4"/>
+      <c r="AX37" s="4"/>
+      <c r="AY37" s="4"/>
+      <c r="AZ37" s="4"/>
+      <c r="BA37" s="4"/>
+      <c r="BB37" s="4"/>
+      <c r="BC37" s="4"/>
+      <c r="BD37" s="4"/>
+      <c r="BE37" s="4"/>
+      <c r="BF37" s="4"/>
+      <c r="BG37" s="4"/>
+      <c r="BH37" s="4"/>
+      <c r="BI37" s="4"/>
+      <c r="BJ37" s="4"/>
+      <c r="BK37" s="4"/>
+      <c r="BL37" s="4"/>
+      <c r="BM37" s="4"/>
+      <c r="BN37" s="4"/>
+      <c r="BO37" s="4"/>
+      <c r="BP37" s="4"/>
+      <c r="BQ37" s="4"/>
+      <c r="BR37" s="4"/>
+      <c r="BS37" s="4"/>
+      <c r="BT37" s="4"/>
+      <c r="BU37" s="4"/>
+      <c r="BV37" s="4"/>
+      <c r="BW37" s="4"/>
+      <c r="BX37" s="4"/>
+      <c r="BY37" s="4"/>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>58</v>
       </c>
+      <c r="X38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y38" s="2">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="Z38" s="4" t="str">
+        <f>IF(MIN(Class_0!B12,Class_1!B12,Class_2!B12)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA38" s="4" t="str">
+        <f>IF(MIN(Class_0!C12,Class_1!C12,Class_2!C12)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB38" s="4" t="str">
+        <f>IF(MIN(Class_0!D12,Class_1!D12,Class_2!D12)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC38" s="4" t="str">
+        <f>IF(MIN(Class_0!E12,Class_1!E12,Class_2!E12)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD38" s="4" t="str">
+        <f>IF(MIN(Class_0!F12,Class_1!F12,Class_2!F12)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE38" s="4" t="str">
+        <f>IF(MIN(Class_0!G12,Class_1!G12,Class_2!G12)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF38" s="4" t="str">
+        <f>IF(MIN(Class_0!H12,Class_1!H12,Class_2!H12)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG38" s="4" t="str">
+        <f>IF(MIN(Class_0!I12,Class_1!I12,Class_2!I12)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH38" s="4" t="str">
+        <f>IF(MIN(Class_0!J12,Class_1!J12,Class_2!J12)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI38" s="4" t="str">
+        <f>IF(MIN(Class_0!K12,Class_1!K12,Class_2!K12)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ38" s="4" t="str">
+        <f>IF(MIN(Class_0!L12,Class_1!L12,Class_2!L12)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK38" s="4"/>
+      <c r="AL38" s="4"/>
+      <c r="AM38" s="4"/>
+      <c r="AN38" s="4"/>
+      <c r="AO38" s="4"/>
+      <c r="AP38" s="4"/>
+      <c r="AQ38" s="4"/>
+      <c r="AR38" s="4"/>
+      <c r="AS38" s="4"/>
+      <c r="AT38" s="4"/>
+      <c r="AU38" s="4"/>
+      <c r="AV38" s="4"/>
+      <c r="AW38" s="4"/>
+      <c r="AX38" s="4"/>
+      <c r="AY38" s="4"/>
+      <c r="AZ38" s="4"/>
+      <c r="BA38" s="4"/>
+      <c r="BB38" s="4"/>
+      <c r="BC38" s="4"/>
+      <c r="BD38" s="4"/>
+      <c r="BE38" s="4"/>
+      <c r="BF38" s="4"/>
+      <c r="BG38" s="4"/>
+      <c r="BH38" s="4"/>
+      <c r="BI38" s="4"/>
+      <c r="BJ38" s="4"/>
+      <c r="BK38" s="4"/>
+      <c r="BL38" s="4"/>
+      <c r="BM38" s="4"/>
+      <c r="BN38" s="4"/>
+      <c r="BO38" s="4"/>
+      <c r="BP38" s="4"/>
+      <c r="BQ38" s="4"/>
+      <c r="BR38" s="4"/>
+      <c r="BS38" s="4"/>
+      <c r="BT38" s="4"/>
+      <c r="BU38" s="4"/>
+      <c r="BV38" s="4"/>
+      <c r="BW38" s="4"/>
+      <c r="BX38" s="4"/>
+      <c r="BY38" s="4"/>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>58</v>
       </c>
+      <c r="X39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y39" s="2">
+        <f t="shared" si="7"/>
+        <v>11</v>
+      </c>
+      <c r="Z39" s="4" t="str">
+        <f>IF(MIN(Class_0!B13,Class_1!B13,Class_2!B13)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA39" s="4" t="str">
+        <f>IF(MIN(Class_0!C13,Class_1!C13,Class_2!C13)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB39" s="4" t="str">
+        <f>IF(MIN(Class_0!D13,Class_1!D13,Class_2!D13)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC39" s="4" t="str">
+        <f>IF(MIN(Class_0!E13,Class_1!E13,Class_2!E13)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD39" s="4" t="str">
+        <f>IF(MIN(Class_0!F13,Class_1!F13,Class_2!F13)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE39" s="4" t="str">
+        <f>IF(MIN(Class_0!G13,Class_1!G13,Class_2!G13)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF39" s="4" t="str">
+        <f>IF(MIN(Class_0!H13,Class_1!H13,Class_2!H13)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG39" s="4" t="str">
+        <f>IF(MIN(Class_0!I13,Class_1!I13,Class_2!I13)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH39" s="4" t="str">
+        <f>IF(MIN(Class_0!J13,Class_1!J13,Class_2!J13)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI39" s="4" t="str">
+        <f>IF(MIN(Class_0!K13,Class_1!K13,Class_2!K13)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ39" s="4" t="str">
+        <f>IF(MIN(Class_0!L13,Class_1!L13,Class_2!L13)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK39" s="4" t="str">
+        <f>IF(MIN(Class_0!M13,Class_1!M13,Class_2!M13)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL39" s="4"/>
+      <c r="AM39" s="4"/>
+      <c r="AN39" s="4"/>
+      <c r="AO39" s="4"/>
+      <c r="AP39" s="4"/>
+      <c r="AQ39" s="4"/>
+      <c r="AR39" s="4"/>
+      <c r="AS39" s="4"/>
+      <c r="AT39" s="4"/>
+      <c r="AU39" s="4"/>
+      <c r="AV39" s="4"/>
+      <c r="AW39" s="4"/>
+      <c r="AX39" s="4"/>
+      <c r="AY39" s="4"/>
+      <c r="AZ39" s="4"/>
+      <c r="BA39" s="4"/>
+      <c r="BB39" s="4"/>
+      <c r="BC39" s="4"/>
+      <c r="BD39" s="4"/>
+      <c r="BE39" s="4"/>
+      <c r="BF39" s="4"/>
+      <c r="BG39" s="4"/>
+      <c r="BH39" s="4"/>
+      <c r="BI39" s="4"/>
+      <c r="BJ39" s="4"/>
+      <c r="BK39" s="4"/>
+      <c r="BL39" s="4"/>
+      <c r="BM39" s="4"/>
+      <c r="BN39" s="4"/>
+      <c r="BO39" s="4"/>
+      <c r="BP39" s="4"/>
+      <c r="BQ39" s="4"/>
+      <c r="BR39" s="4"/>
+      <c r="BS39" s="4"/>
+      <c r="BT39" s="4"/>
+      <c r="BU39" s="4"/>
+      <c r="BV39" s="4"/>
+      <c r="BW39" s="4"/>
+      <c r="BX39" s="4"/>
+      <c r="BY39" s="4"/>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:77" x14ac:dyDescent="0.35">
+      <c r="X40" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y40" s="2">
+        <f t="shared" si="7"/>
+        <v>12</v>
+      </c>
+      <c r="Z40" s="4" t="str">
+        <f>IF(MIN(Class_0!B14,Class_1!B14,Class_2!B14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA40" s="4" t="str">
+        <f>IF(MIN(Class_0!C14,Class_1!C14,Class_2!C14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB40" s="4" t="str">
+        <f>IF(MIN(Class_0!D14,Class_1!D14,Class_2!D14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC40" s="4" t="str">
+        <f>IF(MIN(Class_0!E14,Class_1!E14,Class_2!E14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD40" s="4" t="str">
+        <f>IF(MIN(Class_0!F14,Class_1!F14,Class_2!F14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE40" s="4" t="str">
+        <f>IF(MIN(Class_0!G14,Class_1!G14,Class_2!G14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF40" s="4" t="str">
+        <f>IF(MIN(Class_0!H14,Class_1!H14,Class_2!H14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG40" s="4" t="str">
+        <f>IF(MIN(Class_0!I14,Class_1!I14,Class_2!I14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH40" s="4" t="str">
+        <f>IF(MIN(Class_0!J14,Class_1!J14,Class_2!J14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI40" s="4" t="str">
+        <f>IF(MIN(Class_0!K14,Class_1!K14,Class_2!K14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ40" s="4" t="str">
+        <f>IF(MIN(Class_0!L14,Class_1!L14,Class_2!L14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK40" s="4" t="str">
+        <f>IF(MIN(Class_0!M14,Class_1!M14,Class_2!M14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL40" s="4" t="str">
+        <f>IF(MIN(Class_0!N14,Class_1!N14,Class_2!N14)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM40" s="4"/>
+      <c r="AN40" s="4"/>
+      <c r="AO40" s="4"/>
+      <c r="AP40" s="4"/>
+      <c r="AQ40" s="4"/>
+      <c r="AR40" s="4"/>
+      <c r="AS40" s="4"/>
+      <c r="AT40" s="4"/>
+      <c r="AU40" s="4"/>
+      <c r="AV40" s="4"/>
+      <c r="AW40" s="4"/>
+      <c r="AX40" s="4"/>
+      <c r="AY40" s="4"/>
+      <c r="AZ40" s="4"/>
+      <c r="BA40" s="4"/>
+      <c r="BB40" s="4"/>
+      <c r="BC40" s="4"/>
+      <c r="BD40" s="4"/>
+      <c r="BE40" s="4"/>
+      <c r="BF40" s="4"/>
+      <c r="BG40" s="4"/>
+      <c r="BH40" s="4"/>
+      <c r="BI40" s="4"/>
+      <c r="BJ40" s="4"/>
+      <c r="BK40" s="4"/>
+      <c r="BL40" s="4"/>
+      <c r="BM40" s="4"/>
+      <c r="BN40" s="4"/>
+      <c r="BO40" s="4"/>
+      <c r="BP40" s="4"/>
+      <c r="BQ40" s="4"/>
+      <c r="BR40" s="4"/>
+      <c r="BS40" s="4"/>
+      <c r="BT40" s="4"/>
+      <c r="BU40" s="4"/>
+      <c r="BV40" s="4"/>
+      <c r="BW40" s="4"/>
+      <c r="BX40" s="4"/>
+      <c r="BY40" s="4"/>
+    </row>
+    <row r="41" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>58</v>
       </c>
+      <c r="X41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y41" s="2">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="Z41" s="4" t="str">
+        <f>IF(MIN(Class_0!B15,Class_1!B15,Class_2!B15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA41" s="4" t="str">
+        <f>IF(MIN(Class_0!C15,Class_1!C15,Class_2!C15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB41" s="4" t="str">
+        <f>IF(MIN(Class_0!D15,Class_1!D15,Class_2!D15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC41" s="4" t="str">
+        <f>IF(MIN(Class_0!E15,Class_1!E15,Class_2!E15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD41" s="4" t="str">
+        <f>IF(MIN(Class_0!F15,Class_1!F15,Class_2!F15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE41" s="4" t="str">
+        <f>IF(MIN(Class_0!G15,Class_1!G15,Class_2!G15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF41" s="4" t="str">
+        <f>IF(MIN(Class_0!H15,Class_1!H15,Class_2!H15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG41" s="4" t="str">
+        <f>IF(MIN(Class_0!I15,Class_1!I15,Class_2!I15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH41" s="4" t="str">
+        <f>IF(MIN(Class_0!J15,Class_1!J15,Class_2!J15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI41" s="4" t="str">
+        <f>IF(MIN(Class_0!K15,Class_1!K15,Class_2!K15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ41" s="4" t="str">
+        <f>IF(MIN(Class_0!L15,Class_1!L15,Class_2!L15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK41" s="4" t="str">
+        <f>IF(MIN(Class_0!M15,Class_1!M15,Class_2!M15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL41" s="4" t="str">
+        <f>IF(MIN(Class_0!N15,Class_1!N15,Class_2!N15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM41" s="4" t="str">
+        <f>IF(MIN(Class_0!O15,Class_1!O15,Class_2!O15)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN41" s="4"/>
+      <c r="AO41" s="4"/>
+      <c r="AP41" s="4"/>
+      <c r="AQ41" s="4"/>
+      <c r="AR41" s="4"/>
+      <c r="AS41" s="4"/>
+      <c r="AT41" s="4"/>
+      <c r="AU41" s="4"/>
+      <c r="AV41" s="4"/>
+      <c r="AW41" s="4"/>
+      <c r="AX41" s="4"/>
+      <c r="AY41" s="4"/>
+      <c r="AZ41" s="4"/>
+      <c r="BA41" s="4"/>
+      <c r="BB41" s="4"/>
+      <c r="BC41" s="4"/>
+      <c r="BD41" s="4"/>
+      <c r="BE41" s="4"/>
+      <c r="BF41" s="4"/>
+      <c r="BG41" s="4"/>
+      <c r="BH41" s="4"/>
+      <c r="BI41" s="4"/>
+      <c r="BJ41" s="4"/>
+      <c r="BK41" s="4"/>
+      <c r="BL41" s="4"/>
+      <c r="BM41" s="4"/>
+      <c r="BN41" s="4"/>
+      <c r="BO41" s="4"/>
+      <c r="BP41" s="4"/>
+      <c r="BQ41" s="4"/>
+      <c r="BR41" s="4"/>
+      <c r="BS41" s="4"/>
+      <c r="BT41" s="4"/>
+      <c r="BU41" s="4"/>
+      <c r="BV41" s="4"/>
+      <c r="BW41" s="4"/>
+      <c r="BX41" s="4"/>
+      <c r="BY41" s="4"/>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>58</v>
       </c>
+      <c r="X42" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y42" s="2">
+        <f t="shared" si="7"/>
+        <v>14</v>
+      </c>
+      <c r="Z42" s="4" t="str">
+        <f>IF(MIN(Class_0!B16,Class_1!B16,Class_2!B16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA42" s="4" t="str">
+        <f>IF(MIN(Class_0!C16,Class_1!C16,Class_2!C16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB42" s="4" t="str">
+        <f>IF(MIN(Class_0!D16,Class_1!D16,Class_2!D16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC42" s="4" t="str">
+        <f>IF(MIN(Class_0!E16,Class_1!E16,Class_2!E16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD42" s="4" t="str">
+        <f>IF(MIN(Class_0!F16,Class_1!F16,Class_2!F16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE42" s="4" t="str">
+        <f>IF(MIN(Class_0!G16,Class_1!G16,Class_2!G16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF42" s="4" t="str">
+        <f>IF(MIN(Class_0!H16,Class_1!H16,Class_2!H16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG42" s="4" t="str">
+        <f>IF(MIN(Class_0!I16,Class_1!I16,Class_2!I16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH42" s="4" t="str">
+        <f>IF(MIN(Class_0!J16,Class_1!J16,Class_2!J16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI42" s="4" t="str">
+        <f>IF(MIN(Class_0!K16,Class_1!K16,Class_2!K16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ42" s="4" t="str">
+        <f>IF(MIN(Class_0!L16,Class_1!L16,Class_2!L16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK42" s="4" t="str">
+        <f>IF(MIN(Class_0!M16,Class_1!M16,Class_2!M16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL42" s="4" t="str">
+        <f>IF(MIN(Class_0!N16,Class_1!N16,Class_2!N16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM42" s="4" t="str">
+        <f>IF(MIN(Class_0!O16,Class_1!O16,Class_2!O16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN42" s="4" t="str">
+        <f>IF(MIN(Class_0!P16,Class_1!P16,Class_2!P16)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO42" s="4"/>
+      <c r="AP42" s="4"/>
+      <c r="AQ42" s="4"/>
+      <c r="AR42" s="4"/>
+      <c r="AS42" s="4"/>
+      <c r="AT42" s="4"/>
+      <c r="AU42" s="4"/>
+      <c r="AV42" s="4"/>
+      <c r="AW42" s="4"/>
+      <c r="AX42" s="4"/>
+      <c r="AY42" s="4"/>
+      <c r="AZ42" s="4"/>
+      <c r="BA42" s="4"/>
+      <c r="BB42" s="4"/>
+      <c r="BC42" s="4"/>
+      <c r="BD42" s="4"/>
+      <c r="BE42" s="4"/>
+      <c r="BF42" s="4"/>
+      <c r="BG42" s="4"/>
+      <c r="BH42" s="4"/>
+      <c r="BI42" s="4"/>
+      <c r="BJ42" s="4"/>
+      <c r="BK42" s="4"/>
+      <c r="BL42" s="4"/>
+      <c r="BM42" s="4"/>
+      <c r="BN42" s="4"/>
+      <c r="BO42" s="4"/>
+      <c r="BP42" s="4"/>
+      <c r="BQ42" s="4"/>
+      <c r="BR42" s="4"/>
+      <c r="BS42" s="4"/>
+      <c r="BT42" s="4"/>
+      <c r="BU42" s="4"/>
+      <c r="BV42" s="4"/>
+      <c r="BW42" s="4"/>
+      <c r="BX42" s="4"/>
+      <c r="BY42" s="4"/>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
         <v>58</v>
       </c>
+      <c r="X43" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y43" s="2">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="Z43" s="4" t="str">
+        <f>IF(MIN(Class_0!B17,Class_1!B17,Class_2!B17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA43" s="4" t="str">
+        <f>IF(MIN(Class_0!C17,Class_1!C17,Class_2!C17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB43" s="4" t="str">
+        <f>IF(MIN(Class_0!D17,Class_1!D17,Class_2!D17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC43" s="4" t="str">
+        <f>IF(MIN(Class_0!E17,Class_1!E17,Class_2!E17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD43" s="4" t="str">
+        <f>IF(MIN(Class_0!F17,Class_1!F17,Class_2!F17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE43" s="4" t="str">
+        <f>IF(MIN(Class_0!G17,Class_1!G17,Class_2!G17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF43" s="4" t="str">
+        <f>IF(MIN(Class_0!H17,Class_1!H17,Class_2!H17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG43" s="4" t="str">
+        <f>IF(MIN(Class_0!I17,Class_1!I17,Class_2!I17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH43" s="4" t="str">
+        <f>IF(MIN(Class_0!J17,Class_1!J17,Class_2!J17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI43" s="4" t="str">
+        <f>IF(MIN(Class_0!K17,Class_1!K17,Class_2!K17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ43" s="4" t="str">
+        <f>IF(MIN(Class_0!L17,Class_1!L17,Class_2!L17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK43" s="4" t="str">
+        <f>IF(MIN(Class_0!M17,Class_1!M17,Class_2!M17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL43" s="4" t="str">
+        <f>IF(MIN(Class_0!N17,Class_1!N17,Class_2!N17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM43" s="4" t="str">
+        <f>IF(MIN(Class_0!O17,Class_1!O17,Class_2!O17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN43" s="4" t="str">
+        <f>IF(MIN(Class_0!P17,Class_1!P17,Class_2!P17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO43" s="4" t="str">
+        <f>IF(MIN(Class_0!Q17,Class_1!Q17,Class_2!Q17)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP43" s="4"/>
+      <c r="AQ43" s="4"/>
+      <c r="AR43" s="4"/>
+      <c r="AS43" s="4"/>
+      <c r="AT43" s="4"/>
+      <c r="AU43" s="4"/>
+      <c r="AV43" s="4"/>
+      <c r="AW43" s="4"/>
+      <c r="AX43" s="4"/>
+      <c r="AY43" s="4"/>
+      <c r="AZ43" s="4"/>
+      <c r="BA43" s="4"/>
+      <c r="BB43" s="4"/>
+      <c r="BC43" s="4"/>
+      <c r="BD43" s="4"/>
+      <c r="BE43" s="4"/>
+      <c r="BF43" s="4"/>
+      <c r="BG43" s="4"/>
+      <c r="BH43" s="4"/>
+      <c r="BI43" s="4"/>
+      <c r="BJ43" s="4"/>
+      <c r="BK43" s="4"/>
+      <c r="BL43" s="4"/>
+      <c r="BM43" s="4"/>
+      <c r="BN43" s="4"/>
+      <c r="BO43" s="4"/>
+      <c r="BP43" s="4"/>
+      <c r="BQ43" s="4"/>
+      <c r="BR43" s="4"/>
+      <c r="BS43" s="4"/>
+      <c r="BT43" s="4"/>
+      <c r="BU43" s="4"/>
+      <c r="BV43" s="4"/>
+      <c r="BW43" s="4"/>
+      <c r="BX43" s="4"/>
+      <c r="BY43" s="4"/>
     </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:77" x14ac:dyDescent="0.35">
+      <c r="X44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y44" s="2">
+        <f t="shared" si="7"/>
+        <v>16</v>
+      </c>
+      <c r="Z44" s="4" t="str">
+        <f>IF(MIN(Class_0!B18,Class_1!B18,Class_2!B18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA44" s="4" t="str">
+        <f>IF(MIN(Class_0!C18,Class_1!C18,Class_2!C18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB44" s="4" t="str">
+        <f>IF(MIN(Class_0!D18,Class_1!D18,Class_2!D18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC44" s="4" t="str">
+        <f>IF(MIN(Class_0!E18,Class_1!E18,Class_2!E18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD44" s="4" t="str">
+        <f>IF(MIN(Class_0!F18,Class_1!F18,Class_2!F18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE44" s="4" t="str">
+        <f>IF(MIN(Class_0!G18,Class_1!G18,Class_2!G18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF44" s="4" t="str">
+        <f>IF(MIN(Class_0!H18,Class_1!H18,Class_2!H18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG44" s="4" t="str">
+        <f>IF(MIN(Class_0!I18,Class_1!I18,Class_2!I18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH44" s="4" t="str">
+        <f>IF(MIN(Class_0!J18,Class_1!J18,Class_2!J18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI44" s="4" t="str">
+        <f>IF(MIN(Class_0!K18,Class_1!K18,Class_2!K18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ44" s="4" t="str">
+        <f>IF(MIN(Class_0!L18,Class_1!L18,Class_2!L18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK44" s="4" t="str">
+        <f>IF(MIN(Class_0!M18,Class_1!M18,Class_2!M18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL44" s="4" t="str">
+        <f>IF(MIN(Class_0!N18,Class_1!N18,Class_2!N18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM44" s="4" t="str">
+        <f>IF(MIN(Class_0!O18,Class_1!O18,Class_2!O18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN44" s="4" t="str">
+        <f>IF(MIN(Class_0!P18,Class_1!P18,Class_2!P18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO44" s="4" t="str">
+        <f>IF(MIN(Class_0!Q18,Class_1!Q18,Class_2!Q18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP44" s="4" t="str">
+        <f>IF(MIN(Class_0!R18,Class_1!R18,Class_2!R18)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ44" s="4"/>
+      <c r="AR44" s="4"/>
+      <c r="AS44" s="4"/>
+      <c r="AT44" s="4"/>
+      <c r="AU44" s="4"/>
+      <c r="AV44" s="4"/>
+      <c r="AW44" s="4"/>
+      <c r="AX44" s="4"/>
+      <c r="AY44" s="4"/>
+      <c r="AZ44" s="4"/>
+      <c r="BA44" s="4"/>
+      <c r="BB44" s="4"/>
+      <c r="BC44" s="4"/>
+      <c r="BD44" s="4"/>
+      <c r="BE44" s="4"/>
+      <c r="BF44" s="4"/>
+      <c r="BG44" s="4"/>
+      <c r="BH44" s="4"/>
+      <c r="BI44" s="4"/>
+      <c r="BJ44" s="4"/>
+      <c r="BK44" s="4"/>
+      <c r="BL44" s="4"/>
+      <c r="BM44" s="4"/>
+      <c r="BN44" s="4"/>
+      <c r="BO44" s="4"/>
+      <c r="BP44" s="4"/>
+      <c r="BQ44" s="4"/>
+      <c r="BR44" s="4"/>
+      <c r="BS44" s="4"/>
+      <c r="BT44" s="4"/>
+      <c r="BU44" s="4"/>
+      <c r="BV44" s="4"/>
+      <c r="BW44" s="4"/>
+      <c r="BX44" s="4"/>
+      <c r="BY44" s="4"/>
+    </row>
+    <row r="45" spans="2:77" x14ac:dyDescent="0.35">
+      <c r="X45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y45" s="2">
+        <f t="shared" si="7"/>
+        <v>17</v>
+      </c>
+      <c r="Z45" s="4" t="str">
+        <f>IF(MIN(Class_0!B19,Class_1!B19,Class_2!B19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA45" s="4" t="str">
+        <f>IF(MIN(Class_0!C19,Class_1!C19,Class_2!C19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB45" s="4" t="str">
+        <f>IF(MIN(Class_0!D19,Class_1!D19,Class_2!D19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC45" s="4" t="str">
+        <f>IF(MIN(Class_0!E19,Class_1!E19,Class_2!E19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD45" s="4" t="str">
+        <f>IF(MIN(Class_0!F19,Class_1!F19,Class_2!F19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE45" s="4" t="str">
+        <f>IF(MIN(Class_0!G19,Class_1!G19,Class_2!G19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF45" s="4" t="str">
+        <f>IF(MIN(Class_0!H19,Class_1!H19,Class_2!H19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG45" s="4" t="str">
+        <f>IF(MIN(Class_0!I19,Class_1!I19,Class_2!I19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH45" s="4" t="str">
+        <f>IF(MIN(Class_0!J19,Class_1!J19,Class_2!J19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI45" s="4" t="str">
+        <f>IF(MIN(Class_0!K19,Class_1!K19,Class_2!K19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ45" s="4" t="str">
+        <f>IF(MIN(Class_0!L19,Class_1!L19,Class_2!L19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK45" s="4" t="str">
+        <f>IF(MIN(Class_0!M19,Class_1!M19,Class_2!M19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL45" s="4" t="str">
+        <f>IF(MIN(Class_0!N19,Class_1!N19,Class_2!N19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM45" s="4" t="str">
+        <f>IF(MIN(Class_0!O19,Class_1!O19,Class_2!O19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN45" s="4" t="str">
+        <f>IF(MIN(Class_0!P19,Class_1!P19,Class_2!P19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO45" s="4" t="str">
+        <f>IF(MIN(Class_0!Q19,Class_1!Q19,Class_2!Q19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP45" s="4" t="str">
+        <f>IF(MIN(Class_0!R19,Class_1!R19,Class_2!R19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ45" s="4" t="str">
+        <f>IF(MIN(Class_0!S19,Class_1!S19,Class_2!S19)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR45" s="4"/>
+      <c r="AS45" s="4"/>
+      <c r="AT45" s="4"/>
+      <c r="AU45" s="4"/>
+      <c r="AV45" s="4"/>
+      <c r="AW45" s="4"/>
+      <c r="AX45" s="4"/>
+      <c r="AY45" s="4"/>
+      <c r="AZ45" s="4"/>
+      <c r="BA45" s="4"/>
+      <c r="BB45" s="4"/>
+      <c r="BC45" s="4"/>
+      <c r="BD45" s="4"/>
+      <c r="BE45" s="4"/>
+      <c r="BF45" s="4"/>
+      <c r="BG45" s="4"/>
+      <c r="BH45" s="4"/>
+      <c r="BI45" s="4"/>
+      <c r="BJ45" s="4"/>
+      <c r="BK45" s="4"/>
+      <c r="BL45" s="4"/>
+      <c r="BM45" s="4"/>
+      <c r="BN45" s="4"/>
+      <c r="BO45" s="4"/>
+      <c r="BP45" s="4"/>
+      <c r="BQ45" s="4"/>
+      <c r="BR45" s="4"/>
+      <c r="BS45" s="4"/>
+      <c r="BT45" s="4"/>
+      <c r="BU45" s="4"/>
+      <c r="BV45" s="4"/>
+      <c r="BW45" s="4"/>
+      <c r="BX45" s="4"/>
+      <c r="BY45" s="4"/>
+    </row>
+    <row r="46" spans="2:77" x14ac:dyDescent="0.35">
+      <c r="X46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y46" s="2">
+        <f t="shared" si="7"/>
+        <v>18</v>
+      </c>
+      <c r="Z46" s="4" t="str">
+        <f>IF(MIN(Class_0!B20,Class_1!B20,Class_2!B20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA46" s="4" t="str">
+        <f>IF(MIN(Class_0!C20,Class_1!C20,Class_2!C20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB46" s="4" t="str">
+        <f>IF(MIN(Class_0!D20,Class_1!D20,Class_2!D20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC46" s="4" t="str">
+        <f>IF(MIN(Class_0!E20,Class_1!E20,Class_2!E20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD46" s="4" t="str">
+        <f>IF(MIN(Class_0!F20,Class_1!F20,Class_2!F20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE46" s="4" t="str">
+        <f>IF(MIN(Class_0!G20,Class_1!G20,Class_2!G20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF46" s="4" t="str">
+        <f>IF(MIN(Class_0!H20,Class_1!H20,Class_2!H20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG46" s="4" t="str">
+        <f>IF(MIN(Class_0!I20,Class_1!I20,Class_2!I20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH46" s="4" t="str">
+        <f>IF(MIN(Class_0!J20,Class_1!J20,Class_2!J20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI46" s="4" t="str">
+        <f>IF(MIN(Class_0!K20,Class_1!K20,Class_2!K20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ46" s="4" t="str">
+        <f>IF(MIN(Class_0!L20,Class_1!L20,Class_2!L20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK46" s="4" t="str">
+        <f>IF(MIN(Class_0!M20,Class_1!M20,Class_2!M20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL46" s="4" t="str">
+        <f>IF(MIN(Class_0!N20,Class_1!N20,Class_2!N20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM46" s="4" t="str">
+        <f>IF(MIN(Class_0!O20,Class_1!O20,Class_2!O20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN46" s="4" t="str">
+        <f>IF(MIN(Class_0!P20,Class_1!P20,Class_2!P20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO46" s="4" t="str">
+        <f>IF(MIN(Class_0!Q20,Class_1!Q20,Class_2!Q20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP46" s="4" t="str">
+        <f>IF(MIN(Class_0!R20,Class_1!R20,Class_2!R20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ46" s="4" t="str">
+        <f>IF(MIN(Class_0!S20,Class_1!S20,Class_2!S20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR46" s="4" t="str">
+        <f>IF(MIN(Class_0!T20,Class_1!T20,Class_2!T20)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS46" s="4"/>
+      <c r="AT46" s="4"/>
+      <c r="AU46" s="4"/>
+      <c r="AV46" s="4"/>
+      <c r="AW46" s="4"/>
+      <c r="AX46" s="4"/>
+      <c r="AY46" s="4"/>
+      <c r="AZ46" s="4"/>
+      <c r="BA46" s="4"/>
+      <c r="BB46" s="4"/>
+      <c r="BC46" s="4"/>
+      <c r="BD46" s="4"/>
+      <c r="BE46" s="4"/>
+      <c r="BF46" s="4"/>
+      <c r="BG46" s="4"/>
+      <c r="BH46" s="4"/>
+      <c r="BI46" s="4"/>
+      <c r="BJ46" s="4"/>
+      <c r="BK46" s="4"/>
+      <c r="BL46" s="4"/>
+      <c r="BM46" s="4"/>
+      <c r="BN46" s="4"/>
+      <c r="BO46" s="4"/>
+      <c r="BP46" s="4"/>
+      <c r="BQ46" s="4"/>
+      <c r="BR46" s="4"/>
+      <c r="BS46" s="4"/>
+      <c r="BT46" s="4"/>
+      <c r="BU46" s="4"/>
+      <c r="BV46" s="4"/>
+      <c r="BW46" s="4"/>
+      <c r="BX46" s="4"/>
+      <c r="BY46" s="4"/>
+    </row>
+    <row r="47" spans="2:77" x14ac:dyDescent="0.35">
+      <c r="X47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y47" s="2">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="Z47" s="4" t="str">
+        <f>IF(MIN(Class_0!B21,Class_1!B21,Class_2!B21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA47" s="4" t="str">
+        <f>IF(MIN(Class_0!C21,Class_1!C21,Class_2!C21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB47" s="4" t="str">
+        <f>IF(MIN(Class_0!D21,Class_1!D21,Class_2!D21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC47" s="4" t="str">
+        <f>IF(MIN(Class_0!E21,Class_1!E21,Class_2!E21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD47" s="4" t="str">
+        <f>IF(MIN(Class_0!F21,Class_1!F21,Class_2!F21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE47" s="4" t="str">
+        <f>IF(MIN(Class_0!G21,Class_1!G21,Class_2!G21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF47" s="4" t="str">
+        <f>IF(MIN(Class_0!H21,Class_1!H21,Class_2!H21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG47" s="4" t="str">
+        <f>IF(MIN(Class_0!I21,Class_1!I21,Class_2!I21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH47" s="4" t="str">
+        <f>IF(MIN(Class_0!J21,Class_1!J21,Class_2!J21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI47" s="4" t="str">
+        <f>IF(MIN(Class_0!K21,Class_1!K21,Class_2!K21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ47" s="4" t="str">
+        <f>IF(MIN(Class_0!L21,Class_1!L21,Class_2!L21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK47" s="4" t="str">
+        <f>IF(MIN(Class_0!M21,Class_1!M21,Class_2!M21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL47" s="4" t="str">
+        <f>IF(MIN(Class_0!N21,Class_1!N21,Class_2!N21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM47" s="4" t="str">
+        <f>IF(MIN(Class_0!O21,Class_1!O21,Class_2!O21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN47" s="4" t="str">
+        <f>IF(MIN(Class_0!P21,Class_1!P21,Class_2!P21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO47" s="4" t="str">
+        <f>IF(MIN(Class_0!Q21,Class_1!Q21,Class_2!Q21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP47" s="4" t="str">
+        <f>IF(MIN(Class_0!R21,Class_1!R21,Class_2!R21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ47" s="4" t="str">
+        <f>IF(MIN(Class_0!S21,Class_1!S21,Class_2!S21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR47" s="4" t="str">
+        <f>IF(MIN(Class_0!T21,Class_1!T21,Class_2!T21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AS47" s="4" t="str">
+        <f>IF(MIN(Class_0!U21,Class_1!U21,Class_2!U21)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT47" s="4"/>
+      <c r="AU47" s="4"/>
+      <c r="AV47" s="4"/>
+      <c r="AW47" s="4"/>
+      <c r="AX47" s="4"/>
+      <c r="AY47" s="4"/>
+      <c r="AZ47" s="4"/>
+      <c r="BA47" s="4"/>
+      <c r="BB47" s="4"/>
+      <c r="BC47" s="4"/>
+      <c r="BD47" s="4"/>
+      <c r="BE47" s="4"/>
+      <c r="BF47" s="4"/>
+      <c r="BG47" s="4"/>
+      <c r="BH47" s="4"/>
+      <c r="BI47" s="4"/>
+      <c r="BJ47" s="4"/>
+      <c r="BK47" s="4"/>
+      <c r="BL47" s="4"/>
+      <c r="BM47" s="4"/>
+      <c r="BN47" s="4"/>
+      <c r="BO47" s="4"/>
+      <c r="BP47" s="4"/>
+      <c r="BQ47" s="4"/>
+      <c r="BR47" s="4"/>
+      <c r="BS47" s="4"/>
+      <c r="BT47" s="4"/>
+      <c r="BU47" s="4"/>
+      <c r="BV47" s="4"/>
+      <c r="BW47" s="4"/>
+      <c r="BX47" s="4"/>
+      <c r="BY47" s="4"/>
+    </row>
+    <row r="48" spans="2:77" x14ac:dyDescent="0.35">
+      <c r="X48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y48" s="2">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="Z48" s="4" t="str">
+        <f>IF(MIN(Class_0!B22,Class_1!B22,Class_2!B22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA48" s="4" t="str">
+        <f>IF(MIN(Class_0!C22,Class_1!C22,Class_2!C22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB48" s="4" t="str">
+        <f>IF(MIN(Class_0!D22,Class_1!D22,Class_2!D22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC48" s="4" t="str">
+        <f>IF(MIN(Class_0!E22,Class_1!E22,Class_2!E22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD48" s="4" t="str">
+        <f>IF(MIN(Class_0!F22,Class_1!F22,Class_2!F22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE48" s="4" t="str">
+        <f>IF(MIN(Class_0!G22,Class_1!G22,Class_2!G22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF48" s="4" t="str">
+        <f>IF(MIN(Class_0!H22,Class_1!H22,Class_2!H22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG48" s="4" t="str">
+        <f>IF(MIN(Class_0!I22,Class_1!I22,Class_2!I22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH48" s="4" t="str">
+        <f>IF(MIN(Class_0!J22,Class_1!J22,Class_2!J22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI48" s="4" t="str">
+        <f>IF(MIN(Class_0!K22,Class_1!K22,Class_2!K22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ48" s="4" t="str">
+        <f>IF(MIN(Class_0!L22,Class_1!L22,Class_2!L22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK48" s="4" t="str">
+        <f>IF(MIN(Class_0!M22,Class_1!M22,Class_2!M22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL48" s="4" t="str">
+        <f>IF(MIN(Class_0!N22,Class_1!N22,Class_2!N22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM48" s="4" t="str">
+        <f>IF(MIN(Class_0!O22,Class_1!O22,Class_2!O22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN48" s="4" t="str">
+        <f>IF(MIN(Class_0!P22,Class_1!P22,Class_2!P22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO48" s="4" t="str">
+        <f>IF(MIN(Class_0!Q22,Class_1!Q22,Class_2!Q22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP48" s="4" t="str">
+        <f>IF(MIN(Class_0!R22,Class_1!R22,Class_2!R22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ48" s="4" t="str">
+        <f>IF(MIN(Class_0!S22,Class_1!S22,Class_2!S22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR48" s="4" t="str">
+        <f>IF(MIN(Class_0!T22,Class_1!T22,Class_2!T22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS48" s="4" t="str">
+        <f>IF(MIN(Class_0!U22,Class_1!U22,Class_2!U22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT48" s="4" t="str">
+        <f>IF(MIN(Class_0!V22,Class_1!V22,Class_2!V22)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU48" s="4"/>
+      <c r="AV48" s="4"/>
+      <c r="AW48" s="4"/>
+      <c r="AX48" s="4"/>
+      <c r="AY48" s="4"/>
+      <c r="AZ48" s="4"/>
+      <c r="BA48" s="4"/>
+      <c r="BB48" s="4"/>
+      <c r="BC48" s="4"/>
+      <c r="BD48" s="4"/>
+      <c r="BE48" s="4"/>
+      <c r="BF48" s="4"/>
+      <c r="BG48" s="4"/>
+      <c r="BH48" s="4"/>
+      <c r="BI48" s="4"/>
+      <c r="BJ48" s="4"/>
+      <c r="BK48" s="4"/>
+      <c r="BL48" s="4"/>
+      <c r="BM48" s="4"/>
+      <c r="BN48" s="4"/>
+      <c r="BO48" s="4"/>
+      <c r="BP48" s="4"/>
+      <c r="BQ48" s="4"/>
+      <c r="BR48" s="4"/>
+      <c r="BS48" s="4"/>
+      <c r="BT48" s="4"/>
+      <c r="BU48" s="4"/>
+      <c r="BV48" s="4"/>
+      <c r="BW48" s="4"/>
+      <c r="BX48" s="4"/>
+      <c r="BY48" s="4"/>
+    </row>
+    <row r="49" spans="2:77" x14ac:dyDescent="0.35">
+      <c r="X49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y49" s="2">
+        <f t="shared" si="7"/>
+        <v>21</v>
+      </c>
+      <c r="Z49" s="4" t="str">
+        <f>IF(MIN(Class_0!B23,Class_1!B23,Class_2!B23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA49" s="4" t="str">
+        <f>IF(MIN(Class_0!C23,Class_1!C23,Class_2!C23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB49" s="4" t="str">
+        <f>IF(MIN(Class_0!D23,Class_1!D23,Class_2!D23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC49" s="4" t="str">
+        <f>IF(MIN(Class_0!E23,Class_1!E23,Class_2!E23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD49" s="4" t="str">
+        <f>IF(MIN(Class_0!F23,Class_1!F23,Class_2!F23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE49" s="4" t="str">
+        <f>IF(MIN(Class_0!G23,Class_1!G23,Class_2!G23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF49" s="4" t="str">
+        <f>IF(MIN(Class_0!H23,Class_1!H23,Class_2!H23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG49" s="4" t="str">
+        <f>IF(MIN(Class_0!I23,Class_1!I23,Class_2!I23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH49" s="4" t="str">
+        <f>IF(MIN(Class_0!J23,Class_1!J23,Class_2!J23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI49" s="4" t="str">
+        <f>IF(MIN(Class_0!K23,Class_1!K23,Class_2!K23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ49" s="4" t="str">
+        <f>IF(MIN(Class_0!L23,Class_1!L23,Class_2!L23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK49" s="4" t="str">
+        <f>IF(MIN(Class_0!M23,Class_1!M23,Class_2!M23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL49" s="4" t="str">
+        <f>IF(MIN(Class_0!N23,Class_1!N23,Class_2!N23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM49" s="4" t="str">
+        <f>IF(MIN(Class_0!O23,Class_1!O23,Class_2!O23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN49" s="4" t="str">
+        <f>IF(MIN(Class_0!P23,Class_1!P23,Class_2!P23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO49" s="4" t="str">
+        <f>IF(MIN(Class_0!Q23,Class_1!Q23,Class_2!Q23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP49" s="4" t="str">
+        <f>IF(MIN(Class_0!R23,Class_1!R23,Class_2!R23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ49" s="4" t="str">
+        <f>IF(MIN(Class_0!S23,Class_1!S23,Class_2!S23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR49" s="4" t="str">
+        <f>IF(MIN(Class_0!T23,Class_1!T23,Class_2!T23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS49" s="4" t="str">
+        <f>IF(MIN(Class_0!U23,Class_1!U23,Class_2!U23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT49" s="4" t="str">
+        <f>IF(MIN(Class_0!V23,Class_1!V23,Class_2!V23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU49" s="4" t="str">
+        <f>IF(MIN(Class_0!W23,Class_1!W23,Class_2!W23)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AV49" s="4"/>
+      <c r="AW49" s="4"/>
+      <c r="AX49" s="4"/>
+      <c r="AY49" s="4"/>
+      <c r="AZ49" s="4"/>
+      <c r="BA49" s="4"/>
+      <c r="BB49" s="4"/>
+      <c r="BC49" s="4"/>
+      <c r="BD49" s="4"/>
+      <c r="BE49" s="4"/>
+      <c r="BF49" s="4"/>
+      <c r="BG49" s="4"/>
+      <c r="BH49" s="4"/>
+      <c r="BI49" s="4"/>
+      <c r="BJ49" s="4"/>
+      <c r="BK49" s="4"/>
+      <c r="BL49" s="4"/>
+      <c r="BM49" s="4"/>
+      <c r="BN49" s="4"/>
+      <c r="BO49" s="4"/>
+      <c r="BP49" s="4"/>
+      <c r="BQ49" s="4"/>
+      <c r="BR49" s="4"/>
+      <c r="BS49" s="4"/>
+      <c r="BT49" s="4"/>
+      <c r="BU49" s="4"/>
+      <c r="BV49" s="4"/>
+      <c r="BW49" s="4"/>
+      <c r="BX49" s="4"/>
+      <c r="BY49" s="4"/>
+    </row>
+    <row r="50" spans="2:77" x14ac:dyDescent="0.35">
+      <c r="X50" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y50" s="2">
+        <f t="shared" si="7"/>
+        <v>22</v>
+      </c>
+      <c r="Z50" s="4" t="str">
+        <f>IF(MIN(Class_0!B24,Class_1!B24,Class_2!B24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA50" s="4" t="str">
+        <f>IF(MIN(Class_0!C24,Class_1!C24,Class_2!C24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB50" s="4" t="str">
+        <f>IF(MIN(Class_0!D24,Class_1!D24,Class_2!D24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC50" s="4" t="str">
+        <f>IF(MIN(Class_0!E24,Class_1!E24,Class_2!E24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AD50" s="4" t="str">
+        <f>IF(MIN(Class_0!F24,Class_1!F24,Class_2!F24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE50" s="4" t="str">
+        <f>IF(MIN(Class_0!G24,Class_1!G24,Class_2!G24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF50" s="4" t="str">
+        <f>IF(MIN(Class_0!H24,Class_1!H24,Class_2!H24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG50" s="4" t="str">
+        <f>IF(MIN(Class_0!I24,Class_1!I24,Class_2!I24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH50" s="4" t="str">
+        <f>IF(MIN(Class_0!J24,Class_1!J24,Class_2!J24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI50" s="4" t="str">
+        <f>IF(MIN(Class_0!K24,Class_1!K24,Class_2!K24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ50" s="4" t="str">
+        <f>IF(MIN(Class_0!L24,Class_1!L24,Class_2!L24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK50" s="4" t="str">
+        <f>IF(MIN(Class_0!M24,Class_1!M24,Class_2!M24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL50" s="4" t="str">
+        <f>IF(MIN(Class_0!N24,Class_1!N24,Class_2!N24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM50" s="4" t="str">
+        <f>IF(MIN(Class_0!O24,Class_1!O24,Class_2!O24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN50" s="4" t="str">
+        <f>IF(MIN(Class_0!P24,Class_1!P24,Class_2!P24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AO50" s="4" t="str">
+        <f>IF(MIN(Class_0!Q24,Class_1!Q24,Class_2!Q24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP50" s="4" t="str">
+        <f>IF(MIN(Class_0!R24,Class_1!R24,Class_2!R24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ50" s="4" t="str">
+        <f>IF(MIN(Class_0!S24,Class_1!S24,Class_2!S24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR50" s="4" t="str">
+        <f>IF(MIN(Class_0!T24,Class_1!T24,Class_2!T24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS50" s="4" t="str">
+        <f>IF(MIN(Class_0!U24,Class_1!U24,Class_2!U24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT50" s="4" t="str">
+        <f>IF(MIN(Class_0!V24,Class_1!V24,Class_2!V24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU50" s="4" t="str">
+        <f>IF(MIN(Class_0!W24,Class_1!W24,Class_2!W24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AV50" s="4" t="str">
+        <f>IF(MIN(Class_0!X24,Class_1!X24,Class_2!X24)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AW50" s="4"/>
+      <c r="AX50" s="4"/>
+      <c r="AY50" s="4"/>
+      <c r="AZ50" s="4"/>
+      <c r="BA50" s="4"/>
+      <c r="BB50" s="4"/>
+      <c r="BC50" s="4"/>
+      <c r="BD50" s="4"/>
+      <c r="BE50" s="4"/>
+      <c r="BF50" s="4"/>
+      <c r="BG50" s="4"/>
+      <c r="BH50" s="4"/>
+      <c r="BI50" s="4"/>
+      <c r="BJ50" s="4"/>
+      <c r="BK50" s="4"/>
+      <c r="BL50" s="4"/>
+      <c r="BM50" s="4"/>
+      <c r="BN50" s="4"/>
+      <c r="BO50" s="4"/>
+      <c r="BP50" s="4"/>
+      <c r="BQ50" s="4"/>
+      <c r="BR50" s="4"/>
+      <c r="BS50" s="4"/>
+      <c r="BT50" s="4"/>
+      <c r="BU50" s="4"/>
+      <c r="BV50" s="4"/>
+      <c r="BW50" s="4"/>
+      <c r="BX50" s="4"/>
+      <c r="BY50" s="4"/>
+    </row>
+    <row r="51" spans="2:77" x14ac:dyDescent="0.35">
+      <c r="X51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y51" s="2">
+        <f t="shared" si="7"/>
+        <v>23</v>
+      </c>
+      <c r="Z51" s="4" t="str">
+        <f>IF(MIN(Class_0!B25,Class_1!B25,Class_2!B25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA51" s="4" t="str">
+        <f>IF(MIN(Class_0!C25,Class_1!C25,Class_2!C25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB51" s="4" t="str">
+        <f>IF(MIN(Class_0!D25,Class_1!D25,Class_2!D25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC51" s="4" t="str">
+        <f>IF(MIN(Class_0!E25,Class_1!E25,Class_2!E25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD51" s="4" t="str">
+        <f>IF(MIN(Class_0!F25,Class_1!F25,Class_2!F25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE51" s="4" t="str">
+        <f>IF(MIN(Class_0!G25,Class_1!G25,Class_2!G25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF51" s="4" t="str">
+        <f>IF(MIN(Class_0!H25,Class_1!H25,Class_2!H25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG51" s="4" t="str">
+        <f>IF(MIN(Class_0!I25,Class_1!I25,Class_2!I25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH51" s="4" t="str">
+        <f>IF(MIN(Class_0!J25,Class_1!J25,Class_2!J25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI51" s="4" t="str">
+        <f>IF(MIN(Class_0!K25,Class_1!K25,Class_2!K25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ51" s="4" t="str">
+        <f>IF(MIN(Class_0!L25,Class_1!L25,Class_2!L25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK51" s="4" t="str">
+        <f>IF(MIN(Class_0!M25,Class_1!M25,Class_2!M25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL51" s="4" t="str">
+        <f>IF(MIN(Class_0!N25,Class_1!N25,Class_2!N25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM51" s="4" t="str">
+        <f>IF(MIN(Class_0!O25,Class_1!O25,Class_2!O25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN51" s="4" t="str">
+        <f>IF(MIN(Class_0!P25,Class_1!P25,Class_2!P25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO51" s="4" t="str">
+        <f>IF(MIN(Class_0!Q25,Class_1!Q25,Class_2!Q25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP51" s="4" t="str">
+        <f>IF(MIN(Class_0!R25,Class_1!R25,Class_2!R25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ51" s="4" t="str">
+        <f>IF(MIN(Class_0!S25,Class_1!S25,Class_2!S25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR51" s="4" t="str">
+        <f>IF(MIN(Class_0!T25,Class_1!T25,Class_2!T25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS51" s="4" t="str">
+        <f>IF(MIN(Class_0!U25,Class_1!U25,Class_2!U25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT51" s="4" t="str">
+        <f>IF(MIN(Class_0!V25,Class_1!V25,Class_2!V25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU51" s="4" t="str">
+        <f>IF(MIN(Class_0!W25,Class_1!W25,Class_2!W25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AV51" s="4" t="str">
+        <f>IF(MIN(Class_0!X25,Class_1!X25,Class_2!X25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AW51" s="4" t="str">
+        <f>IF(MIN(Class_0!Y25,Class_1!Y25,Class_2!Y25)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AX51" s="4"/>
+      <c r="AY51" s="4"/>
+      <c r="AZ51" s="4"/>
+      <c r="BA51" s="4"/>
+      <c r="BB51" s="4"/>
+      <c r="BC51" s="4"/>
+      <c r="BD51" s="4"/>
+      <c r="BE51" s="4"/>
+      <c r="BF51" s="4"/>
+      <c r="BG51" s="4"/>
+      <c r="BH51" s="4"/>
+      <c r="BI51" s="4"/>
+      <c r="BJ51" s="4"/>
+      <c r="BK51" s="4"/>
+      <c r="BL51" s="4"/>
+      <c r="BM51" s="4"/>
+      <c r="BN51" s="4"/>
+      <c r="BO51" s="4"/>
+      <c r="BP51" s="4"/>
+      <c r="BQ51" s="4"/>
+      <c r="BR51" s="4"/>
+      <c r="BS51" s="4"/>
+      <c r="BT51" s="4"/>
+      <c r="BU51" s="4"/>
+      <c r="BV51" s="4"/>
+      <c r="BW51" s="4"/>
+      <c r="BX51" s="4"/>
+      <c r="BY51" s="4"/>
+    </row>
+    <row r="52" spans="2:77" x14ac:dyDescent="0.35">
+      <c r="X52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y52" s="2">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="Z52" s="4" t="str">
+        <f>IF(MIN(Class_0!B26,Class_1!B26,Class_2!B26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA52" s="4" t="str">
+        <f>IF(MIN(Class_0!C26,Class_1!C26,Class_2!C26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB52" s="4" t="str">
+        <f>IF(MIN(Class_0!D26,Class_1!D26,Class_2!D26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC52" s="4" t="str">
+        <f>IF(MIN(Class_0!E26,Class_1!E26,Class_2!E26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD52" s="4" t="str">
+        <f>IF(MIN(Class_0!F26,Class_1!F26,Class_2!F26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE52" s="4" t="str">
+        <f>IF(MIN(Class_0!G26,Class_1!G26,Class_2!G26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF52" s="4" t="str">
+        <f>IF(MIN(Class_0!H26,Class_1!H26,Class_2!H26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG52" s="4" t="str">
+        <f>IF(MIN(Class_0!I26,Class_1!I26,Class_2!I26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH52" s="4" t="str">
+        <f>IF(MIN(Class_0!J26,Class_1!J26,Class_2!J26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI52" s="4" t="str">
+        <f>IF(MIN(Class_0!K26,Class_1!K26,Class_2!K26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ52" s="4" t="str">
+        <f>IF(MIN(Class_0!L26,Class_1!L26,Class_2!L26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK52" s="4" t="str">
+        <f>IF(MIN(Class_0!M26,Class_1!M26,Class_2!M26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL52" s="4" t="str">
+        <f>IF(MIN(Class_0!N26,Class_1!N26,Class_2!N26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM52" s="4" t="str">
+        <f>IF(MIN(Class_0!O26,Class_1!O26,Class_2!O26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN52" s="4" t="str">
+        <f>IF(MIN(Class_0!P26,Class_1!P26,Class_2!P26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO52" s="4" t="str">
+        <f>IF(MIN(Class_0!Q26,Class_1!Q26,Class_2!Q26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP52" s="4" t="str">
+        <f>IF(MIN(Class_0!R26,Class_1!R26,Class_2!R26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ52" s="4" t="str">
+        <f>IF(MIN(Class_0!S26,Class_1!S26,Class_2!S26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR52" s="4" t="str">
+        <f>IF(MIN(Class_0!T26,Class_1!T26,Class_2!T26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS52" s="4" t="str">
+        <f>IF(MIN(Class_0!U26,Class_1!U26,Class_2!U26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT52" s="4" t="str">
+        <f>IF(MIN(Class_0!V26,Class_1!V26,Class_2!V26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU52" s="4" t="str">
+        <f>IF(MIN(Class_0!W26,Class_1!W26,Class_2!W26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AV52" s="4" t="str">
+        <f>IF(MIN(Class_0!X26,Class_1!X26,Class_2!X26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW52" s="4" t="str">
+        <f>IF(MIN(Class_0!Y26,Class_1!Y26,Class_2!Y26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AX52" s="4" t="str">
+        <f>IF(MIN(Class_0!Z26,Class_1!Z26,Class_2!Z26)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AY52" s="4"/>
+      <c r="AZ52" s="4"/>
+      <c r="BA52" s="4"/>
+      <c r="BB52" s="4"/>
+      <c r="BC52" s="4"/>
+      <c r="BD52" s="4"/>
+      <c r="BE52" s="4"/>
+      <c r="BF52" s="4"/>
+      <c r="BG52" s="4"/>
+      <c r="BH52" s="4"/>
+      <c r="BI52" s="4"/>
+      <c r="BJ52" s="4"/>
+      <c r="BK52" s="4"/>
+      <c r="BL52" s="4"/>
+      <c r="BM52" s="4"/>
+      <c r="BN52" s="4"/>
+      <c r="BO52" s="4"/>
+      <c r="BP52" s="4"/>
+      <c r="BQ52" s="4"/>
+      <c r="BR52" s="4"/>
+      <c r="BS52" s="4"/>
+      <c r="BT52" s="4"/>
+      <c r="BU52" s="4"/>
+      <c r="BV52" s="4"/>
+      <c r="BW52" s="4"/>
+      <c r="BX52" s="4"/>
+      <c r="BY52" s="4"/>
+    </row>
+    <row r="53" spans="2:77" x14ac:dyDescent="0.35">
+      <c r="X53" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y53" s="2">
+        <f t="shared" si="7"/>
+        <v>25</v>
+      </c>
+      <c r="Z53" s="4" t="str">
+        <f>IF(MIN(Class_0!B27,Class_1!B27,Class_2!B27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA53" s="4" t="str">
+        <f>IF(MIN(Class_0!C27,Class_1!C27,Class_2!C27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB53" s="4" t="str">
+        <f>IF(MIN(Class_0!D27,Class_1!D27,Class_2!D27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC53" s="4" t="str">
+        <f>IF(MIN(Class_0!E27,Class_1!E27,Class_2!E27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD53" s="4" t="str">
+        <f>IF(MIN(Class_0!F27,Class_1!F27,Class_2!F27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE53" s="4" t="str">
+        <f>IF(MIN(Class_0!G27,Class_1!G27,Class_2!G27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF53" s="4" t="str">
+        <f>IF(MIN(Class_0!H27,Class_1!H27,Class_2!H27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG53" s="4" t="str">
+        <f>IF(MIN(Class_0!I27,Class_1!I27,Class_2!I27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH53" s="4" t="str">
+        <f>IF(MIN(Class_0!J27,Class_1!J27,Class_2!J27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI53" s="4" t="str">
+        <f>IF(MIN(Class_0!K27,Class_1!K27,Class_2!K27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ53" s="4" t="str">
+        <f>IF(MIN(Class_0!L27,Class_1!L27,Class_2!L27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK53" s="4" t="str">
+        <f>IF(MIN(Class_0!M27,Class_1!M27,Class_2!M27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL53" s="4" t="str">
+        <f>IF(MIN(Class_0!N27,Class_1!N27,Class_2!N27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM53" s="4" t="str">
+        <f>IF(MIN(Class_0!O27,Class_1!O27,Class_2!O27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN53" s="4" t="str">
+        <f>IF(MIN(Class_0!P27,Class_1!P27,Class_2!P27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO53" s="4" t="str">
+        <f>IF(MIN(Class_0!Q27,Class_1!Q27,Class_2!Q27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP53" s="4" t="str">
+        <f>IF(MIN(Class_0!R27,Class_1!R27,Class_2!R27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ53" s="4" t="str">
+        <f>IF(MIN(Class_0!S27,Class_1!S27,Class_2!S27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR53" s="4" t="str">
+        <f>IF(MIN(Class_0!T27,Class_1!T27,Class_2!T27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS53" s="4" t="str">
+        <f>IF(MIN(Class_0!U27,Class_1!U27,Class_2!U27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AT53" s="4" t="str">
+        <f>IF(MIN(Class_0!V27,Class_1!V27,Class_2!V27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU53" s="4" t="str">
+        <f>IF(MIN(Class_0!W27,Class_1!W27,Class_2!W27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV53" s="4" t="str">
+        <f>IF(MIN(Class_0!X27,Class_1!X27,Class_2!X27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW53" s="4" t="str">
+        <f>IF(MIN(Class_0!Y27,Class_1!Y27,Class_2!Y27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX53" s="4" t="str">
+        <f>IF(MIN(Class_0!Z27,Class_1!Z27,Class_2!Z27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY53" s="4" t="str">
+        <f>IF(MIN(Class_0!AA27,Class_1!AA27,Class_2!AA27)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ53" s="4"/>
+      <c r="BA53" s="4"/>
+      <c r="BB53" s="4"/>
+      <c r="BC53" s="4"/>
+      <c r="BD53" s="4"/>
+      <c r="BE53" s="4"/>
+      <c r="BF53" s="4"/>
+      <c r="BG53" s="4"/>
+      <c r="BH53" s="4"/>
+      <c r="BI53" s="4"/>
+      <c r="BJ53" s="4"/>
+      <c r="BK53" s="4"/>
+      <c r="BL53" s="4"/>
+      <c r="BM53" s="4"/>
+      <c r="BN53" s="4"/>
+      <c r="BO53" s="4"/>
+      <c r="BP53" s="4"/>
+      <c r="BQ53" s="4"/>
+      <c r="BR53" s="4"/>
+      <c r="BS53" s="4"/>
+      <c r="BT53" s="4"/>
+      <c r="BU53" s="4"/>
+      <c r="BV53" s="4"/>
+      <c r="BW53" s="4"/>
+      <c r="BX53" s="4"/>
+      <c r="BY53" s="4"/>
+    </row>
+    <row r="54" spans="2:77" x14ac:dyDescent="0.35">
+      <c r="X54" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y54" s="2">
+        <f t="shared" si="7"/>
+        <v>26</v>
+      </c>
+      <c r="Z54" s="4" t="str">
+        <f>IF(MIN(Class_0!B28,Class_1!B28,Class_2!B28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA54" s="4" t="str">
+        <f>IF(MIN(Class_0!C28,Class_1!C28,Class_2!C28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB54" s="4" t="str">
+        <f>IF(MIN(Class_0!D28,Class_1!D28,Class_2!D28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC54" s="4" t="str">
+        <f>IF(MIN(Class_0!E28,Class_1!E28,Class_2!E28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD54" s="4" t="str">
+        <f>IF(MIN(Class_0!F28,Class_1!F28,Class_2!F28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE54" s="4" t="str">
+        <f>IF(MIN(Class_0!G28,Class_1!G28,Class_2!G28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF54" s="4" t="str">
+        <f>IF(MIN(Class_0!H28,Class_1!H28,Class_2!H28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG54" s="4" t="str">
+        <f>IF(MIN(Class_0!I28,Class_1!I28,Class_2!I28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH54" s="4" t="str">
+        <f>IF(MIN(Class_0!J28,Class_1!J28,Class_2!J28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI54" s="4" t="str">
+        <f>IF(MIN(Class_0!K28,Class_1!K28,Class_2!K28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ54" s="4" t="str">
+        <f>IF(MIN(Class_0!L28,Class_1!L28,Class_2!L28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK54" s="4" t="str">
+        <f>IF(MIN(Class_0!M28,Class_1!M28,Class_2!M28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL54" s="4" t="str">
+        <f>IF(MIN(Class_0!N28,Class_1!N28,Class_2!N28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM54" s="4" t="str">
+        <f>IF(MIN(Class_0!O28,Class_1!O28,Class_2!O28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN54" s="4" t="str">
+        <f>IF(MIN(Class_0!P28,Class_1!P28,Class_2!P28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO54" s="4" t="str">
+        <f>IF(MIN(Class_0!Q28,Class_1!Q28,Class_2!Q28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP54" s="4" t="str">
+        <f>IF(MIN(Class_0!R28,Class_1!R28,Class_2!R28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ54" s="4" t="str">
+        <f>IF(MIN(Class_0!S28,Class_1!S28,Class_2!S28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR54" s="4" t="str">
+        <f>IF(MIN(Class_0!T28,Class_1!T28,Class_2!T28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS54" s="4" t="str">
+        <f>IF(MIN(Class_0!U28,Class_1!U28,Class_2!U28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT54" s="4" t="str">
+        <f>IF(MIN(Class_0!V28,Class_1!V28,Class_2!V28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU54" s="4" t="str">
+        <f>IF(MIN(Class_0!W28,Class_1!W28,Class_2!W28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV54" s="4" t="str">
+        <f>IF(MIN(Class_0!X28,Class_1!X28,Class_2!X28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AW54" s="4" t="str">
+        <f>IF(MIN(Class_0!Y28,Class_1!Y28,Class_2!Y28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX54" s="4" t="str">
+        <f>IF(MIN(Class_0!Z28,Class_1!Z28,Class_2!Z28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY54" s="4" t="str">
+        <f>IF(MIN(Class_0!AA28,Class_1!AA28,Class_2!AA28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ54" s="4" t="str">
+        <f>IF(MIN(Class_0!AB28,Class_1!AB28,Class_2!AB28)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA54" s="4"/>
+      <c r="BB54" s="4"/>
+      <c r="BC54" s="4"/>
+      <c r="BD54" s="4"/>
+      <c r="BE54" s="4"/>
+      <c r="BF54" s="4"/>
+      <c r="BG54" s="4"/>
+      <c r="BH54" s="4"/>
+      <c r="BI54" s="4"/>
+      <c r="BJ54" s="4"/>
+      <c r="BK54" s="4"/>
+      <c r="BL54" s="4"/>
+      <c r="BM54" s="4"/>
+      <c r="BN54" s="4"/>
+      <c r="BO54" s="4"/>
+      <c r="BP54" s="4"/>
+      <c r="BQ54" s="4"/>
+      <c r="BR54" s="4"/>
+      <c r="BS54" s="4"/>
+      <c r="BT54" s="4"/>
+      <c r="BU54" s="4"/>
+      <c r="BV54" s="4"/>
+      <c r="BW54" s="4"/>
+      <c r="BX54" s="4"/>
+      <c r="BY54" s="4"/>
+    </row>
+    <row r="55" spans="2:77" x14ac:dyDescent="0.35">
+      <c r="X55" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y55" s="2">
+        <f t="shared" si="7"/>
+        <v>27</v>
+      </c>
+      <c r="Z55" s="4" t="str">
+        <f>IF(MIN(Class_0!B29,Class_1!B29,Class_2!B29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA55" s="4" t="str">
+        <f>IF(MIN(Class_0!C29,Class_1!C29,Class_2!C29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB55" s="4" t="str">
+        <f>IF(MIN(Class_0!D29,Class_1!D29,Class_2!D29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC55" s="4" t="str">
+        <f>IF(MIN(Class_0!E29,Class_1!E29,Class_2!E29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD55" s="4" t="str">
+        <f>IF(MIN(Class_0!F29,Class_1!F29,Class_2!F29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE55" s="4" t="str">
+        <f>IF(MIN(Class_0!G29,Class_1!G29,Class_2!G29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF55" s="4" t="str">
+        <f>IF(MIN(Class_0!H29,Class_1!H29,Class_2!H29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG55" s="4" t="str">
+        <f>IF(MIN(Class_0!I29,Class_1!I29,Class_2!I29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH55" s="4" t="str">
+        <f>IF(MIN(Class_0!J29,Class_1!J29,Class_2!J29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI55" s="4" t="str">
+        <f>IF(MIN(Class_0!K29,Class_1!K29,Class_2!K29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ55" s="4" t="str">
+        <f>IF(MIN(Class_0!L29,Class_1!L29,Class_2!L29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK55" s="4" t="str">
+        <f>IF(MIN(Class_0!M29,Class_1!M29,Class_2!M29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL55" s="4" t="str">
+        <f>IF(MIN(Class_0!N29,Class_1!N29,Class_2!N29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM55" s="4" t="str">
+        <f>IF(MIN(Class_0!O29,Class_1!O29,Class_2!O29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN55" s="4" t="str">
+        <f>IF(MIN(Class_0!P29,Class_1!P29,Class_2!P29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO55" s="4" t="str">
+        <f>IF(MIN(Class_0!Q29,Class_1!Q29,Class_2!Q29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP55" s="4" t="str">
+        <f>IF(MIN(Class_0!R29,Class_1!R29,Class_2!R29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ55" s="4" t="str">
+        <f>IF(MIN(Class_0!S29,Class_1!S29,Class_2!S29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR55" s="4" t="str">
+        <f>IF(MIN(Class_0!T29,Class_1!T29,Class_2!T29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS55" s="4" t="str">
+        <f>IF(MIN(Class_0!U29,Class_1!U29,Class_2!U29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT55" s="4" t="str">
+        <f>IF(MIN(Class_0!V29,Class_1!V29,Class_2!V29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU55" s="4" t="str">
+        <f>IF(MIN(Class_0!W29,Class_1!W29,Class_2!W29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV55" s="4" t="str">
+        <f>IF(MIN(Class_0!X29,Class_1!X29,Class_2!X29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW55" s="4" t="str">
+        <f>IF(MIN(Class_0!Y29,Class_1!Y29,Class_2!Y29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX55" s="4" t="str">
+        <f>IF(MIN(Class_0!Z29,Class_1!Z29,Class_2!Z29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY55" s="4" t="str">
+        <f>IF(MIN(Class_0!AA29,Class_1!AA29,Class_2!AA29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ55" s="4" t="str">
+        <f>IF(MIN(Class_0!AB29,Class_1!AB29,Class_2!AB29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA55" s="4" t="str">
+        <f>IF(MIN(Class_0!AC29,Class_1!AC29,Class_2!AC29)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB55" s="4"/>
+      <c r="BC55" s="4"/>
+      <c r="BD55" s="4"/>
+      <c r="BE55" s="4"/>
+      <c r="BF55" s="4"/>
+      <c r="BG55" s="4"/>
+      <c r="BH55" s="4"/>
+      <c r="BI55" s="4"/>
+      <c r="BJ55" s="4"/>
+      <c r="BK55" s="4"/>
+      <c r="BL55" s="4"/>
+      <c r="BM55" s="4"/>
+      <c r="BN55" s="4"/>
+      <c r="BO55" s="4"/>
+      <c r="BP55" s="4"/>
+      <c r="BQ55" s="4"/>
+      <c r="BR55" s="4"/>
+      <c r="BS55" s="4"/>
+      <c r="BT55" s="4"/>
+      <c r="BU55" s="4"/>
+      <c r="BV55" s="4"/>
+      <c r="BW55" s="4"/>
+      <c r="BX55" s="4"/>
+      <c r="BY55" s="4"/>
+    </row>
+    <row r="56" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B56" t="s">
         <v>58</v>
       </c>
+      <c r="X56" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y56" s="2">
+        <f t="shared" si="7"/>
+        <v>28</v>
+      </c>
+      <c r="Z56" s="4" t="str">
+        <f>IF(MIN(Class_0!B30,Class_1!B30,Class_2!B30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA56" s="4" t="str">
+        <f>IF(MIN(Class_0!C30,Class_1!C30,Class_2!C30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB56" s="4" t="str">
+        <f>IF(MIN(Class_0!D30,Class_1!D30,Class_2!D30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC56" s="4" t="str">
+        <f>IF(MIN(Class_0!E30,Class_1!E30,Class_2!E30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD56" s="4" t="str">
+        <f>IF(MIN(Class_0!F30,Class_1!F30,Class_2!F30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE56" s="4" t="str">
+        <f>IF(MIN(Class_0!G30,Class_1!G30,Class_2!G30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF56" s="4" t="str">
+        <f>IF(MIN(Class_0!H30,Class_1!H30,Class_2!H30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG56" s="4" t="str">
+        <f>IF(MIN(Class_0!I30,Class_1!I30,Class_2!I30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH56" s="4" t="str">
+        <f>IF(MIN(Class_0!J30,Class_1!J30,Class_2!J30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI56" s="4" t="str">
+        <f>IF(MIN(Class_0!K30,Class_1!K30,Class_2!K30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ56" s="4" t="str">
+        <f>IF(MIN(Class_0!L30,Class_1!L30,Class_2!L30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK56" s="4" t="str">
+        <f>IF(MIN(Class_0!M30,Class_1!M30,Class_2!M30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL56" s="4" t="str">
+        <f>IF(MIN(Class_0!N30,Class_1!N30,Class_2!N30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM56" s="4" t="str">
+        <f>IF(MIN(Class_0!O30,Class_1!O30,Class_2!O30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN56" s="4" t="str">
+        <f>IF(MIN(Class_0!P30,Class_1!P30,Class_2!P30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO56" s="4" t="str">
+        <f>IF(MIN(Class_0!Q30,Class_1!Q30,Class_2!Q30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP56" s="4" t="str">
+        <f>IF(MIN(Class_0!R30,Class_1!R30,Class_2!R30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ56" s="4" t="str">
+        <f>IF(MIN(Class_0!S30,Class_1!S30,Class_2!S30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR56" s="4" t="str">
+        <f>IF(MIN(Class_0!T30,Class_1!T30,Class_2!T30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS56" s="4" t="str">
+        <f>IF(MIN(Class_0!U30,Class_1!U30,Class_2!U30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT56" s="4" t="str">
+        <f>IF(MIN(Class_0!V30,Class_1!V30,Class_2!V30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU56" s="4" t="str">
+        <f>IF(MIN(Class_0!W30,Class_1!W30,Class_2!W30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV56" s="4" t="str">
+        <f>IF(MIN(Class_0!X30,Class_1!X30,Class_2!X30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW56" s="4" t="str">
+        <f>IF(MIN(Class_0!Y30,Class_1!Y30,Class_2!Y30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX56" s="4" t="str">
+        <f>IF(MIN(Class_0!Z30,Class_1!Z30,Class_2!Z30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY56" s="4" t="str">
+        <f>IF(MIN(Class_0!AA30,Class_1!AA30,Class_2!AA30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AZ56" s="4" t="str">
+        <f>IF(MIN(Class_0!AB30,Class_1!AB30,Class_2!AB30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BA56" s="4" t="str">
+        <f>IF(MIN(Class_0!AC30,Class_1!AC30,Class_2!AC30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB56" s="4" t="str">
+        <f>IF(MIN(Class_0!AD30,Class_1!AD30,Class_2!AD30)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BC56" s="4"/>
+      <c r="BD56" s="4"/>
+      <c r="BE56" s="4"/>
+      <c r="BF56" s="4"/>
+      <c r="BG56" s="4"/>
+      <c r="BH56" s="4"/>
+      <c r="BI56" s="4"/>
+      <c r="BJ56" s="4"/>
+      <c r="BK56" s="4"/>
+      <c r="BL56" s="4"/>
+      <c r="BM56" s="4"/>
+      <c r="BN56" s="4"/>
+      <c r="BO56" s="4"/>
+      <c r="BP56" s="4"/>
+      <c r="BQ56" s="4"/>
+      <c r="BR56" s="4"/>
+      <c r="BS56" s="4"/>
+      <c r="BT56" s="4"/>
+      <c r="BU56" s="4"/>
+      <c r="BV56" s="4"/>
+      <c r="BW56" s="4"/>
+      <c r="BX56" s="4"/>
+      <c r="BY56" s="4"/>
     </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B57" t="s">
         <v>58</v>
       </c>
+      <c r="X57" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y57" s="2">
+        <f t="shared" si="7"/>
+        <v>29</v>
+      </c>
+      <c r="Z57" s="4" t="str">
+        <f>IF(MIN(Class_0!B31,Class_1!B31,Class_2!B31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA57" s="4" t="str">
+        <f>IF(MIN(Class_0!C31,Class_1!C31,Class_2!C31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB57" s="4" t="str">
+        <f>IF(MIN(Class_0!D31,Class_1!D31,Class_2!D31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC57" s="4" t="str">
+        <f>IF(MIN(Class_0!E31,Class_1!E31,Class_2!E31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD57" s="4" t="str">
+        <f>IF(MIN(Class_0!F31,Class_1!F31,Class_2!F31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE57" s="4" t="str">
+        <f>IF(MIN(Class_0!G31,Class_1!G31,Class_2!G31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF57" s="4" t="str">
+        <f>IF(MIN(Class_0!H31,Class_1!H31,Class_2!H31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG57" s="4" t="str">
+        <f>IF(MIN(Class_0!I31,Class_1!I31,Class_2!I31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH57" s="4" t="str">
+        <f>IF(MIN(Class_0!J31,Class_1!J31,Class_2!J31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI57" s="4" t="str">
+        <f>IF(MIN(Class_0!K31,Class_1!K31,Class_2!K31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ57" s="4" t="str">
+        <f>IF(MIN(Class_0!L31,Class_1!L31,Class_2!L31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK57" s="4" t="str">
+        <f>IF(MIN(Class_0!M31,Class_1!M31,Class_2!M31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL57" s="4" t="str">
+        <f>IF(MIN(Class_0!N31,Class_1!N31,Class_2!N31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM57" s="4" t="str">
+        <f>IF(MIN(Class_0!O31,Class_1!O31,Class_2!O31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN57" s="4" t="str">
+        <f>IF(MIN(Class_0!P31,Class_1!P31,Class_2!P31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO57" s="4" t="str">
+        <f>IF(MIN(Class_0!Q31,Class_1!Q31,Class_2!Q31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP57" s="4" t="str">
+        <f>IF(MIN(Class_0!R31,Class_1!R31,Class_2!R31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ57" s="4" t="str">
+        <f>IF(MIN(Class_0!S31,Class_1!S31,Class_2!S31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR57" s="4" t="str">
+        <f>IF(MIN(Class_0!T31,Class_1!T31,Class_2!T31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS57" s="4" t="str">
+        <f>IF(MIN(Class_0!U31,Class_1!U31,Class_2!U31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT57" s="4" t="str">
+        <f>IF(MIN(Class_0!V31,Class_1!V31,Class_2!V31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU57" s="4" t="str">
+        <f>IF(MIN(Class_0!W31,Class_1!W31,Class_2!W31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV57" s="4" t="str">
+        <f>IF(MIN(Class_0!X31,Class_1!X31,Class_2!X31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW57" s="4" t="str">
+        <f>IF(MIN(Class_0!Y31,Class_1!Y31,Class_2!Y31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX57" s="4" t="str">
+        <f>IF(MIN(Class_0!Z31,Class_1!Z31,Class_2!Z31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY57" s="4" t="str">
+        <f>IF(MIN(Class_0!AA31,Class_1!AA31,Class_2!AA31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AZ57" s="4" t="str">
+        <f>IF(MIN(Class_0!AB31,Class_1!AB31,Class_2!AB31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BA57" s="4" t="str">
+        <f>IF(MIN(Class_0!AC31,Class_1!AC31,Class_2!AC31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BB57" s="4" t="str">
+        <f>IF(MIN(Class_0!AD31,Class_1!AD31,Class_2!AD31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BC57" s="4" t="str">
+        <f>IF(MIN(Class_0!AE31,Class_1!AE31,Class_2!AE31)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BD57" s="4"/>
+      <c r="BE57" s="4"/>
+      <c r="BF57" s="4"/>
+      <c r="BG57" s="4"/>
+      <c r="BH57" s="4"/>
+      <c r="BI57" s="4"/>
+      <c r="BJ57" s="4"/>
+      <c r="BK57" s="4"/>
+      <c r="BL57" s="4"/>
+      <c r="BM57" s="4"/>
+      <c r="BN57" s="4"/>
+      <c r="BO57" s="4"/>
+      <c r="BP57" s="4"/>
+      <c r="BQ57" s="4"/>
+      <c r="BR57" s="4"/>
+      <c r="BS57" s="4"/>
+      <c r="BT57" s="4"/>
+      <c r="BU57" s="4"/>
+      <c r="BV57" s="4"/>
+      <c r="BW57" s="4"/>
+      <c r="BX57" s="4"/>
+      <c r="BY57" s="4"/>
     </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B58" t="s">
         <v>58</v>
       </c>
+      <c r="X58" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y58" s="2">
+        <f t="shared" si="7"/>
+        <v>30</v>
+      </c>
+      <c r="Z58" s="4" t="str">
+        <f>IF(MIN(Class_0!B32,Class_1!B32,Class_2!B32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA58" s="4" t="str">
+        <f>IF(MIN(Class_0!C32,Class_1!C32,Class_2!C32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB58" s="4" t="str">
+        <f>IF(MIN(Class_0!D32,Class_1!D32,Class_2!D32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC58" s="4" t="str">
+        <f>IF(MIN(Class_0!E32,Class_1!E32,Class_2!E32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD58" s="4" t="str">
+        <f>IF(MIN(Class_0!F32,Class_1!F32,Class_2!F32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE58" s="4" t="str">
+        <f>IF(MIN(Class_0!G32,Class_1!G32,Class_2!G32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF58" s="4" t="str">
+        <f>IF(MIN(Class_0!H32,Class_1!H32,Class_2!H32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG58" s="4" t="str">
+        <f>IF(MIN(Class_0!I32,Class_1!I32,Class_2!I32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH58" s="4" t="str">
+        <f>IF(MIN(Class_0!J32,Class_1!J32,Class_2!J32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI58" s="4" t="str">
+        <f>IF(MIN(Class_0!K32,Class_1!K32,Class_2!K32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ58" s="4" t="str">
+        <f>IF(MIN(Class_0!L32,Class_1!L32,Class_2!L32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK58" s="4" t="str">
+        <f>IF(MIN(Class_0!M32,Class_1!M32,Class_2!M32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL58" s="4" t="str">
+        <f>IF(MIN(Class_0!N32,Class_1!N32,Class_2!N32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM58" s="4" t="str">
+        <f>IF(MIN(Class_0!O32,Class_1!O32,Class_2!O32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN58" s="4" t="str">
+        <f>IF(MIN(Class_0!P32,Class_1!P32,Class_2!P32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO58" s="4" t="str">
+        <f>IF(MIN(Class_0!Q32,Class_1!Q32,Class_2!Q32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP58" s="4" t="str">
+        <f>IF(MIN(Class_0!R32,Class_1!R32,Class_2!R32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ58" s="4" t="str">
+        <f>IF(MIN(Class_0!S32,Class_1!S32,Class_2!S32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR58" s="4" t="str">
+        <f>IF(MIN(Class_0!T32,Class_1!T32,Class_2!T32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS58" s="4" t="str">
+        <f>IF(MIN(Class_0!U32,Class_1!U32,Class_2!U32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT58" s="4" t="str">
+        <f>IF(MIN(Class_0!V32,Class_1!V32,Class_2!V32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU58" s="4" t="str">
+        <f>IF(MIN(Class_0!W32,Class_1!W32,Class_2!W32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV58" s="4" t="str">
+        <f>IF(MIN(Class_0!X32,Class_1!X32,Class_2!X32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AW58" s="4" t="str">
+        <f>IF(MIN(Class_0!Y32,Class_1!Y32,Class_2!Y32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX58" s="4" t="str">
+        <f>IF(MIN(Class_0!Z32,Class_1!Z32,Class_2!Z32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY58" s="4" t="str">
+        <f>IF(MIN(Class_0!AA32,Class_1!AA32,Class_2!AA32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ58" s="4" t="str">
+        <f>IF(MIN(Class_0!AB32,Class_1!AB32,Class_2!AB32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA58" s="4" t="str">
+        <f>IF(MIN(Class_0!AC32,Class_1!AC32,Class_2!AC32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB58" s="4" t="str">
+        <f>IF(MIN(Class_0!AD32,Class_1!AD32,Class_2!AD32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BC58" s="4" t="str">
+        <f>IF(MIN(Class_0!AE32,Class_1!AE32,Class_2!AE32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BD58" s="4" t="str">
+        <f>IF(MIN(Class_0!AF32,Class_1!AF32,Class_2!AF32)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE58" s="4"/>
+      <c r="BF58" s="4"/>
+      <c r="BG58" s="4"/>
+      <c r="BH58" s="4"/>
+      <c r="BI58" s="4"/>
+      <c r="BJ58" s="4"/>
+      <c r="BK58" s="4"/>
+      <c r="BL58" s="4"/>
+      <c r="BM58" s="4"/>
+      <c r="BN58" s="4"/>
+      <c r="BO58" s="4"/>
+      <c r="BP58" s="4"/>
+      <c r="BQ58" s="4"/>
+      <c r="BR58" s="4"/>
+      <c r="BS58" s="4"/>
+      <c r="BT58" s="4"/>
+      <c r="BU58" s="4"/>
+      <c r="BV58" s="4"/>
+      <c r="BW58" s="4"/>
+      <c r="BX58" s="4"/>
+      <c r="BY58" s="4"/>
     </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
         <v>58</v>
       </c>
+      <c r="X59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y59" s="2">
+        <f t="shared" si="7"/>
+        <v>31</v>
+      </c>
+      <c r="Z59" s="4" t="str">
+        <f>IF(MIN(Class_0!B33,Class_1!B33,Class_2!B33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA59" s="4" t="str">
+        <f>IF(MIN(Class_0!C33,Class_1!C33,Class_2!C33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB59" s="4" t="str">
+        <f>IF(MIN(Class_0!D33,Class_1!D33,Class_2!D33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC59" s="4" t="str">
+        <f>IF(MIN(Class_0!E33,Class_1!E33,Class_2!E33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD59" s="4" t="str">
+        <f>IF(MIN(Class_0!F33,Class_1!F33,Class_2!F33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE59" s="4" t="str">
+        <f>IF(MIN(Class_0!G33,Class_1!G33,Class_2!G33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF59" s="4" t="str">
+        <f>IF(MIN(Class_0!H33,Class_1!H33,Class_2!H33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG59" s="4" t="str">
+        <f>IF(MIN(Class_0!I33,Class_1!I33,Class_2!I33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH59" s="4" t="str">
+        <f>IF(MIN(Class_0!J33,Class_1!J33,Class_2!J33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AI59" s="4" t="str">
+        <f>IF(MIN(Class_0!K33,Class_1!K33,Class_2!K33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ59" s="4" t="str">
+        <f>IF(MIN(Class_0!L33,Class_1!L33,Class_2!L33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK59" s="4" t="str">
+        <f>IF(MIN(Class_0!M33,Class_1!M33,Class_2!M33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL59" s="4" t="str">
+        <f>IF(MIN(Class_0!N33,Class_1!N33,Class_2!N33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM59" s="4" t="str">
+        <f>IF(MIN(Class_0!O33,Class_1!O33,Class_2!O33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN59" s="4" t="str">
+        <f>IF(MIN(Class_0!P33,Class_1!P33,Class_2!P33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO59" s="4" t="str">
+        <f>IF(MIN(Class_0!Q33,Class_1!Q33,Class_2!Q33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP59" s="4" t="str">
+        <f>IF(MIN(Class_0!R33,Class_1!R33,Class_2!R33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ59" s="4" t="str">
+        <f>IF(MIN(Class_0!S33,Class_1!S33,Class_2!S33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR59" s="4" t="str">
+        <f>IF(MIN(Class_0!T33,Class_1!T33,Class_2!T33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS59" s="4" t="str">
+        <f>IF(MIN(Class_0!U33,Class_1!U33,Class_2!U33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT59" s="4" t="str">
+        <f>IF(MIN(Class_0!V33,Class_1!V33,Class_2!V33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU59" s="4" t="str">
+        <f>IF(MIN(Class_0!W33,Class_1!W33,Class_2!W33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV59" s="4" t="str">
+        <f>IF(MIN(Class_0!X33,Class_1!X33,Class_2!X33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AW59" s="4" t="str">
+        <f>IF(MIN(Class_0!Y33,Class_1!Y33,Class_2!Y33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX59" s="4" t="str">
+        <f>IF(MIN(Class_0!Z33,Class_1!Z33,Class_2!Z33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY59" s="4" t="str">
+        <f>IF(MIN(Class_0!AA33,Class_1!AA33,Class_2!AA33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AZ59" s="4" t="str">
+        <f>IF(MIN(Class_0!AB33,Class_1!AB33,Class_2!AB33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA59" s="4" t="str">
+        <f>IF(MIN(Class_0!AC33,Class_1!AC33,Class_2!AC33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB59" s="4" t="str">
+        <f>IF(MIN(Class_0!AD33,Class_1!AD33,Class_2!AD33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BC59" s="4" t="str">
+        <f>IF(MIN(Class_0!AE33,Class_1!AE33,Class_2!AE33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BD59" s="4" t="str">
+        <f>IF(MIN(Class_0!AF33,Class_1!AF33,Class_2!AF33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE59" s="4" t="str">
+        <f>IF(MIN(Class_0!AG33,Class_1!AG33,Class_2!AG33)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BF59" s="4"/>
+      <c r="BG59" s="4"/>
+      <c r="BH59" s="4"/>
+      <c r="BI59" s="4"/>
+      <c r="BJ59" s="4"/>
+      <c r="BK59" s="4"/>
+      <c r="BL59" s="4"/>
+      <c r="BM59" s="4"/>
+      <c r="BN59" s="4"/>
+      <c r="BO59" s="4"/>
+      <c r="BP59" s="4"/>
+      <c r="BQ59" s="4"/>
+      <c r="BR59" s="4"/>
+      <c r="BS59" s="4"/>
+      <c r="BT59" s="4"/>
+      <c r="BU59" s="4"/>
+      <c r="BV59" s="4"/>
+      <c r="BW59" s="4"/>
+      <c r="BX59" s="4"/>
+      <c r="BY59" s="4"/>
     </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:77" x14ac:dyDescent="0.35">
+      <c r="X60" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y60" s="2">
+        <f t="shared" si="7"/>
+        <v>32</v>
+      </c>
+      <c r="Z60" s="4" t="str">
+        <f>IF(MIN(Class_0!B34,Class_1!B34,Class_2!B34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA60" s="4" t="str">
+        <f>IF(MIN(Class_0!C34,Class_1!C34,Class_2!C34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB60" s="4" t="str">
+        <f>IF(MIN(Class_0!D34,Class_1!D34,Class_2!D34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC60" s="4" t="str">
+        <f>IF(MIN(Class_0!E34,Class_1!E34,Class_2!E34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD60" s="4" t="str">
+        <f>IF(MIN(Class_0!F34,Class_1!F34,Class_2!F34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE60" s="4" t="str">
+        <f>IF(MIN(Class_0!G34,Class_1!G34,Class_2!G34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF60" s="4" t="str">
+        <f>IF(MIN(Class_0!H34,Class_1!H34,Class_2!H34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG60" s="4" t="str">
+        <f>IF(MIN(Class_0!I34,Class_1!I34,Class_2!I34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH60" s="4" t="str">
+        <f>IF(MIN(Class_0!J34,Class_1!J34,Class_2!J34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI60" s="4" t="str">
+        <f>IF(MIN(Class_0!K34,Class_1!K34,Class_2!K34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ60" s="4" t="str">
+        <f>IF(MIN(Class_0!L34,Class_1!L34,Class_2!L34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK60" s="4" t="str">
+        <f>IF(MIN(Class_0!M34,Class_1!M34,Class_2!M34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL60" s="4" t="str">
+        <f>IF(MIN(Class_0!N34,Class_1!N34,Class_2!N34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM60" s="4" t="str">
+        <f>IF(MIN(Class_0!O34,Class_1!O34,Class_2!O34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN60" s="4" t="str">
+        <f>IF(MIN(Class_0!P34,Class_1!P34,Class_2!P34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO60" s="4" t="str">
+        <f>IF(MIN(Class_0!Q34,Class_1!Q34,Class_2!Q34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP60" s="4" t="str">
+        <f>IF(MIN(Class_0!R34,Class_1!R34,Class_2!R34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ60" s="4" t="str">
+        <f>IF(MIN(Class_0!S34,Class_1!S34,Class_2!S34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR60" s="4" t="str">
+        <f>IF(MIN(Class_0!T34,Class_1!T34,Class_2!T34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS60" s="4" t="str">
+        <f>IF(MIN(Class_0!U34,Class_1!U34,Class_2!U34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT60" s="4" t="str">
+        <f>IF(MIN(Class_0!V34,Class_1!V34,Class_2!V34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU60" s="4" t="str">
+        <f>IF(MIN(Class_0!W34,Class_1!W34,Class_2!W34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV60" s="4" t="str">
+        <f>IF(MIN(Class_0!X34,Class_1!X34,Class_2!X34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW60" s="4" t="str">
+        <f>IF(MIN(Class_0!Y34,Class_1!Y34,Class_2!Y34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX60" s="4" t="str">
+        <f>IF(MIN(Class_0!Z34,Class_1!Z34,Class_2!Z34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY60" s="4" t="str">
+        <f>IF(MIN(Class_0!AA34,Class_1!AA34,Class_2!AA34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AZ60" s="4" t="str">
+        <f>IF(MIN(Class_0!AB34,Class_1!AB34,Class_2!AB34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA60" s="4" t="str">
+        <f>IF(MIN(Class_0!AC34,Class_1!AC34,Class_2!AC34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB60" s="4" t="str">
+        <f>IF(MIN(Class_0!AD34,Class_1!AD34,Class_2!AD34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BC60" s="4" t="str">
+        <f>IF(MIN(Class_0!AE34,Class_1!AE34,Class_2!AE34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BD60" s="4" t="str">
+        <f>IF(MIN(Class_0!AF34,Class_1!AF34,Class_2!AF34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE60" s="4" t="str">
+        <f>IF(MIN(Class_0!AG34,Class_1!AG34,Class_2!AG34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BF60" s="4" t="str">
+        <f>IF(MIN(Class_0!AH34,Class_1!AH34,Class_2!AH34)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BG60" s="4"/>
+      <c r="BH60" s="4"/>
+      <c r="BI60" s="4"/>
+      <c r="BJ60" s="4"/>
+      <c r="BK60" s="4"/>
+      <c r="BL60" s="4"/>
+      <c r="BM60" s="4"/>
+      <c r="BN60" s="4"/>
+      <c r="BO60" s="4"/>
+      <c r="BP60" s="4"/>
+      <c r="BQ60" s="4"/>
+      <c r="BR60" s="4"/>
+      <c r="BS60" s="4"/>
+      <c r="BT60" s="4"/>
+      <c r="BU60" s="4"/>
+      <c r="BV60" s="4"/>
+      <c r="BW60" s="4"/>
+      <c r="BX60" s="4"/>
+      <c r="BY60" s="4"/>
+    </row>
+    <row r="61" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B61" t="s">
         <v>58</v>
       </c>
+      <c r="X61" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y61" s="2">
+        <f t="shared" si="7"/>
+        <v>33</v>
+      </c>
+      <c r="Z61" s="4" t="str">
+        <f>IF(MIN(Class_0!B35,Class_1!B35,Class_2!B35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA61" s="4" t="str">
+        <f>IF(MIN(Class_0!C35,Class_1!C35,Class_2!C35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB61" s="4" t="str">
+        <f>IF(MIN(Class_0!D35,Class_1!D35,Class_2!D35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC61" s="4" t="str">
+        <f>IF(MIN(Class_0!E35,Class_1!E35,Class_2!E35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD61" s="4" t="str">
+        <f>IF(MIN(Class_0!F35,Class_1!F35,Class_2!F35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE61" s="4" t="str">
+        <f>IF(MIN(Class_0!G35,Class_1!G35,Class_2!G35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF61" s="4" t="str">
+        <f>IF(MIN(Class_0!H35,Class_1!H35,Class_2!H35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG61" s="4" t="str">
+        <f>IF(MIN(Class_0!I35,Class_1!I35,Class_2!I35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH61" s="4" t="str">
+        <f>IF(MIN(Class_0!J35,Class_1!J35,Class_2!J35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI61" s="4" t="str">
+        <f>IF(MIN(Class_0!K35,Class_1!K35,Class_2!K35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ61" s="4" t="str">
+        <f>IF(MIN(Class_0!L35,Class_1!L35,Class_2!L35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK61" s="4" t="str">
+        <f>IF(MIN(Class_0!M35,Class_1!M35,Class_2!M35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL61" s="4" t="str">
+        <f>IF(MIN(Class_0!N35,Class_1!N35,Class_2!N35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM61" s="4" t="str">
+        <f>IF(MIN(Class_0!O35,Class_1!O35,Class_2!O35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN61" s="4" t="str">
+        <f>IF(MIN(Class_0!P35,Class_1!P35,Class_2!P35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO61" s="4" t="str">
+        <f>IF(MIN(Class_0!Q35,Class_1!Q35,Class_2!Q35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP61" s="4" t="str">
+        <f>IF(MIN(Class_0!R35,Class_1!R35,Class_2!R35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ61" s="4" t="str">
+        <f>IF(MIN(Class_0!S35,Class_1!S35,Class_2!S35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR61" s="4" t="str">
+        <f>IF(MIN(Class_0!T35,Class_1!T35,Class_2!T35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS61" s="4" t="str">
+        <f>IF(MIN(Class_0!U35,Class_1!U35,Class_2!U35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT61" s="4" t="str">
+        <f>IF(MIN(Class_0!V35,Class_1!V35,Class_2!V35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU61" s="4" t="str">
+        <f>IF(MIN(Class_0!W35,Class_1!W35,Class_2!W35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV61" s="4" t="str">
+        <f>IF(MIN(Class_0!X35,Class_1!X35,Class_2!X35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW61" s="4" t="str">
+        <f>IF(MIN(Class_0!Y35,Class_1!Y35,Class_2!Y35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AX61" s="4" t="str">
+        <f>IF(MIN(Class_0!Z35,Class_1!Z35,Class_2!Z35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY61" s="4" t="str">
+        <f>IF(MIN(Class_0!AA35,Class_1!AA35,Class_2!AA35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ61" s="4" t="str">
+        <f>IF(MIN(Class_0!AB35,Class_1!AB35,Class_2!AB35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA61" s="4" t="str">
+        <f>IF(MIN(Class_0!AC35,Class_1!AC35,Class_2!AC35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB61" s="4" t="str">
+        <f>IF(MIN(Class_0!AD35,Class_1!AD35,Class_2!AD35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BC61" s="4" t="str">
+        <f>IF(MIN(Class_0!AE35,Class_1!AE35,Class_2!AE35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BD61" s="4" t="str">
+        <f>IF(MIN(Class_0!AF35,Class_1!AF35,Class_2!AF35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE61" s="4" t="str">
+        <f>IF(MIN(Class_0!AG35,Class_1!AG35,Class_2!AG35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BF61" s="4" t="str">
+        <f>IF(MIN(Class_0!AH35,Class_1!AH35,Class_2!AH35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BG61" s="4" t="str">
+        <f>IF(MIN(Class_0!AI35,Class_1!AI35,Class_2!AI35)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BH61" s="4"/>
+      <c r="BI61" s="4"/>
+      <c r="BJ61" s="4"/>
+      <c r="BK61" s="4"/>
+      <c r="BL61" s="4"/>
+      <c r="BM61" s="4"/>
+      <c r="BN61" s="4"/>
+      <c r="BO61" s="4"/>
+      <c r="BP61" s="4"/>
+      <c r="BQ61" s="4"/>
+      <c r="BR61" s="4"/>
+      <c r="BS61" s="4"/>
+      <c r="BT61" s="4"/>
+      <c r="BU61" s="4"/>
+      <c r="BV61" s="4"/>
+      <c r="BW61" s="4"/>
+      <c r="BX61" s="4"/>
+      <c r="BY61" s="4"/>
     </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B62" t="s">
         <v>58</v>
       </c>
+      <c r="X62" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y62" s="2">
+        <f t="shared" si="7"/>
+        <v>34</v>
+      </c>
+      <c r="Z62" s="4" t="str">
+        <f>IF(MIN(Class_0!B36,Class_1!B36,Class_2!B36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA62" s="4" t="str">
+        <f>IF(MIN(Class_0!C36,Class_1!C36,Class_2!C36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB62" s="4" t="str">
+        <f>IF(MIN(Class_0!D36,Class_1!D36,Class_2!D36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC62" s="4" t="str">
+        <f>IF(MIN(Class_0!E36,Class_1!E36,Class_2!E36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD62" s="4" t="str">
+        <f>IF(MIN(Class_0!F36,Class_1!F36,Class_2!F36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE62" s="4" t="str">
+        <f>IF(MIN(Class_0!G36,Class_1!G36,Class_2!G36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF62" s="4" t="str">
+        <f>IF(MIN(Class_0!H36,Class_1!H36,Class_2!H36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG62" s="4" t="str">
+        <f>IF(MIN(Class_0!I36,Class_1!I36,Class_2!I36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH62" s="4" t="str">
+        <f>IF(MIN(Class_0!J36,Class_1!J36,Class_2!J36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI62" s="4" t="str">
+        <f>IF(MIN(Class_0!K36,Class_1!K36,Class_2!K36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ62" s="4" t="str">
+        <f>IF(MIN(Class_0!L36,Class_1!L36,Class_2!L36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK62" s="4" t="str">
+        <f>IF(MIN(Class_0!M36,Class_1!M36,Class_2!M36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL62" s="4" t="str">
+        <f>IF(MIN(Class_0!N36,Class_1!N36,Class_2!N36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM62" s="4" t="str">
+        <f>IF(MIN(Class_0!O36,Class_1!O36,Class_2!O36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN62" s="4" t="str">
+        <f>IF(MIN(Class_0!P36,Class_1!P36,Class_2!P36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO62" s="4" t="str">
+        <f>IF(MIN(Class_0!Q36,Class_1!Q36,Class_2!Q36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP62" s="4" t="str">
+        <f>IF(MIN(Class_0!R36,Class_1!R36,Class_2!R36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ62" s="4" t="str">
+        <f>IF(MIN(Class_0!S36,Class_1!S36,Class_2!S36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR62" s="4" t="str">
+        <f>IF(MIN(Class_0!T36,Class_1!T36,Class_2!T36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS62" s="4" t="str">
+        <f>IF(MIN(Class_0!U36,Class_1!U36,Class_2!U36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT62" s="4" t="str">
+        <f>IF(MIN(Class_0!V36,Class_1!V36,Class_2!V36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU62" s="4" t="str">
+        <f>IF(MIN(Class_0!W36,Class_1!W36,Class_2!W36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV62" s="4" t="str">
+        <f>IF(MIN(Class_0!X36,Class_1!X36,Class_2!X36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AW62" s="4" t="str">
+        <f>IF(MIN(Class_0!Y36,Class_1!Y36,Class_2!Y36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX62" s="4" t="str">
+        <f>IF(MIN(Class_0!Z36,Class_1!Z36,Class_2!Z36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY62" s="4" t="str">
+        <f>IF(MIN(Class_0!AA36,Class_1!AA36,Class_2!AA36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AZ62" s="4" t="str">
+        <f>IF(MIN(Class_0!AB36,Class_1!AB36,Class_2!AB36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BA62" s="4" t="str">
+        <f>IF(MIN(Class_0!AC36,Class_1!AC36,Class_2!AC36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BB62" s="4" t="str">
+        <f>IF(MIN(Class_0!AD36,Class_1!AD36,Class_2!AD36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BC62" s="4" t="str">
+        <f>IF(MIN(Class_0!AE36,Class_1!AE36,Class_2!AE36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BD62" s="4" t="str">
+        <f>IF(MIN(Class_0!AF36,Class_1!AF36,Class_2!AF36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BE62" s="4" t="str">
+        <f>IF(MIN(Class_0!AG36,Class_1!AG36,Class_2!AG36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BF62" s="4" t="str">
+        <f>IF(MIN(Class_0!AH36,Class_1!AH36,Class_2!AH36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BG62" s="4" t="str">
+        <f>IF(MIN(Class_0!AI36,Class_1!AI36,Class_2!AI36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BH62" s="4" t="str">
+        <f>IF(MIN(Class_0!AJ36,Class_1!AJ36,Class_2!AJ36)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BI62" s="4"/>
+      <c r="BJ62" s="4"/>
+      <c r="BK62" s="4"/>
+      <c r="BL62" s="4"/>
+      <c r="BM62" s="4"/>
+      <c r="BN62" s="4"/>
+      <c r="BO62" s="4"/>
+      <c r="BP62" s="4"/>
+      <c r="BQ62" s="4"/>
+      <c r="BR62" s="4"/>
+      <c r="BS62" s="4"/>
+      <c r="BT62" s="4"/>
+      <c r="BU62" s="4"/>
+      <c r="BV62" s="4"/>
+      <c r="BW62" s="4"/>
+      <c r="BX62" s="4"/>
+      <c r="BY62" s="4"/>
     </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B63" t="s">
         <v>58</v>
       </c>
+      <c r="X63" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y63" s="2">
+        <f t="shared" si="7"/>
+        <v>35</v>
+      </c>
+      <c r="Z63" s="4" t="str">
+        <f>IF(MIN(Class_0!B37,Class_1!B37,Class_2!B37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA63" s="4" t="str">
+        <f>IF(MIN(Class_0!C37,Class_1!C37,Class_2!C37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB63" s="4" t="str">
+        <f>IF(MIN(Class_0!D37,Class_1!D37,Class_2!D37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC63" s="4" t="str">
+        <f>IF(MIN(Class_0!E37,Class_1!E37,Class_2!E37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD63" s="4" t="str">
+        <f>IF(MIN(Class_0!F37,Class_1!F37,Class_2!F37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE63" s="4" t="str">
+        <f>IF(MIN(Class_0!G37,Class_1!G37,Class_2!G37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF63" s="4" t="str">
+        <f>IF(MIN(Class_0!H37,Class_1!H37,Class_2!H37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG63" s="4" t="str">
+        <f>IF(MIN(Class_0!I37,Class_1!I37,Class_2!I37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH63" s="4" t="str">
+        <f>IF(MIN(Class_0!J37,Class_1!J37,Class_2!J37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI63" s="4" t="str">
+        <f>IF(MIN(Class_0!K37,Class_1!K37,Class_2!K37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ63" s="4" t="str">
+        <f>IF(MIN(Class_0!L37,Class_1!L37,Class_2!L37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK63" s="4" t="str">
+        <f>IF(MIN(Class_0!M37,Class_1!M37,Class_2!M37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL63" s="4" t="str">
+        <f>IF(MIN(Class_0!N37,Class_1!N37,Class_2!N37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM63" s="4" t="str">
+        <f>IF(MIN(Class_0!O37,Class_1!O37,Class_2!O37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN63" s="4" t="str">
+        <f>IF(MIN(Class_0!P37,Class_1!P37,Class_2!P37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO63" s="4" t="str">
+        <f>IF(MIN(Class_0!Q37,Class_1!Q37,Class_2!Q37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP63" s="4" t="str">
+        <f>IF(MIN(Class_0!R37,Class_1!R37,Class_2!R37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ63" s="4" t="str">
+        <f>IF(MIN(Class_0!S37,Class_1!S37,Class_2!S37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR63" s="4" t="str">
+        <f>IF(MIN(Class_0!T37,Class_1!T37,Class_2!T37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS63" s="4" t="str">
+        <f>IF(MIN(Class_0!U37,Class_1!U37,Class_2!U37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT63" s="4" t="str">
+        <f>IF(MIN(Class_0!V37,Class_1!V37,Class_2!V37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU63" s="4" t="str">
+        <f>IF(MIN(Class_0!W37,Class_1!W37,Class_2!W37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV63" s="4" t="str">
+        <f>IF(MIN(Class_0!X37,Class_1!X37,Class_2!X37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW63" s="4" t="str">
+        <f>IF(MIN(Class_0!Y37,Class_1!Y37,Class_2!Y37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX63" s="4" t="str">
+        <f>IF(MIN(Class_0!Z37,Class_1!Z37,Class_2!Z37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY63" s="4" t="str">
+        <f>IF(MIN(Class_0!AA37,Class_1!AA37,Class_2!AA37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AZ63" s="4" t="str">
+        <f>IF(MIN(Class_0!AB37,Class_1!AB37,Class_2!AB37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BA63" s="4" t="str">
+        <f>IF(MIN(Class_0!AC37,Class_1!AC37,Class_2!AC37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB63" s="4" t="str">
+        <f>IF(MIN(Class_0!AD37,Class_1!AD37,Class_2!AD37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BC63" s="4" t="str">
+        <f>IF(MIN(Class_0!AE37,Class_1!AE37,Class_2!AE37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BD63" s="4" t="str">
+        <f>IF(MIN(Class_0!AF37,Class_1!AF37,Class_2!AF37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE63" s="4" t="str">
+        <f>IF(MIN(Class_0!AG37,Class_1!AG37,Class_2!AG37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BF63" s="4" t="str">
+        <f>IF(MIN(Class_0!AH37,Class_1!AH37,Class_2!AH37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BG63" s="4" t="str">
+        <f>IF(MIN(Class_0!AI37,Class_1!AI37,Class_2!AI37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BH63" s="4" t="str">
+        <f>IF(MIN(Class_0!AJ37,Class_1!AJ37,Class_2!AJ37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BI63" s="4" t="str">
+        <f>IF(MIN(Class_0!AK37,Class_1!AK37,Class_2!AK37)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BJ63" s="4"/>
+      <c r="BK63" s="4"/>
+      <c r="BL63" s="4"/>
+      <c r="BM63" s="4"/>
+      <c r="BN63" s="4"/>
+      <c r="BO63" s="4"/>
+      <c r="BP63" s="4"/>
+      <c r="BQ63" s="4"/>
+      <c r="BR63" s="4"/>
+      <c r="BS63" s="4"/>
+      <c r="BT63" s="4"/>
+      <c r="BU63" s="4"/>
+      <c r="BV63" s="4"/>
+      <c r="BW63" s="4"/>
+      <c r="BX63" s="4"/>
+      <c r="BY63" s="4"/>
     </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:77" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
         <v>58</v>
+      </c>
+      <c r="X64" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y64" s="2">
+        <f t="shared" si="7"/>
+        <v>36</v>
+      </c>
+      <c r="Z64" s="4" t="str">
+        <f>IF(MIN(Class_0!B38,Class_1!B38,Class_2!B38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA64" s="4" t="str">
+        <f>IF(MIN(Class_0!C38,Class_1!C38,Class_2!C38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB64" s="4" t="str">
+        <f>IF(MIN(Class_0!D38,Class_1!D38,Class_2!D38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC64" s="4" t="str">
+        <f>IF(MIN(Class_0!E38,Class_1!E38,Class_2!E38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD64" s="4" t="str">
+        <f>IF(MIN(Class_0!F38,Class_1!F38,Class_2!F38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE64" s="4" t="str">
+        <f>IF(MIN(Class_0!G38,Class_1!G38,Class_2!G38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF64" s="4" t="str">
+        <f>IF(MIN(Class_0!H38,Class_1!H38,Class_2!H38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG64" s="4" t="str">
+        <f>IF(MIN(Class_0!I38,Class_1!I38,Class_2!I38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH64" s="4" t="str">
+        <f>IF(MIN(Class_0!J38,Class_1!J38,Class_2!J38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI64" s="4" t="str">
+        <f>IF(MIN(Class_0!K38,Class_1!K38,Class_2!K38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ64" s="4" t="str">
+        <f>IF(MIN(Class_0!L38,Class_1!L38,Class_2!L38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK64" s="4" t="str">
+        <f>IF(MIN(Class_0!M38,Class_1!M38,Class_2!M38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL64" s="4" t="str">
+        <f>IF(MIN(Class_0!N38,Class_1!N38,Class_2!N38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM64" s="4" t="str">
+        <f>IF(MIN(Class_0!O38,Class_1!O38,Class_2!O38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN64" s="4" t="str">
+        <f>IF(MIN(Class_0!P38,Class_1!P38,Class_2!P38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO64" s="4" t="str">
+        <f>IF(MIN(Class_0!Q38,Class_1!Q38,Class_2!Q38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP64" s="4" t="str">
+        <f>IF(MIN(Class_0!R38,Class_1!R38,Class_2!R38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ64" s="4" t="str">
+        <f>IF(MIN(Class_0!S38,Class_1!S38,Class_2!S38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR64" s="4" t="str">
+        <f>IF(MIN(Class_0!T38,Class_1!T38,Class_2!T38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS64" s="4" t="str">
+        <f>IF(MIN(Class_0!U38,Class_1!U38,Class_2!U38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT64" s="4" t="str">
+        <f>IF(MIN(Class_0!V38,Class_1!V38,Class_2!V38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU64" s="4" t="str">
+        <f>IF(MIN(Class_0!W38,Class_1!W38,Class_2!W38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV64" s="4" t="str">
+        <f>IF(MIN(Class_0!X38,Class_1!X38,Class_2!X38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AW64" s="4" t="str">
+        <f>IF(MIN(Class_0!Y38,Class_1!Y38,Class_2!Y38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AX64" s="4" t="str">
+        <f>IF(MIN(Class_0!Z38,Class_1!Z38,Class_2!Z38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY64" s="4" t="str">
+        <f>IF(MIN(Class_0!AA38,Class_1!AA38,Class_2!AA38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ64" s="4" t="str">
+        <f>IF(MIN(Class_0!AB38,Class_1!AB38,Class_2!AB38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA64" s="4" t="str">
+        <f>IF(MIN(Class_0!AC38,Class_1!AC38,Class_2!AC38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB64" s="4" t="str">
+        <f>IF(MIN(Class_0!AD38,Class_1!AD38,Class_2!AD38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BC64" s="4" t="str">
+        <f>IF(MIN(Class_0!AE38,Class_1!AE38,Class_2!AE38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BD64" s="4" t="str">
+        <f>IF(MIN(Class_0!AF38,Class_1!AF38,Class_2!AF38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE64" s="4" t="str">
+        <f>IF(MIN(Class_0!AG38,Class_1!AG38,Class_2!AG38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BF64" s="4" t="str">
+        <f>IF(MIN(Class_0!AH38,Class_1!AH38,Class_2!AH38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BG64" s="4" t="str">
+        <f>IF(MIN(Class_0!AI38,Class_1!AI38,Class_2!AI38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BH64" s="4" t="str">
+        <f>IF(MIN(Class_0!AJ38,Class_1!AJ38,Class_2!AJ38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BI64" s="4" t="str">
+        <f>IF(MIN(Class_0!AK38,Class_1!AK38,Class_2!AK38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BJ64" s="4" t="str">
+        <f>IF(MIN(Class_0!AL38,Class_1!AL38,Class_2!AL38)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BK64" s="4"/>
+      <c r="BL64" s="4"/>
+      <c r="BM64" s="4"/>
+      <c r="BN64" s="4"/>
+      <c r="BO64" s="4"/>
+      <c r="BP64" s="4"/>
+      <c r="BQ64" s="4"/>
+      <c r="BR64" s="4"/>
+      <c r="BS64" s="4"/>
+      <c r="BT64" s="4"/>
+      <c r="BU64" s="4"/>
+      <c r="BV64" s="4"/>
+      <c r="BW64" s="4"/>
+      <c r="BX64" s="4"/>
+      <c r="BY64" s="4"/>
+    </row>
+    <row r="65" spans="24:77" x14ac:dyDescent="0.35">
+      <c r="X65" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y65" s="2">
+        <f t="shared" si="7"/>
+        <v>37</v>
+      </c>
+      <c r="Z65" s="4" t="str">
+        <f>IF(MIN(Class_0!B39,Class_1!B39,Class_2!B39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA65" s="4" t="str">
+        <f>IF(MIN(Class_0!C39,Class_1!C39,Class_2!C39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB65" s="4" t="str">
+        <f>IF(MIN(Class_0!D39,Class_1!D39,Class_2!D39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC65" s="4" t="str">
+        <f>IF(MIN(Class_0!E39,Class_1!E39,Class_2!E39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD65" s="4" t="str">
+        <f>IF(MIN(Class_0!F39,Class_1!F39,Class_2!F39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE65" s="4" t="str">
+        <f>IF(MIN(Class_0!G39,Class_1!G39,Class_2!G39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF65" s="4" t="str">
+        <f>IF(MIN(Class_0!H39,Class_1!H39,Class_2!H39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG65" s="4" t="str">
+        <f>IF(MIN(Class_0!I39,Class_1!I39,Class_2!I39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH65" s="4" t="str">
+        <f>IF(MIN(Class_0!J39,Class_1!J39,Class_2!J39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI65" s="4" t="str">
+        <f>IF(MIN(Class_0!K39,Class_1!K39,Class_2!K39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ65" s="4" t="str">
+        <f>IF(MIN(Class_0!L39,Class_1!L39,Class_2!L39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK65" s="4" t="str">
+        <f>IF(MIN(Class_0!M39,Class_1!M39,Class_2!M39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL65" s="4" t="str">
+        <f>IF(MIN(Class_0!N39,Class_1!N39,Class_2!N39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM65" s="4" t="str">
+        <f>IF(MIN(Class_0!O39,Class_1!O39,Class_2!O39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN65" s="4" t="str">
+        <f>IF(MIN(Class_0!P39,Class_1!P39,Class_2!P39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO65" s="4" t="str">
+        <f>IF(MIN(Class_0!Q39,Class_1!Q39,Class_2!Q39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP65" s="4" t="str">
+        <f>IF(MIN(Class_0!R39,Class_1!R39,Class_2!R39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ65" s="4" t="str">
+        <f>IF(MIN(Class_0!S39,Class_1!S39,Class_2!S39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR65" s="4" t="str">
+        <f>IF(MIN(Class_0!T39,Class_1!T39,Class_2!T39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS65" s="4" t="str">
+        <f>IF(MIN(Class_0!U39,Class_1!U39,Class_2!U39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT65" s="4" t="str">
+        <f>IF(MIN(Class_0!V39,Class_1!V39,Class_2!V39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU65" s="4" t="str">
+        <f>IF(MIN(Class_0!W39,Class_1!W39,Class_2!W39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV65" s="4" t="str">
+        <f>IF(MIN(Class_0!X39,Class_1!X39,Class_2!X39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW65" s="4" t="str">
+        <f>IF(MIN(Class_0!Y39,Class_1!Y39,Class_2!Y39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX65" s="4" t="str">
+        <f>IF(MIN(Class_0!Z39,Class_1!Z39,Class_2!Z39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY65" s="4" t="str">
+        <f>IF(MIN(Class_0!AA39,Class_1!AA39,Class_2!AA39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ65" s="4" t="str">
+        <f>IF(MIN(Class_0!AB39,Class_1!AB39,Class_2!AB39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA65" s="4" t="str">
+        <f>IF(MIN(Class_0!AC39,Class_1!AC39,Class_2!AC39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB65" s="4" t="str">
+        <f>IF(MIN(Class_0!AD39,Class_1!AD39,Class_2!AD39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BC65" s="4" t="str">
+        <f>IF(MIN(Class_0!AE39,Class_1!AE39,Class_2!AE39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BD65" s="4" t="str">
+        <f>IF(MIN(Class_0!AF39,Class_1!AF39,Class_2!AF39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE65" s="4" t="str">
+        <f>IF(MIN(Class_0!AG39,Class_1!AG39,Class_2!AG39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BF65" s="4" t="str">
+        <f>IF(MIN(Class_0!AH39,Class_1!AH39,Class_2!AH39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BG65" s="4" t="str">
+        <f>IF(MIN(Class_0!AI39,Class_1!AI39,Class_2!AI39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BH65" s="4" t="str">
+        <f>IF(MIN(Class_0!AJ39,Class_1!AJ39,Class_2!AJ39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BI65" s="4" t="str">
+        <f>IF(MIN(Class_0!AK39,Class_1!AK39,Class_2!AK39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BJ65" s="4" t="str">
+        <f>IF(MIN(Class_0!AL39,Class_1!AL39,Class_2!AL39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BK65" s="4" t="str">
+        <f>IF(MIN(Class_0!AM39,Class_1!AM39,Class_2!AM39)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BL65" s="4"/>
+      <c r="BM65" s="4"/>
+      <c r="BN65" s="4"/>
+      <c r="BO65" s="4"/>
+      <c r="BP65" s="4"/>
+      <c r="BQ65" s="4"/>
+      <c r="BR65" s="4"/>
+      <c r="BS65" s="4"/>
+      <c r="BT65" s="4"/>
+      <c r="BU65" s="4"/>
+      <c r="BV65" s="4"/>
+      <c r="BW65" s="4"/>
+      <c r="BX65" s="4"/>
+      <c r="BY65" s="4"/>
+    </row>
+    <row r="66" spans="24:77" x14ac:dyDescent="0.35">
+      <c r="X66" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y66" s="2">
+        <f t="shared" si="7"/>
+        <v>38</v>
+      </c>
+      <c r="Z66" s="4" t="str">
+        <f>IF(MIN(Class_0!B40,Class_1!B40,Class_2!B40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA66" s="4" t="str">
+        <f>IF(MIN(Class_0!C40,Class_1!C40,Class_2!C40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB66" s="4" t="str">
+        <f>IF(MIN(Class_0!D40,Class_1!D40,Class_2!D40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC66" s="4" t="str">
+        <f>IF(MIN(Class_0!E40,Class_1!E40,Class_2!E40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD66" s="4" t="str">
+        <f>IF(MIN(Class_0!F40,Class_1!F40,Class_2!F40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE66" s="4" t="str">
+        <f>IF(MIN(Class_0!G40,Class_1!G40,Class_2!G40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF66" s="4" t="str">
+        <f>IF(MIN(Class_0!H40,Class_1!H40,Class_2!H40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG66" s="4" t="str">
+        <f>IF(MIN(Class_0!I40,Class_1!I40,Class_2!I40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH66" s="4" t="str">
+        <f>IF(MIN(Class_0!J40,Class_1!J40,Class_2!J40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI66" s="4" t="str">
+        <f>IF(MIN(Class_0!K40,Class_1!K40,Class_2!K40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ66" s="4" t="str">
+        <f>IF(MIN(Class_0!L40,Class_1!L40,Class_2!L40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK66" s="4" t="str">
+        <f>IF(MIN(Class_0!M40,Class_1!M40,Class_2!M40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL66" s="4" t="str">
+        <f>IF(MIN(Class_0!N40,Class_1!N40,Class_2!N40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM66" s="4" t="str">
+        <f>IF(MIN(Class_0!O40,Class_1!O40,Class_2!O40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN66" s="4" t="str">
+        <f>IF(MIN(Class_0!P40,Class_1!P40,Class_2!P40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO66" s="4" t="str">
+        <f>IF(MIN(Class_0!Q40,Class_1!Q40,Class_2!Q40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP66" s="4" t="str">
+        <f>IF(MIN(Class_0!R40,Class_1!R40,Class_2!R40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ66" s="4" t="str">
+        <f>IF(MIN(Class_0!S40,Class_1!S40,Class_2!S40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR66" s="4" t="str">
+        <f>IF(MIN(Class_0!T40,Class_1!T40,Class_2!T40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS66" s="4" t="str">
+        <f>IF(MIN(Class_0!U40,Class_1!U40,Class_2!U40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT66" s="4" t="str">
+        <f>IF(MIN(Class_0!V40,Class_1!V40,Class_2!V40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU66" s="4" t="str">
+        <f>IF(MIN(Class_0!W40,Class_1!W40,Class_2!W40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV66" s="4" t="str">
+        <f>IF(MIN(Class_0!X40,Class_1!X40,Class_2!X40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW66" s="4" t="str">
+        <f>IF(MIN(Class_0!Y40,Class_1!Y40,Class_2!Y40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX66" s="4" t="str">
+        <f>IF(MIN(Class_0!Z40,Class_1!Z40,Class_2!Z40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY66" s="4" t="str">
+        <f>IF(MIN(Class_0!AA40,Class_1!AA40,Class_2!AA40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AZ66" s="4" t="str">
+        <f>IF(MIN(Class_0!AB40,Class_1!AB40,Class_2!AB40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA66" s="4" t="str">
+        <f>IF(MIN(Class_0!AC40,Class_1!AC40,Class_2!AC40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB66" s="4" t="str">
+        <f>IF(MIN(Class_0!AD40,Class_1!AD40,Class_2!AD40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BC66" s="4" t="str">
+        <f>IF(MIN(Class_0!AE40,Class_1!AE40,Class_2!AE40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BD66" s="4" t="str">
+        <f>IF(MIN(Class_0!AF40,Class_1!AF40,Class_2!AF40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BE66" s="4" t="str">
+        <f>IF(MIN(Class_0!AG40,Class_1!AG40,Class_2!AG40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BF66" s="4" t="str">
+        <f>IF(MIN(Class_0!AH40,Class_1!AH40,Class_2!AH40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BG66" s="4" t="str">
+        <f>IF(MIN(Class_0!AI40,Class_1!AI40,Class_2!AI40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BH66" s="4" t="str">
+        <f>IF(MIN(Class_0!AJ40,Class_1!AJ40,Class_2!AJ40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BI66" s="4" t="str">
+        <f>IF(MIN(Class_0!AK40,Class_1!AK40,Class_2!AK40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BJ66" s="4" t="str">
+        <f>IF(MIN(Class_0!AL40,Class_1!AL40,Class_2!AL40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BK66" s="4" t="str">
+        <f>IF(MIN(Class_0!AM40,Class_1!AM40,Class_2!AM40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BL66" s="4" t="str">
+        <f>IF(MIN(Class_0!AN40,Class_1!AN40,Class_2!AN40)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BM66" s="4"/>
+      <c r="BN66" s="4"/>
+      <c r="BO66" s="4"/>
+      <c r="BP66" s="4"/>
+      <c r="BQ66" s="4"/>
+      <c r="BR66" s="4"/>
+      <c r="BS66" s="4"/>
+      <c r="BT66" s="4"/>
+      <c r="BU66" s="4"/>
+      <c r="BV66" s="4"/>
+      <c r="BW66" s="4"/>
+      <c r="BX66" s="4"/>
+      <c r="BY66" s="4"/>
+    </row>
+    <row r="67" spans="24:77" x14ac:dyDescent="0.35">
+      <c r="X67" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y67" s="2">
+        <f t="shared" si="7"/>
+        <v>39</v>
+      </c>
+      <c r="Z67" s="4" t="str">
+        <f>IF(MIN(Class_0!B41,Class_1!B41,Class_2!B41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA67" s="4" t="str">
+        <f>IF(MIN(Class_0!C41,Class_1!C41,Class_2!C41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB67" s="4" t="str">
+        <f>IF(MIN(Class_0!D41,Class_1!D41,Class_2!D41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC67" s="4" t="str">
+        <f>IF(MIN(Class_0!E41,Class_1!E41,Class_2!E41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD67" s="4" t="str">
+        <f>IF(MIN(Class_0!F41,Class_1!F41,Class_2!F41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE67" s="4" t="str">
+        <f>IF(MIN(Class_0!G41,Class_1!G41,Class_2!G41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF67" s="4" t="str">
+        <f>IF(MIN(Class_0!H41,Class_1!H41,Class_2!H41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG67" s="4" t="str">
+        <f>IF(MIN(Class_0!I41,Class_1!I41,Class_2!I41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH67" s="4" t="str">
+        <f>IF(MIN(Class_0!J41,Class_1!J41,Class_2!J41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI67" s="4" t="str">
+        <f>IF(MIN(Class_0!K41,Class_1!K41,Class_2!K41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ67" s="4" t="str">
+        <f>IF(MIN(Class_0!L41,Class_1!L41,Class_2!L41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK67" s="4" t="str">
+        <f>IF(MIN(Class_0!M41,Class_1!M41,Class_2!M41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL67" s="4" t="str">
+        <f>IF(MIN(Class_0!N41,Class_1!N41,Class_2!N41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM67" s="4" t="str">
+        <f>IF(MIN(Class_0!O41,Class_1!O41,Class_2!O41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN67" s="4" t="str">
+        <f>IF(MIN(Class_0!P41,Class_1!P41,Class_2!P41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO67" s="4" t="str">
+        <f>IF(MIN(Class_0!Q41,Class_1!Q41,Class_2!Q41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP67" s="4" t="str">
+        <f>IF(MIN(Class_0!R41,Class_1!R41,Class_2!R41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ67" s="4" t="str">
+        <f>IF(MIN(Class_0!S41,Class_1!S41,Class_2!S41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR67" s="4" t="str">
+        <f>IF(MIN(Class_0!T41,Class_1!T41,Class_2!T41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS67" s="4" t="str">
+        <f>IF(MIN(Class_0!U41,Class_1!U41,Class_2!U41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT67" s="4" t="str">
+        <f>IF(MIN(Class_0!V41,Class_1!V41,Class_2!V41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU67" s="4" t="str">
+        <f>IF(MIN(Class_0!W41,Class_1!W41,Class_2!W41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AV67" s="4" t="str">
+        <f>IF(MIN(Class_0!X41,Class_1!X41,Class_2!X41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW67" s="4" t="str">
+        <f>IF(MIN(Class_0!Y41,Class_1!Y41,Class_2!Y41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX67" s="4" t="str">
+        <f>IF(MIN(Class_0!Z41,Class_1!Z41,Class_2!Z41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY67" s="4" t="str">
+        <f>IF(MIN(Class_0!AA41,Class_1!AA41,Class_2!AA41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AZ67" s="4" t="str">
+        <f>IF(MIN(Class_0!AB41,Class_1!AB41,Class_2!AB41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA67" s="4" t="str">
+        <f>IF(MIN(Class_0!AC41,Class_1!AC41,Class_2!AC41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BB67" s="4" t="str">
+        <f>IF(MIN(Class_0!AD41,Class_1!AD41,Class_2!AD41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BC67" s="4" t="str">
+        <f>IF(MIN(Class_0!AE41,Class_1!AE41,Class_2!AE41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BD67" s="4" t="str">
+        <f>IF(MIN(Class_0!AF41,Class_1!AF41,Class_2!AF41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BE67" s="4" t="str">
+        <f>IF(MIN(Class_0!AG41,Class_1!AG41,Class_2!AG41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BF67" s="4" t="str">
+        <f>IF(MIN(Class_0!AH41,Class_1!AH41,Class_2!AH41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BG67" s="4" t="str">
+        <f>IF(MIN(Class_0!AI41,Class_1!AI41,Class_2!AI41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BH67" s="4" t="str">
+        <f>IF(MIN(Class_0!AJ41,Class_1!AJ41,Class_2!AJ41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BI67" s="4" t="str">
+        <f>IF(MIN(Class_0!AK41,Class_1!AK41,Class_2!AK41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BJ67" s="4" t="str">
+        <f>IF(MIN(Class_0!AL41,Class_1!AL41,Class_2!AL41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BK67" s="4" t="str">
+        <f>IF(MIN(Class_0!AM41,Class_1!AM41,Class_2!AM41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BL67" s="4" t="str">
+        <f>IF(MIN(Class_0!AN41,Class_1!AN41,Class_2!AN41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BM67" s="4" t="str">
+        <f>IF(MIN(Class_0!AO41,Class_1!AO41,Class_2!AO41)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BN67" s="4"/>
+      <c r="BO67" s="4"/>
+      <c r="BP67" s="4"/>
+      <c r="BQ67" s="4"/>
+      <c r="BR67" s="4"/>
+      <c r="BS67" s="4"/>
+      <c r="BT67" s="4"/>
+      <c r="BU67" s="4"/>
+      <c r="BV67" s="4"/>
+      <c r="BW67" s="4"/>
+      <c r="BX67" s="4"/>
+      <c r="BY67" s="4"/>
+    </row>
+    <row r="68" spans="24:77" x14ac:dyDescent="0.35">
+      <c r="X68" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y68" s="2">
+        <f t="shared" si="7"/>
+        <v>40</v>
+      </c>
+      <c r="Z68" s="4" t="str">
+        <f>IF(MIN(Class_0!B42,Class_1!B42,Class_2!B42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA68" s="4" t="str">
+        <f>IF(MIN(Class_0!C42,Class_1!C42,Class_2!C42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB68" s="4" t="str">
+        <f>IF(MIN(Class_0!D42,Class_1!D42,Class_2!D42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC68" s="4" t="str">
+        <f>IF(MIN(Class_0!E42,Class_1!E42,Class_2!E42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD68" s="4" t="str">
+        <f>IF(MIN(Class_0!F42,Class_1!F42,Class_2!F42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE68" s="4" t="str">
+        <f>IF(MIN(Class_0!G42,Class_1!G42,Class_2!G42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF68" s="4" t="str">
+        <f>IF(MIN(Class_0!H42,Class_1!H42,Class_2!H42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG68" s="4" t="str">
+        <f>IF(MIN(Class_0!I42,Class_1!I42,Class_2!I42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH68" s="4" t="str">
+        <f>IF(MIN(Class_0!J42,Class_1!J42,Class_2!J42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI68" s="4" t="str">
+        <f>IF(MIN(Class_0!K42,Class_1!K42,Class_2!K42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ68" s="4" t="str">
+        <f>IF(MIN(Class_0!L42,Class_1!L42,Class_2!L42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK68" s="4" t="str">
+        <f>IF(MIN(Class_0!M42,Class_1!M42,Class_2!M42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL68" s="4" t="str">
+        <f>IF(MIN(Class_0!N42,Class_1!N42,Class_2!N42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM68" s="4" t="str">
+        <f>IF(MIN(Class_0!O42,Class_1!O42,Class_2!O42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN68" s="4" t="str">
+        <f>IF(MIN(Class_0!P42,Class_1!P42,Class_2!P42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO68" s="4" t="str">
+        <f>IF(MIN(Class_0!Q42,Class_1!Q42,Class_2!Q42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP68" s="4" t="str">
+        <f>IF(MIN(Class_0!R42,Class_1!R42,Class_2!R42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ68" s="4" t="str">
+        <f>IF(MIN(Class_0!S42,Class_1!S42,Class_2!S42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR68" s="4" t="str">
+        <f>IF(MIN(Class_0!T42,Class_1!T42,Class_2!T42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS68" s="4" t="str">
+        <f>IF(MIN(Class_0!U42,Class_1!U42,Class_2!U42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT68" s="4" t="str">
+        <f>IF(MIN(Class_0!V42,Class_1!V42,Class_2!V42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU68" s="4" t="str">
+        <f>IF(MIN(Class_0!W42,Class_1!W42,Class_2!W42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV68" s="4" t="str">
+        <f>IF(MIN(Class_0!X42,Class_1!X42,Class_2!X42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW68" s="4" t="str">
+        <f>IF(MIN(Class_0!Y42,Class_1!Y42,Class_2!Y42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX68" s="4" t="str">
+        <f>IF(MIN(Class_0!Z42,Class_1!Z42,Class_2!Z42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY68" s="4" t="str">
+        <f>IF(MIN(Class_0!AA42,Class_1!AA42,Class_2!AA42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ68" s="4" t="str">
+        <f>IF(MIN(Class_0!AB42,Class_1!AB42,Class_2!AB42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA68" s="4" t="str">
+        <f>IF(MIN(Class_0!AC42,Class_1!AC42,Class_2!AC42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB68" s="4" t="str">
+        <f>IF(MIN(Class_0!AD42,Class_1!AD42,Class_2!AD42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BC68" s="4" t="str">
+        <f>IF(MIN(Class_0!AE42,Class_1!AE42,Class_2!AE42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BD68" s="4" t="str">
+        <f>IF(MIN(Class_0!AF42,Class_1!AF42,Class_2!AF42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE68" s="4" t="str">
+        <f>IF(MIN(Class_0!AG42,Class_1!AG42,Class_2!AG42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BF68" s="4" t="str">
+        <f>IF(MIN(Class_0!AH42,Class_1!AH42,Class_2!AH42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BG68" s="4" t="str">
+        <f>IF(MIN(Class_0!AI42,Class_1!AI42,Class_2!AI42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BH68" s="4" t="str">
+        <f>IF(MIN(Class_0!AJ42,Class_1!AJ42,Class_2!AJ42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BI68" s="4" t="str">
+        <f>IF(MIN(Class_0!AK42,Class_1!AK42,Class_2!AK42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BJ68" s="4" t="str">
+        <f>IF(MIN(Class_0!AL42,Class_1!AL42,Class_2!AL42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BK68" s="4" t="str">
+        <f>IF(MIN(Class_0!AM42,Class_1!AM42,Class_2!AM42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BL68" s="4" t="str">
+        <f>IF(MIN(Class_0!AN42,Class_1!AN42,Class_2!AN42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BM68" s="4" t="str">
+        <f>IF(MIN(Class_0!AO42,Class_1!AO42,Class_2!AO42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BN68" s="4" t="str">
+        <f>IF(MIN(Class_0!AP42,Class_1!AP42,Class_2!AP42)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BO68" s="4"/>
+      <c r="BP68" s="4"/>
+      <c r="BQ68" s="4"/>
+      <c r="BR68" s="4"/>
+      <c r="BS68" s="4"/>
+      <c r="BT68" s="4"/>
+      <c r="BU68" s="4"/>
+      <c r="BV68" s="4"/>
+      <c r="BW68" s="4"/>
+      <c r="BX68" s="4"/>
+      <c r="BY68" s="4"/>
+    </row>
+    <row r="69" spans="24:77" x14ac:dyDescent="0.35">
+      <c r="X69" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y69" s="2">
+        <f t="shared" si="7"/>
+        <v>41</v>
+      </c>
+      <c r="Z69" s="4" t="str">
+        <f>IF(MIN(Class_0!B43,Class_1!B43,Class_2!B43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA69" s="4" t="str">
+        <f>IF(MIN(Class_0!C43,Class_1!C43,Class_2!C43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB69" s="4" t="str">
+        <f>IF(MIN(Class_0!D43,Class_1!D43,Class_2!D43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC69" s="4" t="str">
+        <f>IF(MIN(Class_0!E43,Class_1!E43,Class_2!E43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD69" s="4" t="str">
+        <f>IF(MIN(Class_0!F43,Class_1!F43,Class_2!F43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE69" s="4" t="str">
+        <f>IF(MIN(Class_0!G43,Class_1!G43,Class_2!G43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF69" s="4" t="str">
+        <f>IF(MIN(Class_0!H43,Class_1!H43,Class_2!H43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG69" s="4" t="str">
+        <f>IF(MIN(Class_0!I43,Class_1!I43,Class_2!I43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH69" s="4" t="str">
+        <f>IF(MIN(Class_0!J43,Class_1!J43,Class_2!J43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI69" s="4" t="str">
+        <f>IF(MIN(Class_0!K43,Class_1!K43,Class_2!K43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ69" s="4" t="str">
+        <f>IF(MIN(Class_0!L43,Class_1!L43,Class_2!L43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK69" s="4" t="str">
+        <f>IF(MIN(Class_0!M43,Class_1!M43,Class_2!M43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL69" s="4" t="str">
+        <f>IF(MIN(Class_0!N43,Class_1!N43,Class_2!N43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM69" s="4" t="str">
+        <f>IF(MIN(Class_0!O43,Class_1!O43,Class_2!O43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN69" s="4" t="str">
+        <f>IF(MIN(Class_0!P43,Class_1!P43,Class_2!P43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO69" s="4" t="str">
+        <f>IF(MIN(Class_0!Q43,Class_1!Q43,Class_2!Q43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP69" s="4" t="str">
+        <f>IF(MIN(Class_0!R43,Class_1!R43,Class_2!R43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ69" s="4" t="str">
+        <f>IF(MIN(Class_0!S43,Class_1!S43,Class_2!S43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR69" s="4" t="str">
+        <f>IF(MIN(Class_0!T43,Class_1!T43,Class_2!T43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS69" s="4" t="str">
+        <f>IF(MIN(Class_0!U43,Class_1!U43,Class_2!U43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT69" s="4" t="str">
+        <f>IF(MIN(Class_0!V43,Class_1!V43,Class_2!V43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU69" s="4" t="str">
+        <f>IF(MIN(Class_0!W43,Class_1!W43,Class_2!W43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV69" s="4" t="str">
+        <f>IF(MIN(Class_0!X43,Class_1!X43,Class_2!X43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW69" s="4" t="str">
+        <f>IF(MIN(Class_0!Y43,Class_1!Y43,Class_2!Y43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX69" s="4" t="str">
+        <f>IF(MIN(Class_0!Z43,Class_1!Z43,Class_2!Z43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY69" s="4" t="str">
+        <f>IF(MIN(Class_0!AA43,Class_1!AA43,Class_2!AA43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ69" s="4" t="str">
+        <f>IF(MIN(Class_0!AB43,Class_1!AB43,Class_2!AB43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA69" s="4" t="str">
+        <f>IF(MIN(Class_0!AC43,Class_1!AC43,Class_2!AC43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB69" s="4" t="str">
+        <f>IF(MIN(Class_0!AD43,Class_1!AD43,Class_2!AD43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BC69" s="4" t="str">
+        <f>IF(MIN(Class_0!AE43,Class_1!AE43,Class_2!AE43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BD69" s="4" t="str">
+        <f>IF(MIN(Class_0!AF43,Class_1!AF43,Class_2!AF43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE69" s="4" t="str">
+        <f>IF(MIN(Class_0!AG43,Class_1!AG43,Class_2!AG43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BF69" s="4" t="str">
+        <f>IF(MIN(Class_0!AH43,Class_1!AH43,Class_2!AH43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BG69" s="4" t="str">
+        <f>IF(MIN(Class_0!AI43,Class_1!AI43,Class_2!AI43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BH69" s="4" t="str">
+        <f>IF(MIN(Class_0!AJ43,Class_1!AJ43,Class_2!AJ43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BI69" s="4" t="str">
+        <f>IF(MIN(Class_0!AK43,Class_1!AK43,Class_2!AK43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BJ69" s="4" t="str">
+        <f>IF(MIN(Class_0!AL43,Class_1!AL43,Class_2!AL43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BK69" s="4" t="str">
+        <f>IF(MIN(Class_0!AM43,Class_1!AM43,Class_2!AM43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BL69" s="4" t="str">
+        <f>IF(MIN(Class_0!AN43,Class_1!AN43,Class_2!AN43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BM69" s="4" t="str">
+        <f>IF(MIN(Class_0!AO43,Class_1!AO43,Class_2!AO43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BN69" s="4" t="str">
+        <f>IF(MIN(Class_0!AP43,Class_1!AP43,Class_2!AP43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BO69" s="4" t="str">
+        <f>IF(MIN(Class_0!AQ43,Class_1!AQ43,Class_2!AQ43)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BP69" s="4"/>
+      <c r="BQ69" s="4"/>
+      <c r="BR69" s="4"/>
+      <c r="BS69" s="4"/>
+      <c r="BT69" s="4"/>
+      <c r="BU69" s="4"/>
+      <c r="BV69" s="4"/>
+      <c r="BW69" s="4"/>
+      <c r="BX69" s="4"/>
+      <c r="BY69" s="4"/>
+    </row>
+    <row r="70" spans="24:77" x14ac:dyDescent="0.35">
+      <c r="X70" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y70" s="2">
+        <f t="shared" si="7"/>
+        <v>42</v>
+      </c>
+      <c r="Z70" s="4" t="str">
+        <f>IF(MIN(Class_0!B44,Class_1!B44,Class_2!B44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA70" s="4" t="str">
+        <f>IF(MIN(Class_0!C44,Class_1!C44,Class_2!C44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB70" s="4" t="str">
+        <f>IF(MIN(Class_0!D44,Class_1!D44,Class_2!D44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC70" s="4" t="str">
+        <f>IF(MIN(Class_0!E44,Class_1!E44,Class_2!E44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD70" s="4" t="str">
+        <f>IF(MIN(Class_0!F44,Class_1!F44,Class_2!F44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE70" s="4" t="str">
+        <f>IF(MIN(Class_0!G44,Class_1!G44,Class_2!G44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF70" s="4" t="str">
+        <f>IF(MIN(Class_0!H44,Class_1!H44,Class_2!H44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG70" s="4" t="str">
+        <f>IF(MIN(Class_0!I44,Class_1!I44,Class_2!I44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH70" s="4" t="str">
+        <f>IF(MIN(Class_0!J44,Class_1!J44,Class_2!J44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI70" s="4" t="str">
+        <f>IF(MIN(Class_0!K44,Class_1!K44,Class_2!K44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ70" s="4" t="str">
+        <f>IF(MIN(Class_0!L44,Class_1!L44,Class_2!L44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK70" s="4" t="str">
+        <f>IF(MIN(Class_0!M44,Class_1!M44,Class_2!M44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL70" s="4" t="str">
+        <f>IF(MIN(Class_0!N44,Class_1!N44,Class_2!N44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM70" s="4" t="str">
+        <f>IF(MIN(Class_0!O44,Class_1!O44,Class_2!O44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN70" s="4" t="str">
+        <f>IF(MIN(Class_0!P44,Class_1!P44,Class_2!P44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO70" s="4" t="str">
+        <f>IF(MIN(Class_0!Q44,Class_1!Q44,Class_2!Q44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP70" s="4" t="str">
+        <f>IF(MIN(Class_0!R44,Class_1!R44,Class_2!R44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ70" s="4" t="str">
+        <f>IF(MIN(Class_0!S44,Class_1!S44,Class_2!S44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR70" s="4" t="str">
+        <f>IF(MIN(Class_0!T44,Class_1!T44,Class_2!T44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS70" s="4" t="str">
+        <f>IF(MIN(Class_0!U44,Class_1!U44,Class_2!U44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT70" s="4" t="str">
+        <f>IF(MIN(Class_0!V44,Class_1!V44,Class_2!V44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU70" s="4" t="str">
+        <f>IF(MIN(Class_0!W44,Class_1!W44,Class_2!W44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV70" s="4" t="str">
+        <f>IF(MIN(Class_0!X44,Class_1!X44,Class_2!X44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW70" s="4" t="str">
+        <f>IF(MIN(Class_0!Y44,Class_1!Y44,Class_2!Y44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX70" s="4" t="str">
+        <f>IF(MIN(Class_0!Z44,Class_1!Z44,Class_2!Z44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY70" s="4" t="str">
+        <f>IF(MIN(Class_0!AA44,Class_1!AA44,Class_2!AA44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ70" s="4" t="str">
+        <f>IF(MIN(Class_0!AB44,Class_1!AB44,Class_2!AB44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA70" s="4" t="str">
+        <f>IF(MIN(Class_0!AC44,Class_1!AC44,Class_2!AC44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB70" s="4" t="str">
+        <f>IF(MIN(Class_0!AD44,Class_1!AD44,Class_2!AD44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BC70" s="4" t="str">
+        <f>IF(MIN(Class_0!AE44,Class_1!AE44,Class_2!AE44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BD70" s="4" t="str">
+        <f>IF(MIN(Class_0!AF44,Class_1!AF44,Class_2!AF44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE70" s="4" t="str">
+        <f>IF(MIN(Class_0!AG44,Class_1!AG44,Class_2!AG44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BF70" s="4" t="str">
+        <f>IF(MIN(Class_0!AH44,Class_1!AH44,Class_2!AH44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BG70" s="4" t="str">
+        <f>IF(MIN(Class_0!AI44,Class_1!AI44,Class_2!AI44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BH70" s="4" t="str">
+        <f>IF(MIN(Class_0!AJ44,Class_1!AJ44,Class_2!AJ44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BI70" s="4" t="str">
+        <f>IF(MIN(Class_0!AK44,Class_1!AK44,Class_2!AK44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BJ70" s="4" t="str">
+        <f>IF(MIN(Class_0!AL44,Class_1!AL44,Class_2!AL44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BK70" s="4" t="str">
+        <f>IF(MIN(Class_0!AM44,Class_1!AM44,Class_2!AM44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BL70" s="4" t="str">
+        <f>IF(MIN(Class_0!AN44,Class_1!AN44,Class_2!AN44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BM70" s="4" t="str">
+        <f>IF(MIN(Class_0!AO44,Class_1!AO44,Class_2!AO44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BN70" s="4" t="str">
+        <f>IF(MIN(Class_0!AP44,Class_1!AP44,Class_2!AP44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BO70" s="4" t="str">
+        <f>IF(MIN(Class_0!AQ44,Class_1!AQ44,Class_2!AQ44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BP70" s="4" t="str">
+        <f>IF(MIN(Class_0!AR44,Class_1!AR44,Class_2!AR44)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BQ70" s="4"/>
+      <c r="BR70" s="4"/>
+      <c r="BS70" s="4"/>
+      <c r="BT70" s="4"/>
+      <c r="BU70" s="4"/>
+      <c r="BV70" s="4"/>
+      <c r="BW70" s="4"/>
+      <c r="BX70" s="4"/>
+      <c r="BY70" s="4"/>
+    </row>
+    <row r="71" spans="24:77" x14ac:dyDescent="0.35">
+      <c r="X71" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y71" s="2">
+        <f t="shared" si="7"/>
+        <v>43</v>
+      </c>
+      <c r="Z71" s="4" t="str">
+        <f>IF(MIN(Class_0!B45,Class_1!B45,Class_2!B45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA71" s="4" t="str">
+        <f>IF(MIN(Class_0!C45,Class_1!C45,Class_2!C45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB71" s="4" t="str">
+        <f>IF(MIN(Class_0!D45,Class_1!D45,Class_2!D45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC71" s="4" t="str">
+        <f>IF(MIN(Class_0!E45,Class_1!E45,Class_2!E45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD71" s="4" t="str">
+        <f>IF(MIN(Class_0!F45,Class_1!F45,Class_2!F45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE71" s="4" t="str">
+        <f>IF(MIN(Class_0!G45,Class_1!G45,Class_2!G45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF71" s="4" t="str">
+        <f>IF(MIN(Class_0!H45,Class_1!H45,Class_2!H45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG71" s="4" t="str">
+        <f>IF(MIN(Class_0!I45,Class_1!I45,Class_2!I45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH71" s="4" t="str">
+        <f>IF(MIN(Class_0!J45,Class_1!J45,Class_2!J45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI71" s="4" t="str">
+        <f>IF(MIN(Class_0!K45,Class_1!K45,Class_2!K45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ71" s="4" t="str">
+        <f>IF(MIN(Class_0!L45,Class_1!L45,Class_2!L45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK71" s="4" t="str">
+        <f>IF(MIN(Class_0!M45,Class_1!M45,Class_2!M45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL71" s="4" t="str">
+        <f>IF(MIN(Class_0!N45,Class_1!N45,Class_2!N45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM71" s="4" t="str">
+        <f>IF(MIN(Class_0!O45,Class_1!O45,Class_2!O45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN71" s="4" t="str">
+        <f>IF(MIN(Class_0!P45,Class_1!P45,Class_2!P45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO71" s="4" t="str">
+        <f>IF(MIN(Class_0!Q45,Class_1!Q45,Class_2!Q45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP71" s="4" t="str">
+        <f>IF(MIN(Class_0!R45,Class_1!R45,Class_2!R45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ71" s="4" t="str">
+        <f>IF(MIN(Class_0!S45,Class_1!S45,Class_2!S45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR71" s="4" t="str">
+        <f>IF(MIN(Class_0!T45,Class_1!T45,Class_2!T45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS71" s="4" t="str">
+        <f>IF(MIN(Class_0!U45,Class_1!U45,Class_2!U45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT71" s="4" t="str">
+        <f>IF(MIN(Class_0!V45,Class_1!V45,Class_2!V45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU71" s="4" t="str">
+        <f>IF(MIN(Class_0!W45,Class_1!W45,Class_2!W45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV71" s="4" t="str">
+        <f>IF(MIN(Class_0!X45,Class_1!X45,Class_2!X45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW71" s="4" t="str">
+        <f>IF(MIN(Class_0!Y45,Class_1!Y45,Class_2!Y45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX71" s="4" t="str">
+        <f>IF(MIN(Class_0!Z45,Class_1!Z45,Class_2!Z45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY71" s="4" t="str">
+        <f>IF(MIN(Class_0!AA45,Class_1!AA45,Class_2!AA45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AZ71" s="4" t="str">
+        <f>IF(MIN(Class_0!AB45,Class_1!AB45,Class_2!AB45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA71" s="4" t="str">
+        <f>IF(MIN(Class_0!AC45,Class_1!AC45,Class_2!AC45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB71" s="4" t="str">
+        <f>IF(MIN(Class_0!AD45,Class_1!AD45,Class_2!AD45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BC71" s="4" t="str">
+        <f>IF(MIN(Class_0!AE45,Class_1!AE45,Class_2!AE45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BD71" s="4" t="str">
+        <f>IF(MIN(Class_0!AF45,Class_1!AF45,Class_2!AF45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE71" s="4" t="str">
+        <f>IF(MIN(Class_0!AG45,Class_1!AG45,Class_2!AG45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BF71" s="4" t="str">
+        <f>IF(MIN(Class_0!AH45,Class_1!AH45,Class_2!AH45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BG71" s="4" t="str">
+        <f>IF(MIN(Class_0!AI45,Class_1!AI45,Class_2!AI45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BH71" s="4" t="str">
+        <f>IF(MIN(Class_0!AJ45,Class_1!AJ45,Class_2!AJ45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BI71" s="4" t="str">
+        <f>IF(MIN(Class_0!AK45,Class_1!AK45,Class_2!AK45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BJ71" s="4" t="str">
+        <f>IF(MIN(Class_0!AL45,Class_1!AL45,Class_2!AL45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BK71" s="4" t="str">
+        <f>IF(MIN(Class_0!AM45,Class_1!AM45,Class_2!AM45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BL71" s="4" t="str">
+        <f>IF(MIN(Class_0!AN45,Class_1!AN45,Class_2!AN45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BM71" s="4" t="str">
+        <f>IF(MIN(Class_0!AO45,Class_1!AO45,Class_2!AO45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BN71" s="4" t="str">
+        <f>IF(MIN(Class_0!AP45,Class_1!AP45,Class_2!AP45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BO71" s="4" t="str">
+        <f>IF(MIN(Class_0!AQ45,Class_1!AQ45,Class_2!AQ45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BP71" s="4" t="str">
+        <f>IF(MIN(Class_0!AR45,Class_1!AR45,Class_2!AR45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BQ71" s="4" t="str">
+        <f>IF(MIN(Class_0!AS45,Class_1!AS45,Class_2!AS45)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BR71" s="4"/>
+      <c r="BS71" s="4"/>
+      <c r="BT71" s="4"/>
+      <c r="BU71" s="4"/>
+      <c r="BV71" s="4"/>
+      <c r="BW71" s="4"/>
+      <c r="BX71" s="4"/>
+      <c r="BY71" s="4"/>
+    </row>
+    <row r="72" spans="24:77" x14ac:dyDescent="0.35">
+      <c r="X72" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y72" s="2">
+        <f t="shared" si="7"/>
+        <v>44</v>
+      </c>
+      <c r="Z72" s="4" t="str">
+        <f>IF(MIN(Class_0!B46,Class_1!B46,Class_2!B46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA72" s="4" t="str">
+        <f>IF(MIN(Class_0!C46,Class_1!C46,Class_2!C46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB72" s="4" t="str">
+        <f>IF(MIN(Class_0!D46,Class_1!D46,Class_2!D46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC72" s="4" t="str">
+        <f>IF(MIN(Class_0!E46,Class_1!E46,Class_2!E46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD72" s="4" t="str">
+        <f>IF(MIN(Class_0!F46,Class_1!F46,Class_2!F46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE72" s="4" t="str">
+        <f>IF(MIN(Class_0!G46,Class_1!G46,Class_2!G46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF72" s="4" t="str">
+        <f>IF(MIN(Class_0!H46,Class_1!H46,Class_2!H46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG72" s="4" t="str">
+        <f>IF(MIN(Class_0!I46,Class_1!I46,Class_2!I46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH72" s="4" t="str">
+        <f>IF(MIN(Class_0!J46,Class_1!J46,Class_2!J46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI72" s="4" t="str">
+        <f>IF(MIN(Class_0!K46,Class_1!K46,Class_2!K46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ72" s="4" t="str">
+        <f>IF(MIN(Class_0!L46,Class_1!L46,Class_2!L46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK72" s="4" t="str">
+        <f>IF(MIN(Class_0!M46,Class_1!M46,Class_2!M46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL72" s="4" t="str">
+        <f>IF(MIN(Class_0!N46,Class_1!N46,Class_2!N46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM72" s="4" t="str">
+        <f>IF(MIN(Class_0!O46,Class_1!O46,Class_2!O46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN72" s="4" t="str">
+        <f>IF(MIN(Class_0!P46,Class_1!P46,Class_2!P46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO72" s="4" t="str">
+        <f>IF(MIN(Class_0!Q46,Class_1!Q46,Class_2!Q46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP72" s="4" t="str">
+        <f>IF(MIN(Class_0!R46,Class_1!R46,Class_2!R46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ72" s="4" t="str">
+        <f>IF(MIN(Class_0!S46,Class_1!S46,Class_2!S46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR72" s="4" t="str">
+        <f>IF(MIN(Class_0!T46,Class_1!T46,Class_2!T46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS72" s="4" t="str">
+        <f>IF(MIN(Class_0!U46,Class_1!U46,Class_2!U46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT72" s="4" t="str">
+        <f>IF(MIN(Class_0!V46,Class_1!V46,Class_2!V46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU72" s="4" t="str">
+        <f>IF(MIN(Class_0!W46,Class_1!W46,Class_2!W46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV72" s="4" t="str">
+        <f>IF(MIN(Class_0!X46,Class_1!X46,Class_2!X46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW72" s="4" t="str">
+        <f>IF(MIN(Class_0!Y46,Class_1!Y46,Class_2!Y46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX72" s="4" t="str">
+        <f>IF(MIN(Class_0!Z46,Class_1!Z46,Class_2!Z46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY72" s="4" t="str">
+        <f>IF(MIN(Class_0!AA46,Class_1!AA46,Class_2!AA46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AZ72" s="4" t="str">
+        <f>IF(MIN(Class_0!AB46,Class_1!AB46,Class_2!AB46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BA72" s="4" t="str">
+        <f>IF(MIN(Class_0!AC46,Class_1!AC46,Class_2!AC46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB72" s="4" t="str">
+        <f>IF(MIN(Class_0!AD46,Class_1!AD46,Class_2!AD46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BC72" s="4" t="str">
+        <f>IF(MIN(Class_0!AE46,Class_1!AE46,Class_2!AE46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BD72" s="4" t="str">
+        <f>IF(MIN(Class_0!AF46,Class_1!AF46,Class_2!AF46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE72" s="4" t="str">
+        <f>IF(MIN(Class_0!AG46,Class_1!AG46,Class_2!AG46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BF72" s="4" t="str">
+        <f>IF(MIN(Class_0!AH46,Class_1!AH46,Class_2!AH46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BG72" s="4" t="str">
+        <f>IF(MIN(Class_0!AI46,Class_1!AI46,Class_2!AI46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BH72" s="4" t="str">
+        <f>IF(MIN(Class_0!AJ46,Class_1!AJ46,Class_2!AJ46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BI72" s="4" t="str">
+        <f>IF(MIN(Class_0!AK46,Class_1!AK46,Class_2!AK46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BJ72" s="4" t="str">
+        <f>IF(MIN(Class_0!AL46,Class_1!AL46,Class_2!AL46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BK72" s="4" t="str">
+        <f>IF(MIN(Class_0!AM46,Class_1!AM46,Class_2!AM46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BL72" s="4" t="str">
+        <f>IF(MIN(Class_0!AN46,Class_1!AN46,Class_2!AN46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BM72" s="4" t="str">
+        <f>IF(MIN(Class_0!AO46,Class_1!AO46,Class_2!AO46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BN72" s="4" t="str">
+        <f>IF(MIN(Class_0!AP46,Class_1!AP46,Class_2!AP46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BO72" s="4" t="str">
+        <f>IF(MIN(Class_0!AQ46,Class_1!AQ46,Class_2!AQ46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BP72" s="4" t="str">
+        <f>IF(MIN(Class_0!AR46,Class_1!AR46,Class_2!AR46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BQ72" s="4" t="str">
+        <f>IF(MIN(Class_0!AS46,Class_1!AS46,Class_2!AS46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BR72" s="4" t="str">
+        <f>IF(MIN(Class_0!AT46,Class_1!AT46,Class_2!AT46)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BS72" s="4"/>
+      <c r="BT72" s="4"/>
+      <c r="BU72" s="4"/>
+      <c r="BV72" s="4"/>
+      <c r="BW72" s="4"/>
+      <c r="BX72" s="4"/>
+      <c r="BY72" s="4"/>
+    </row>
+    <row r="73" spans="24:77" x14ac:dyDescent="0.35">
+      <c r="X73" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y73" s="2">
+        <f t="shared" si="7"/>
+        <v>45</v>
+      </c>
+      <c r="Z73" s="4" t="str">
+        <f>IF(MIN(Class_0!B47,Class_1!B47,Class_2!B47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AA73" s="4" t="str">
+        <f>IF(MIN(Class_0!C47,Class_1!C47,Class_2!C47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB73" s="4" t="str">
+        <f>IF(MIN(Class_0!D47,Class_1!D47,Class_2!D47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC73" s="4" t="str">
+        <f>IF(MIN(Class_0!E47,Class_1!E47,Class_2!E47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD73" s="4" t="str">
+        <f>IF(MIN(Class_0!F47,Class_1!F47,Class_2!F47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE73" s="4" t="str">
+        <f>IF(MIN(Class_0!G47,Class_1!G47,Class_2!G47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF73" s="4" t="str">
+        <f>IF(MIN(Class_0!H47,Class_1!H47,Class_2!H47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG73" s="4" t="str">
+        <f>IF(MIN(Class_0!I47,Class_1!I47,Class_2!I47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH73" s="4" t="str">
+        <f>IF(MIN(Class_0!J47,Class_1!J47,Class_2!J47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI73" s="4" t="str">
+        <f>IF(MIN(Class_0!K47,Class_1!K47,Class_2!K47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ73" s="4" t="str">
+        <f>IF(MIN(Class_0!L47,Class_1!L47,Class_2!L47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK73" s="4" t="str">
+        <f>IF(MIN(Class_0!M47,Class_1!M47,Class_2!M47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL73" s="4" t="str">
+        <f>IF(MIN(Class_0!N47,Class_1!N47,Class_2!N47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM73" s="4" t="str">
+        <f>IF(MIN(Class_0!O47,Class_1!O47,Class_2!O47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN73" s="4" t="str">
+        <f>IF(MIN(Class_0!P47,Class_1!P47,Class_2!P47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO73" s="4" t="str">
+        <f>IF(MIN(Class_0!Q47,Class_1!Q47,Class_2!Q47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP73" s="4" t="str">
+        <f>IF(MIN(Class_0!R47,Class_1!R47,Class_2!R47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ73" s="4" t="str">
+        <f>IF(MIN(Class_0!S47,Class_1!S47,Class_2!S47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR73" s="4" t="str">
+        <f>IF(MIN(Class_0!T47,Class_1!T47,Class_2!T47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS73" s="4" t="str">
+        <f>IF(MIN(Class_0!U47,Class_1!U47,Class_2!U47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT73" s="4" t="str">
+        <f>IF(MIN(Class_0!V47,Class_1!V47,Class_2!V47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU73" s="4" t="str">
+        <f>IF(MIN(Class_0!W47,Class_1!W47,Class_2!W47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV73" s="4" t="str">
+        <f>IF(MIN(Class_0!X47,Class_1!X47,Class_2!X47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW73" s="4" t="str">
+        <f>IF(MIN(Class_0!Y47,Class_1!Y47,Class_2!Y47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX73" s="4" t="str">
+        <f>IF(MIN(Class_0!Z47,Class_1!Z47,Class_2!Z47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY73" s="4" t="str">
+        <f>IF(MIN(Class_0!AA47,Class_1!AA47,Class_2!AA47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ73" s="4" t="str">
+        <f>IF(MIN(Class_0!AB47,Class_1!AB47,Class_2!AB47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA73" s="4" t="str">
+        <f>IF(MIN(Class_0!AC47,Class_1!AC47,Class_2!AC47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB73" s="4" t="str">
+        <f>IF(MIN(Class_0!AD47,Class_1!AD47,Class_2!AD47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BC73" s="4" t="str">
+        <f>IF(MIN(Class_0!AE47,Class_1!AE47,Class_2!AE47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BD73" s="4" t="str">
+        <f>IF(MIN(Class_0!AF47,Class_1!AF47,Class_2!AF47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE73" s="4" t="str">
+        <f>IF(MIN(Class_0!AG47,Class_1!AG47,Class_2!AG47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BF73" s="4" t="str">
+        <f>IF(MIN(Class_0!AH47,Class_1!AH47,Class_2!AH47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BG73" s="4" t="str">
+        <f>IF(MIN(Class_0!AI47,Class_1!AI47,Class_2!AI47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BH73" s="4" t="str">
+        <f>IF(MIN(Class_0!AJ47,Class_1!AJ47,Class_2!AJ47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BI73" s="4" t="str">
+        <f>IF(MIN(Class_0!AK47,Class_1!AK47,Class_2!AK47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BJ73" s="4" t="str">
+        <f>IF(MIN(Class_0!AL47,Class_1!AL47,Class_2!AL47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BK73" s="4" t="str">
+        <f>IF(MIN(Class_0!AM47,Class_1!AM47,Class_2!AM47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BL73" s="4" t="str">
+        <f>IF(MIN(Class_0!AN47,Class_1!AN47,Class_2!AN47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BM73" s="4" t="str">
+        <f>IF(MIN(Class_0!AO47,Class_1!AO47,Class_2!AO47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BN73" s="4" t="str">
+        <f>IF(MIN(Class_0!AP47,Class_1!AP47,Class_2!AP47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BO73" s="4" t="str">
+        <f>IF(MIN(Class_0!AQ47,Class_1!AQ47,Class_2!AQ47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BP73" s="4" t="str">
+        <f>IF(MIN(Class_0!AR47,Class_1!AR47,Class_2!AR47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BQ73" s="4" t="str">
+        <f>IF(MIN(Class_0!AS47,Class_1!AS47,Class_2!AS47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BR73" s="4" t="str">
+        <f>IF(MIN(Class_0!AT47,Class_1!AT47,Class_2!AT47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BS73" s="4" t="str">
+        <f>IF(MIN(Class_0!AU47,Class_1!AU47,Class_2!AU47)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BT73" s="4"/>
+      <c r="BU73" s="4"/>
+      <c r="BV73" s="4"/>
+      <c r="BW73" s="4"/>
+      <c r="BX73" s="4"/>
+      <c r="BY73" s="4"/>
+    </row>
+    <row r="74" spans="24:77" x14ac:dyDescent="0.35">
+      <c r="X74" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y74" s="2">
+        <f t="shared" si="7"/>
+        <v>46</v>
+      </c>
+      <c r="Z74" s="4" t="str">
+        <f>IF(MIN(Class_0!B48,Class_1!B48,Class_2!B48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA74" s="4" t="str">
+        <f>IF(MIN(Class_0!C48,Class_1!C48,Class_2!C48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB74" s="4" t="str">
+        <f>IF(MIN(Class_0!D48,Class_1!D48,Class_2!D48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC74" s="4" t="str">
+        <f>IF(MIN(Class_0!E48,Class_1!E48,Class_2!E48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD74" s="4" t="str">
+        <f>IF(MIN(Class_0!F48,Class_1!F48,Class_2!F48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE74" s="4" t="str">
+        <f>IF(MIN(Class_0!G48,Class_1!G48,Class_2!G48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF74" s="4" t="str">
+        <f>IF(MIN(Class_0!H48,Class_1!H48,Class_2!H48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG74" s="4" t="str">
+        <f>IF(MIN(Class_0!I48,Class_1!I48,Class_2!I48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH74" s="4" t="str">
+        <f>IF(MIN(Class_0!J48,Class_1!J48,Class_2!J48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI74" s="4" t="str">
+        <f>IF(MIN(Class_0!K48,Class_1!K48,Class_2!K48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ74" s="4" t="str">
+        <f>IF(MIN(Class_0!L48,Class_1!L48,Class_2!L48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK74" s="4" t="str">
+        <f>IF(MIN(Class_0!M48,Class_1!M48,Class_2!M48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL74" s="4" t="str">
+        <f>IF(MIN(Class_0!N48,Class_1!N48,Class_2!N48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM74" s="4" t="str">
+        <f>IF(MIN(Class_0!O48,Class_1!O48,Class_2!O48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN74" s="4" t="str">
+        <f>IF(MIN(Class_0!P48,Class_1!P48,Class_2!P48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO74" s="4" t="str">
+        <f>IF(MIN(Class_0!Q48,Class_1!Q48,Class_2!Q48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP74" s="4" t="str">
+        <f>IF(MIN(Class_0!R48,Class_1!R48,Class_2!R48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ74" s="4" t="str">
+        <f>IF(MIN(Class_0!S48,Class_1!S48,Class_2!S48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR74" s="4" t="str">
+        <f>IF(MIN(Class_0!T48,Class_1!T48,Class_2!T48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS74" s="4" t="str">
+        <f>IF(MIN(Class_0!U48,Class_1!U48,Class_2!U48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT74" s="4" t="str">
+        <f>IF(MIN(Class_0!V48,Class_1!V48,Class_2!V48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU74" s="4" t="str">
+        <f>IF(MIN(Class_0!W48,Class_1!W48,Class_2!W48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AV74" s="4" t="str">
+        <f>IF(MIN(Class_0!X48,Class_1!X48,Class_2!X48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW74" s="4" t="str">
+        <f>IF(MIN(Class_0!Y48,Class_1!Y48,Class_2!Y48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX74" s="4" t="str">
+        <f>IF(MIN(Class_0!Z48,Class_1!Z48,Class_2!Z48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY74" s="4" t="str">
+        <f>IF(MIN(Class_0!AA48,Class_1!AA48,Class_2!AA48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AZ74" s="4" t="str">
+        <f>IF(MIN(Class_0!AB48,Class_1!AB48,Class_2!AB48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA74" s="4" t="str">
+        <f>IF(MIN(Class_0!AC48,Class_1!AC48,Class_2!AC48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB74" s="4" t="str">
+        <f>IF(MIN(Class_0!AD48,Class_1!AD48,Class_2!AD48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BC74" s="4" t="str">
+        <f>IF(MIN(Class_0!AE48,Class_1!AE48,Class_2!AE48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BD74" s="4" t="str">
+        <f>IF(MIN(Class_0!AF48,Class_1!AF48,Class_2!AF48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE74" s="4" t="str">
+        <f>IF(MIN(Class_0!AG48,Class_1!AG48,Class_2!AG48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BF74" s="4" t="str">
+        <f>IF(MIN(Class_0!AH48,Class_1!AH48,Class_2!AH48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BG74" s="4" t="str">
+        <f>IF(MIN(Class_0!AI48,Class_1!AI48,Class_2!AI48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BH74" s="4" t="str">
+        <f>IF(MIN(Class_0!AJ48,Class_1!AJ48,Class_2!AJ48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BI74" s="4" t="str">
+        <f>IF(MIN(Class_0!AK48,Class_1!AK48,Class_2!AK48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BJ74" s="4" t="str">
+        <f>IF(MIN(Class_0!AL48,Class_1!AL48,Class_2!AL48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BK74" s="4" t="str">
+        <f>IF(MIN(Class_0!AM48,Class_1!AM48,Class_2!AM48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BL74" s="4" t="str">
+        <f>IF(MIN(Class_0!AN48,Class_1!AN48,Class_2!AN48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BM74" s="4" t="str">
+        <f>IF(MIN(Class_0!AO48,Class_1!AO48,Class_2!AO48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BN74" s="4" t="str">
+        <f>IF(MIN(Class_0!AP48,Class_1!AP48,Class_2!AP48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BO74" s="4" t="str">
+        <f>IF(MIN(Class_0!AQ48,Class_1!AQ48,Class_2!AQ48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BP74" s="4" t="str">
+        <f>IF(MIN(Class_0!AR48,Class_1!AR48,Class_2!AR48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BQ74" s="4" t="str">
+        <f>IF(MIN(Class_0!AS48,Class_1!AS48,Class_2!AS48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BR74" s="4" t="str">
+        <f>IF(MIN(Class_0!AT48,Class_1!AT48,Class_2!AT48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BS74" s="4" t="str">
+        <f>IF(MIN(Class_0!AU48,Class_1!AU48,Class_2!AU48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BT74" s="4" t="str">
+        <f>IF(MIN(Class_0!AV48,Class_1!AV48,Class_2!AV48)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BU74" s="4"/>
+      <c r="BV74" s="4"/>
+      <c r="BW74" s="4"/>
+      <c r="BX74" s="4"/>
+      <c r="BY74" s="4"/>
+    </row>
+    <row r="75" spans="24:77" x14ac:dyDescent="0.35">
+      <c r="X75" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y75" s="2">
+        <f t="shared" si="7"/>
+        <v>47</v>
+      </c>
+      <c r="Z75" s="4" t="str">
+        <f>IF(MIN(Class_0!B49,Class_1!B49,Class_2!B49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA75" s="4" t="str">
+        <f>IF(MIN(Class_0!C49,Class_1!C49,Class_2!C49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB75" s="4" t="str">
+        <f>IF(MIN(Class_0!D49,Class_1!D49,Class_2!D49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC75" s="4" t="str">
+        <f>IF(MIN(Class_0!E49,Class_1!E49,Class_2!E49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD75" s="4" t="str">
+        <f>IF(MIN(Class_0!F49,Class_1!F49,Class_2!F49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AE75" s="4" t="str">
+        <f>IF(MIN(Class_0!G49,Class_1!G49,Class_2!G49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AF75" s="4" t="str">
+        <f>IF(MIN(Class_0!H49,Class_1!H49,Class_2!H49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AG75" s="4" t="str">
+        <f>IF(MIN(Class_0!I49,Class_1!I49,Class_2!I49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH75" s="4" t="str">
+        <f>IF(MIN(Class_0!J49,Class_1!J49,Class_2!J49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI75" s="4" t="str">
+        <f>IF(MIN(Class_0!K49,Class_1!K49,Class_2!K49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ75" s="4" t="str">
+        <f>IF(MIN(Class_0!L49,Class_1!L49,Class_2!L49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK75" s="4" t="str">
+        <f>IF(MIN(Class_0!M49,Class_1!M49,Class_2!M49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL75" s="4" t="str">
+        <f>IF(MIN(Class_0!N49,Class_1!N49,Class_2!N49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM75" s="4" t="str">
+        <f>IF(MIN(Class_0!O49,Class_1!O49,Class_2!O49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN75" s="4" t="str">
+        <f>IF(MIN(Class_0!P49,Class_1!P49,Class_2!P49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO75" s="4" t="str">
+        <f>IF(MIN(Class_0!Q49,Class_1!Q49,Class_2!Q49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP75" s="4" t="str">
+        <f>IF(MIN(Class_0!R49,Class_1!R49,Class_2!R49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ75" s="4" t="str">
+        <f>IF(MIN(Class_0!S49,Class_1!S49,Class_2!S49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR75" s="4" t="str">
+        <f>IF(MIN(Class_0!T49,Class_1!T49,Class_2!T49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS75" s="4" t="str">
+        <f>IF(MIN(Class_0!U49,Class_1!U49,Class_2!U49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT75" s="4" t="str">
+        <f>IF(MIN(Class_0!V49,Class_1!V49,Class_2!V49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU75" s="4" t="str">
+        <f>IF(MIN(Class_0!W49,Class_1!W49,Class_2!W49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV75" s="4" t="str">
+        <f>IF(MIN(Class_0!X49,Class_1!X49,Class_2!X49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW75" s="4" t="str">
+        <f>IF(MIN(Class_0!Y49,Class_1!Y49,Class_2!Y49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX75" s="4" t="str">
+        <f>IF(MIN(Class_0!Z49,Class_1!Z49,Class_2!Z49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY75" s="4" t="str">
+        <f>IF(MIN(Class_0!AA49,Class_1!AA49,Class_2!AA49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AZ75" s="4" t="str">
+        <f>IF(MIN(Class_0!AB49,Class_1!AB49,Class_2!AB49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA75" s="4" t="str">
+        <f>IF(MIN(Class_0!AC49,Class_1!AC49,Class_2!AC49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB75" s="4" t="str">
+        <f>IF(MIN(Class_0!AD49,Class_1!AD49,Class_2!AD49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BC75" s="4" t="str">
+        <f>IF(MIN(Class_0!AE49,Class_1!AE49,Class_2!AE49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BD75" s="4" t="str">
+        <f>IF(MIN(Class_0!AF49,Class_1!AF49,Class_2!AF49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE75" s="4" t="str">
+        <f>IF(MIN(Class_0!AG49,Class_1!AG49,Class_2!AG49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BF75" s="4" t="str">
+        <f>IF(MIN(Class_0!AH49,Class_1!AH49,Class_2!AH49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BG75" s="4" t="str">
+        <f>IF(MIN(Class_0!AI49,Class_1!AI49,Class_2!AI49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BH75" s="4" t="str">
+        <f>IF(MIN(Class_0!AJ49,Class_1!AJ49,Class_2!AJ49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BI75" s="4" t="str">
+        <f>IF(MIN(Class_0!AK49,Class_1!AK49,Class_2!AK49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BJ75" s="4" t="str">
+        <f>IF(MIN(Class_0!AL49,Class_1!AL49,Class_2!AL49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BK75" s="4" t="str">
+        <f>IF(MIN(Class_0!AM49,Class_1!AM49,Class_2!AM49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BL75" s="4" t="str">
+        <f>IF(MIN(Class_0!AN49,Class_1!AN49,Class_2!AN49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BM75" s="4" t="str">
+        <f>IF(MIN(Class_0!AO49,Class_1!AO49,Class_2!AO49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BN75" s="4" t="str">
+        <f>IF(MIN(Class_0!AP49,Class_1!AP49,Class_2!AP49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BO75" s="4" t="str">
+        <f>IF(MIN(Class_0!AQ49,Class_1!AQ49,Class_2!AQ49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BP75" s="4" t="str">
+        <f>IF(MIN(Class_0!AR49,Class_1!AR49,Class_2!AR49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BQ75" s="4" t="str">
+        <f>IF(MIN(Class_0!AS49,Class_1!AS49,Class_2!AS49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BR75" s="4" t="str">
+        <f>IF(MIN(Class_0!AT49,Class_1!AT49,Class_2!AT49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BS75" s="4" t="str">
+        <f>IF(MIN(Class_0!AU49,Class_1!AU49,Class_2!AU49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BT75" s="4" t="str">
+        <f>IF(MIN(Class_0!AV49,Class_1!AV49,Class_2!AV49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BU75" s="4" t="str">
+        <f>IF(MIN(Class_0!AW49,Class_1!AW49,Class_2!AW49)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BV75" s="4"/>
+      <c r="BW75" s="4"/>
+      <c r="BX75" s="4"/>
+      <c r="BY75" s="4"/>
+    </row>
+    <row r="76" spans="24:77" x14ac:dyDescent="0.35">
+      <c r="X76" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y76" s="2">
+        <f t="shared" si="7"/>
+        <v>48</v>
+      </c>
+      <c r="Z76" s="4" t="str">
+        <f>IF(MIN(Class_0!B50,Class_1!B50,Class_2!B50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA76" s="4" t="str">
+        <f>IF(MIN(Class_0!C50,Class_1!C50,Class_2!C50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB76" s="4" t="str">
+        <f>IF(MIN(Class_0!D50,Class_1!D50,Class_2!D50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC76" s="4" t="str">
+        <f>IF(MIN(Class_0!E50,Class_1!E50,Class_2!E50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD76" s="4" t="str">
+        <f>IF(MIN(Class_0!F50,Class_1!F50,Class_2!F50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE76" s="4" t="str">
+        <f>IF(MIN(Class_0!G50,Class_1!G50,Class_2!G50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF76" s="4" t="str">
+        <f>IF(MIN(Class_0!H50,Class_1!H50,Class_2!H50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG76" s="4" t="str">
+        <f>IF(MIN(Class_0!I50,Class_1!I50,Class_2!I50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AH76" s="4" t="str">
+        <f>IF(MIN(Class_0!J50,Class_1!J50,Class_2!J50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI76" s="4" t="str">
+        <f>IF(MIN(Class_0!K50,Class_1!K50,Class_2!K50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ76" s="4" t="str">
+        <f>IF(MIN(Class_0!L50,Class_1!L50,Class_2!L50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK76" s="4" t="str">
+        <f>IF(MIN(Class_0!M50,Class_1!M50,Class_2!M50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL76" s="4" t="str">
+        <f>IF(MIN(Class_0!N50,Class_1!N50,Class_2!N50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM76" s="4" t="str">
+        <f>IF(MIN(Class_0!O50,Class_1!O50,Class_2!O50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN76" s="4" t="str">
+        <f>IF(MIN(Class_0!P50,Class_1!P50,Class_2!P50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO76" s="4" t="str">
+        <f>IF(MIN(Class_0!Q50,Class_1!Q50,Class_2!Q50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AP76" s="4" t="str">
+        <f>IF(MIN(Class_0!R50,Class_1!R50,Class_2!R50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ76" s="4" t="str">
+        <f>IF(MIN(Class_0!S50,Class_1!S50,Class_2!S50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR76" s="4" t="str">
+        <f>IF(MIN(Class_0!T50,Class_1!T50,Class_2!T50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS76" s="4" t="str">
+        <f>IF(MIN(Class_0!U50,Class_1!U50,Class_2!U50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT76" s="4" t="str">
+        <f>IF(MIN(Class_0!V50,Class_1!V50,Class_2!V50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU76" s="4" t="str">
+        <f>IF(MIN(Class_0!W50,Class_1!W50,Class_2!W50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AV76" s="4" t="str">
+        <f>IF(MIN(Class_0!X50,Class_1!X50,Class_2!X50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW76" s="4" t="str">
+        <f>IF(MIN(Class_0!Y50,Class_1!Y50,Class_2!Y50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX76" s="4" t="str">
+        <f>IF(MIN(Class_0!Z50,Class_1!Z50,Class_2!Z50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY76" s="4" t="str">
+        <f>IF(MIN(Class_0!AA50,Class_1!AA50,Class_2!AA50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AZ76" s="4" t="str">
+        <f>IF(MIN(Class_0!AB50,Class_1!AB50,Class_2!AB50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA76" s="4" t="str">
+        <f>IF(MIN(Class_0!AC50,Class_1!AC50,Class_2!AC50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB76" s="4" t="str">
+        <f>IF(MIN(Class_0!AD50,Class_1!AD50,Class_2!AD50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BC76" s="4" t="str">
+        <f>IF(MIN(Class_0!AE50,Class_1!AE50,Class_2!AE50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BD76" s="4" t="str">
+        <f>IF(MIN(Class_0!AF50,Class_1!AF50,Class_2!AF50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE76" s="4" t="str">
+        <f>IF(MIN(Class_0!AG50,Class_1!AG50,Class_2!AG50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BF76" s="4" t="str">
+        <f>IF(MIN(Class_0!AH50,Class_1!AH50,Class_2!AH50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BG76" s="4" t="str">
+        <f>IF(MIN(Class_0!AI50,Class_1!AI50,Class_2!AI50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BH76" s="4" t="str">
+        <f>IF(MIN(Class_0!AJ50,Class_1!AJ50,Class_2!AJ50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BI76" s="4" t="str">
+        <f>IF(MIN(Class_0!AK50,Class_1!AK50,Class_2!AK50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BJ76" s="4" t="str">
+        <f>IF(MIN(Class_0!AL50,Class_1!AL50,Class_2!AL50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BK76" s="4" t="str">
+        <f>IF(MIN(Class_0!AM50,Class_1!AM50,Class_2!AM50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BL76" s="4" t="str">
+        <f>IF(MIN(Class_0!AN50,Class_1!AN50,Class_2!AN50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BM76" s="4" t="str">
+        <f>IF(MIN(Class_0!AO50,Class_1!AO50,Class_2!AO50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BN76" s="4" t="str">
+        <f>IF(MIN(Class_0!AP50,Class_1!AP50,Class_2!AP50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BO76" s="4" t="str">
+        <f>IF(MIN(Class_0!AQ50,Class_1!AQ50,Class_2!AQ50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BP76" s="4" t="str">
+        <f>IF(MIN(Class_0!AR50,Class_1!AR50,Class_2!AR50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BQ76" s="4" t="str">
+        <f>IF(MIN(Class_0!AS50,Class_1!AS50,Class_2!AS50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BR76" s="4" t="str">
+        <f>IF(MIN(Class_0!AT50,Class_1!AT50,Class_2!AT50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BS76" s="4" t="str">
+        <f>IF(MIN(Class_0!AU50,Class_1!AU50,Class_2!AU50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BT76" s="4" t="str">
+        <f>IF(MIN(Class_0!AV50,Class_1!AV50,Class_2!AV50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BU76" s="4" t="str">
+        <f>IF(MIN(Class_0!AW50,Class_1!AW50,Class_2!AW50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BV76" s="4" t="str">
+        <f>IF(MIN(Class_0!AX50,Class_1!AX50,Class_2!AX50)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BW76" s="4"/>
+      <c r="BX76" s="4"/>
+      <c r="BY76" s="4"/>
+    </row>
+    <row r="77" spans="24:77" x14ac:dyDescent="0.35">
+      <c r="X77" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y77" s="2">
+        <f t="shared" si="7"/>
+        <v>49</v>
+      </c>
+      <c r="Z77" s="4" t="str">
+        <f>IF(MIN(Class_0!B51,Class_1!B51,Class_2!B51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA77" s="4" t="str">
+        <f>IF(MIN(Class_0!C51,Class_1!C51,Class_2!C51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB77" s="4" t="str">
+        <f>IF(MIN(Class_0!D51,Class_1!D51,Class_2!D51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC77" s="4" t="str">
+        <f>IF(MIN(Class_0!E51,Class_1!E51,Class_2!E51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD77" s="4" t="str">
+        <f>IF(MIN(Class_0!F51,Class_1!F51,Class_2!F51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE77" s="4" t="str">
+        <f>IF(MIN(Class_0!G51,Class_1!G51,Class_2!G51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF77" s="4" t="str">
+        <f>IF(MIN(Class_0!H51,Class_1!H51,Class_2!H51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG77" s="4" t="str">
+        <f>IF(MIN(Class_0!I51,Class_1!I51,Class_2!I51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH77" s="4" t="str">
+        <f>IF(MIN(Class_0!J51,Class_1!J51,Class_2!J51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI77" s="4" t="str">
+        <f>IF(MIN(Class_0!K51,Class_1!K51,Class_2!K51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AJ77" s="4" t="str">
+        <f>IF(MIN(Class_0!L51,Class_1!L51,Class_2!L51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AK77" s="4" t="str">
+        <f>IF(MIN(Class_0!M51,Class_1!M51,Class_2!M51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AL77" s="4" t="str">
+        <f>IF(MIN(Class_0!N51,Class_1!N51,Class_2!N51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AM77" s="4" t="str">
+        <f>IF(MIN(Class_0!O51,Class_1!O51,Class_2!O51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AN77" s="4" t="str">
+        <f>IF(MIN(Class_0!P51,Class_1!P51,Class_2!P51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO77" s="4" t="str">
+        <f>IF(MIN(Class_0!Q51,Class_1!Q51,Class_2!Q51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP77" s="4" t="str">
+        <f>IF(MIN(Class_0!R51,Class_1!R51,Class_2!R51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ77" s="4" t="str">
+        <f>IF(MIN(Class_0!S51,Class_1!S51,Class_2!S51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AR77" s="4" t="str">
+        <f>IF(MIN(Class_0!T51,Class_1!T51,Class_2!T51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS77" s="4" t="str">
+        <f>IF(MIN(Class_0!U51,Class_1!U51,Class_2!U51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT77" s="4" t="str">
+        <f>IF(MIN(Class_0!V51,Class_1!V51,Class_2!V51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU77" s="4" t="str">
+        <f>IF(MIN(Class_0!W51,Class_1!W51,Class_2!W51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV77" s="4" t="str">
+        <f>IF(MIN(Class_0!X51,Class_1!X51,Class_2!X51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW77" s="4" t="str">
+        <f>IF(MIN(Class_0!Y51,Class_1!Y51,Class_2!Y51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX77" s="4" t="str">
+        <f>IF(MIN(Class_0!Z51,Class_1!Z51,Class_2!Z51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY77" s="4" t="str">
+        <f>IF(MIN(Class_0!AA51,Class_1!AA51,Class_2!AA51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AZ77" s="4" t="str">
+        <f>IF(MIN(Class_0!AB51,Class_1!AB51,Class_2!AB51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA77" s="4" t="str">
+        <f>IF(MIN(Class_0!AC51,Class_1!AC51,Class_2!AC51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BB77" s="4" t="str">
+        <f>IF(MIN(Class_0!AD51,Class_1!AD51,Class_2!AD51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BC77" s="4" t="str">
+        <f>IF(MIN(Class_0!AE51,Class_1!AE51,Class_2!AE51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BD77" s="4" t="str">
+        <f>IF(MIN(Class_0!AF51,Class_1!AF51,Class_2!AF51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE77" s="4" t="str">
+        <f>IF(MIN(Class_0!AG51,Class_1!AG51,Class_2!AG51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BF77" s="4" t="str">
+        <f>IF(MIN(Class_0!AH51,Class_1!AH51,Class_2!AH51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BG77" s="4" t="str">
+        <f>IF(MIN(Class_0!AI51,Class_1!AI51,Class_2!AI51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BH77" s="4" t="str">
+        <f>IF(MIN(Class_0!AJ51,Class_1!AJ51,Class_2!AJ51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BI77" s="4" t="str">
+        <f>IF(MIN(Class_0!AK51,Class_1!AK51,Class_2!AK51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BJ77" s="4" t="str">
+        <f>IF(MIN(Class_0!AL51,Class_1!AL51,Class_2!AL51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BK77" s="4" t="str">
+        <f>IF(MIN(Class_0!AM51,Class_1!AM51,Class_2!AM51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BL77" s="4" t="str">
+        <f>IF(MIN(Class_0!AN51,Class_1!AN51,Class_2!AN51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BM77" s="4" t="str">
+        <f>IF(MIN(Class_0!AO51,Class_1!AO51,Class_2!AO51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BN77" s="4" t="str">
+        <f>IF(MIN(Class_0!AP51,Class_1!AP51,Class_2!AP51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BO77" s="4" t="str">
+        <f>IF(MIN(Class_0!AQ51,Class_1!AQ51,Class_2!AQ51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BP77" s="4" t="str">
+        <f>IF(MIN(Class_0!AR51,Class_1!AR51,Class_2!AR51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BQ77" s="4" t="str">
+        <f>IF(MIN(Class_0!AS51,Class_1!AS51,Class_2!AS51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BR77" s="4" t="str">
+        <f>IF(MIN(Class_0!AT51,Class_1!AT51,Class_2!AT51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BS77" s="4" t="str">
+        <f>IF(MIN(Class_0!AU51,Class_1!AU51,Class_2!AU51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BT77" s="4" t="str">
+        <f>IF(MIN(Class_0!AV51,Class_1!AV51,Class_2!AV51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BU77" s="4" t="str">
+        <f>IF(MIN(Class_0!AW51,Class_1!AW51,Class_2!AW51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BV77" s="4" t="str">
+        <f>IF(MIN(Class_0!AX51,Class_1!AX51,Class_2!AX51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BW77" s="4" t="str">
+        <f>IF(MIN(Class_0!AY51,Class_1!AY51,Class_2!AY51)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BX77" s="4"/>
+      <c r="BY77" s="4"/>
+    </row>
+    <row r="78" spans="24:77" x14ac:dyDescent="0.35">
+      <c r="X78" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y78" s="2">
+        <f t="shared" si="7"/>
+        <v>50</v>
+      </c>
+      <c r="Z78" s="4" t="str">
+        <f>IF(MIN(Class_0!B52,Class_1!B52,Class_2!B52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA78" s="4" t="str">
+        <f>IF(MIN(Class_0!C52,Class_1!C52,Class_2!C52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AB78" s="4" t="str">
+        <f>IF(MIN(Class_0!D52,Class_1!D52,Class_2!D52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC78" s="4" t="str">
+        <f>IF(MIN(Class_0!E52,Class_1!E52,Class_2!E52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD78" s="4" t="str">
+        <f>IF(MIN(Class_0!F52,Class_1!F52,Class_2!F52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE78" s="4" t="str">
+        <f>IF(MIN(Class_0!G52,Class_1!G52,Class_2!G52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF78" s="4" t="str">
+        <f>IF(MIN(Class_0!H52,Class_1!H52,Class_2!H52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG78" s="4" t="str">
+        <f>IF(MIN(Class_0!I52,Class_1!I52,Class_2!I52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH78" s="4" t="str">
+        <f>IF(MIN(Class_0!J52,Class_1!J52,Class_2!J52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI78" s="4" t="str">
+        <f>IF(MIN(Class_0!K52,Class_1!K52,Class_2!K52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ78" s="4" t="str">
+        <f>IF(MIN(Class_0!L52,Class_1!L52,Class_2!L52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK78" s="4" t="str">
+        <f>IF(MIN(Class_0!M52,Class_1!M52,Class_2!M52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL78" s="4" t="str">
+        <f>IF(MIN(Class_0!N52,Class_1!N52,Class_2!N52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM78" s="4" t="str">
+        <f>IF(MIN(Class_0!O52,Class_1!O52,Class_2!O52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN78" s="4" t="str">
+        <f>IF(MIN(Class_0!P52,Class_1!P52,Class_2!P52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO78" s="4" t="str">
+        <f>IF(MIN(Class_0!Q52,Class_1!Q52,Class_2!Q52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP78" s="4" t="str">
+        <f>IF(MIN(Class_0!R52,Class_1!R52,Class_2!R52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AQ78" s="4" t="str">
+        <f>IF(MIN(Class_0!S52,Class_1!S52,Class_2!S52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR78" s="4" t="str">
+        <f>IF(MIN(Class_0!T52,Class_1!T52,Class_2!T52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS78" s="4" t="str">
+        <f>IF(MIN(Class_0!U52,Class_1!U52,Class_2!U52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT78" s="4" t="str">
+        <f>IF(MIN(Class_0!V52,Class_1!V52,Class_2!V52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AU78" s="4" t="str">
+        <f>IF(MIN(Class_0!W52,Class_1!W52,Class_2!W52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV78" s="4" t="str">
+        <f>IF(MIN(Class_0!X52,Class_1!X52,Class_2!X52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW78" s="4" t="str">
+        <f>IF(MIN(Class_0!Y52,Class_1!Y52,Class_2!Y52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX78" s="4" t="str">
+        <f>IF(MIN(Class_0!Z52,Class_1!Z52,Class_2!Z52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY78" s="4" t="str">
+        <f>IF(MIN(Class_0!AA52,Class_1!AA52,Class_2!AA52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AZ78" s="4" t="str">
+        <f>IF(MIN(Class_0!AB52,Class_1!AB52,Class_2!AB52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BA78" s="4" t="str">
+        <f>IF(MIN(Class_0!AC52,Class_1!AC52,Class_2!AC52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BB78" s="4" t="str">
+        <f>IF(MIN(Class_0!AD52,Class_1!AD52,Class_2!AD52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BC78" s="4" t="str">
+        <f>IF(MIN(Class_0!AE52,Class_1!AE52,Class_2!AE52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BD78" s="4" t="str">
+        <f>IF(MIN(Class_0!AF52,Class_1!AF52,Class_2!AF52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE78" s="4" t="str">
+        <f>IF(MIN(Class_0!AG52,Class_1!AG52,Class_2!AG52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BF78" s="4" t="str">
+        <f>IF(MIN(Class_0!AH52,Class_1!AH52,Class_2!AH52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BG78" s="4" t="str">
+        <f>IF(MIN(Class_0!AI52,Class_1!AI52,Class_2!AI52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BH78" s="4" t="str">
+        <f>IF(MIN(Class_0!AJ52,Class_1!AJ52,Class_2!AJ52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BI78" s="4" t="str">
+        <f>IF(MIN(Class_0!AK52,Class_1!AK52,Class_2!AK52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BJ78" s="4" t="str">
+        <f>IF(MIN(Class_0!AL52,Class_1!AL52,Class_2!AL52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BK78" s="4" t="str">
+        <f>IF(MIN(Class_0!AM52,Class_1!AM52,Class_2!AM52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BL78" s="4" t="str">
+        <f>IF(MIN(Class_0!AN52,Class_1!AN52,Class_2!AN52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BM78" s="4" t="str">
+        <f>IF(MIN(Class_0!AO52,Class_1!AO52,Class_2!AO52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BN78" s="4" t="str">
+        <f>IF(MIN(Class_0!AP52,Class_1!AP52,Class_2!AP52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BO78" s="4" t="str">
+        <f>IF(MIN(Class_0!AQ52,Class_1!AQ52,Class_2!AQ52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BP78" s="4" t="str">
+        <f>IF(MIN(Class_0!AR52,Class_1!AR52,Class_2!AR52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BQ78" s="4" t="str">
+        <f>IF(MIN(Class_0!AS52,Class_1!AS52,Class_2!AS52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BR78" s="4" t="str">
+        <f>IF(MIN(Class_0!AT52,Class_1!AT52,Class_2!AT52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BS78" s="4" t="str">
+        <f>IF(MIN(Class_0!AU52,Class_1!AU52,Class_2!AU52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BT78" s="4" t="str">
+        <f>IF(MIN(Class_0!AV52,Class_1!AV52,Class_2!AV52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BU78" s="4" t="str">
+        <f>IF(MIN(Class_0!AW52,Class_1!AW52,Class_2!AW52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BV78" s="4" t="str">
+        <f>IF(MIN(Class_0!AX52,Class_1!AX52,Class_2!AX52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BW78" s="4" t="str">
+        <f>IF(MIN(Class_0!AY52,Class_1!AY52,Class_2!AY52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BX78" s="4" t="str">
+        <f>IF(MIN(Class_0!AZ52,Class_1!AZ52,Class_2!AZ52)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BY78" s="4"/>
+    </row>
+    <row r="79" spans="24:77" x14ac:dyDescent="0.35">
+      <c r="X79" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y79" s="2">
+        <f t="shared" si="7"/>
+        <v>51</v>
+      </c>
+      <c r="Z79" s="4" t="str">
+        <f>IF(MIN(Class_0!B53,Class_1!B53,Class_2!B53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AA79" s="4" t="str">
+        <f>IF(MIN(Class_0!C53,Class_1!C53,Class_2!C53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AB79" s="4" t="str">
+        <f>IF(MIN(Class_0!D53,Class_1!D53,Class_2!D53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AC79" s="4" t="str">
+        <f>IF(MIN(Class_0!E53,Class_1!E53,Class_2!E53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AD79" s="4" t="str">
+        <f>IF(MIN(Class_0!F53,Class_1!F53,Class_2!F53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AE79" s="4" t="str">
+        <f>IF(MIN(Class_0!G53,Class_1!G53,Class_2!G53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AF79" s="4" t="str">
+        <f>IF(MIN(Class_0!H53,Class_1!H53,Class_2!H53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AG79" s="4" t="str">
+        <f>IF(MIN(Class_0!I53,Class_1!I53,Class_2!I53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AH79" s="4" t="str">
+        <f>IF(MIN(Class_0!J53,Class_1!J53,Class_2!J53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AI79" s="4" t="str">
+        <f>IF(MIN(Class_0!K53,Class_1!K53,Class_2!K53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AJ79" s="4" t="str">
+        <f>IF(MIN(Class_0!L53,Class_1!L53,Class_2!L53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AK79" s="4" t="str">
+        <f>IF(MIN(Class_0!M53,Class_1!M53,Class_2!M53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AL79" s="4" t="str">
+        <f>IF(MIN(Class_0!N53,Class_1!N53,Class_2!N53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AM79" s="4" t="str">
+        <f>IF(MIN(Class_0!O53,Class_1!O53,Class_2!O53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AN79" s="4" t="str">
+        <f>IF(MIN(Class_0!P53,Class_1!P53,Class_2!P53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AO79" s="4" t="str">
+        <f>IF(MIN(Class_0!Q53,Class_1!Q53,Class_2!Q53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AP79" s="4" t="str">
+        <f>IF(MIN(Class_0!R53,Class_1!R53,Class_2!R53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AQ79" s="4" t="str">
+        <f>IF(MIN(Class_0!S53,Class_1!S53,Class_2!S53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AR79" s="4" t="str">
+        <f>IF(MIN(Class_0!T53,Class_1!T53,Class_2!T53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AS79" s="4" t="str">
+        <f>IF(MIN(Class_0!U53,Class_1!U53,Class_2!U53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AT79" s="4" t="str">
+        <f>IF(MIN(Class_0!V53,Class_1!V53,Class_2!V53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AU79" s="4" t="str">
+        <f>IF(MIN(Class_0!W53,Class_1!W53,Class_2!W53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AV79" s="4" t="str">
+        <f>IF(MIN(Class_0!X53,Class_1!X53,Class_2!X53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AW79" s="4" t="str">
+        <f>IF(MIN(Class_0!Y53,Class_1!Y53,Class_2!Y53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AX79" s="4" t="str">
+        <f>IF(MIN(Class_0!Z53,Class_1!Z53,Class_2!Z53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="AY79" s="4" t="str">
+        <f>IF(MIN(Class_0!AA53,Class_1!AA53,Class_2!AA53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="AZ79" s="4" t="str">
+        <f>IF(MIN(Class_0!AB53,Class_1!AB53,Class_2!AB53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BA79" s="4" t="str">
+        <f>IF(MIN(Class_0!AC53,Class_1!AC53,Class_2!AC53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BB79" s="4" t="str">
+        <f>IF(MIN(Class_0!AD53,Class_1!AD53,Class_2!AD53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BC79" s="4" t="str">
+        <f>IF(MIN(Class_0!AE53,Class_1!AE53,Class_2!AE53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BD79" s="4" t="str">
+        <f>IF(MIN(Class_0!AF53,Class_1!AF53,Class_2!AF53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BE79" s="4" t="str">
+        <f>IF(MIN(Class_0!AG53,Class_1!AG53,Class_2!AG53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BF79" s="4" t="str">
+        <f>IF(MIN(Class_0!AH53,Class_1!AH53,Class_2!AH53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BG79" s="4" t="str">
+        <f>IF(MIN(Class_0!AI53,Class_1!AI53,Class_2!AI53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BH79" s="4" t="str">
+        <f>IF(MIN(Class_0!AJ53,Class_1!AJ53,Class_2!AJ53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BI79" s="4" t="str">
+        <f>IF(MIN(Class_0!AK53,Class_1!AK53,Class_2!AK53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BJ79" s="4" t="str">
+        <f>IF(MIN(Class_0!AL53,Class_1!AL53,Class_2!AL53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BK79" s="4" t="str">
+        <f>IF(MIN(Class_0!AM53,Class_1!AM53,Class_2!AM53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BL79" s="4" t="str">
+        <f>IF(MIN(Class_0!AN53,Class_1!AN53,Class_2!AN53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BM79" s="4" t="str">
+        <f>IF(MIN(Class_0!AO53,Class_1!AO53,Class_2!AO53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BN79" s="4" t="str">
+        <f>IF(MIN(Class_0!AP53,Class_1!AP53,Class_2!AP53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BO79" s="4" t="str">
+        <f>IF(MIN(Class_0!AQ53,Class_1!AQ53,Class_2!AQ53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BP79" s="4" t="str">
+        <f>IF(MIN(Class_0!AR53,Class_1!AR53,Class_2!AR53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BQ79" s="4" t="str">
+        <f>IF(MIN(Class_0!AS53,Class_1!AS53,Class_2!AS53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BR79" s="4" t="str">
+        <f>IF(MIN(Class_0!AT53,Class_1!AT53,Class_2!AT53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BS79" s="4" t="str">
+        <f>IF(MIN(Class_0!AU53,Class_1!AU53,Class_2!AU53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BT79" s="4" t="str">
+        <f>IF(MIN(Class_0!AV53,Class_1!AV53,Class_2!AV53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BU79" s="4" t="str">
+        <f>IF(MIN(Class_0!AW53,Class_1!AW53,Class_2!AW53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BV79" s="4" t="str">
+        <f>IF(MIN(Class_0!AX53,Class_1!AX53,Class_2!AX53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BW79" s="4" t="str">
+        <f>IF(MIN(Class_0!AY53,Class_1!AY53,Class_2!AY53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>-</v>
+      </c>
+      <c r="BX79" s="4" t="str">
+        <f>IF(MIN(Class_0!AZ53,Class_1!AZ53,Class_2!AZ53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
+      </c>
+      <c r="BY79" s="4" t="str">
+        <f>IF(MIN(Class_0!BA53,Class_1!BA53,Class_2!BA53)&gt;0,CHAR(43),CHAR(45))</f>
+        <v>+</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B6:AZ6">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B7:AZ7">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9:AZ9">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D10">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B9:AZ9">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>TRUE</formula>
+  <conditionalFormatting sqref="Z28:BY79">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"-"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7:AZ7">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>TRUE</formula>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"+"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/sensitivity_results/legacy/mobilenet_v3_small_beforecorrelation_matrices.xlsx
+++ b/sensitivity_results/legacy/mobilenet_v3_small_beforecorrelation_matrices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\temp\ToGIT\Legacy\pearson_corelation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7837051-866E-4E2F-B938-92A3D633C502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4463001-294D-4DF0-9746-87A41501BA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -665,7 +665,7 @@
   <dimension ref="A1:BY79"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="24" max="24" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="27.36328125" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="19.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2429,207 +2429,207 @@
         <v>0</v>
       </c>
       <c r="AA27" s="2">
-        <f>Z27+1</f>
+        <f t="shared" ref="AA27:BF27" si="7">Z27+1</f>
         <v>1</v>
       </c>
       <c r="AB27" s="2">
-        <f>AA27+1</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="AC27" s="2">
-        <f>AB27+1</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="AD27" s="2">
-        <f>AC27+1</f>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="AE27" s="2">
-        <f>AD27+1</f>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="AF27" s="2">
-        <f>AE27+1</f>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="AG27" s="2">
-        <f>AF27+1</f>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="AH27" s="2">
-        <f>AG27+1</f>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="AI27" s="2">
-        <f>AH27+1</f>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="AJ27" s="2">
-        <f>AI27+1</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="AK27" s="2">
-        <f>AJ27+1</f>
+        <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="AL27" s="2">
-        <f>AK27+1</f>
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="AM27" s="2">
-        <f>AL27+1</f>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="AN27" s="2">
-        <f>AM27+1</f>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="AO27" s="2">
-        <f>AN27+1</f>
+        <f t="shared" si="7"/>
         <v>15</v>
       </c>
       <c r="AP27" s="2">
-        <f>AO27+1</f>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="AQ27" s="2">
-        <f>AP27+1</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="AR27" s="2">
-        <f>AQ27+1</f>
+        <f t="shared" si="7"/>
         <v>18</v>
       </c>
       <c r="AS27" s="2">
-        <f>AR27+1</f>
+        <f t="shared" si="7"/>
         <v>19</v>
       </c>
       <c r="AT27" s="2">
-        <f>AS27+1</f>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="AU27" s="2">
-        <f>AT27+1</f>
+        <f t="shared" si="7"/>
         <v>21</v>
       </c>
       <c r="AV27" s="2">
-        <f>AU27+1</f>
+        <f t="shared" si="7"/>
         <v>22</v>
       </c>
       <c r="AW27" s="2">
-        <f>AV27+1</f>
+        <f t="shared" si="7"/>
         <v>23</v>
       </c>
       <c r="AX27" s="2">
-        <f>AW27+1</f>
+        <f t="shared" si="7"/>
         <v>24</v>
       </c>
       <c r="AY27" s="2">
-        <f>AX27+1</f>
+        <f t="shared" si="7"/>
         <v>25</v>
       </c>
       <c r="AZ27" s="2">
-        <f>AY27+1</f>
+        <f t="shared" si="7"/>
         <v>26</v>
       </c>
       <c r="BA27" s="2">
-        <f>AZ27+1</f>
+        <f t="shared" si="7"/>
         <v>27</v>
       </c>
       <c r="BB27" s="2">
-        <f>BA27+1</f>
+        <f t="shared" si="7"/>
         <v>28</v>
       </c>
       <c r="BC27" s="2">
-        <f>BB27+1</f>
+        <f t="shared" si="7"/>
         <v>29</v>
       </c>
       <c r="BD27" s="2">
-        <f>BC27+1</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="BE27" s="2">
-        <f>BD27+1</f>
+        <f t="shared" si="7"/>
         <v>31</v>
       </c>
       <c r="BF27" s="2">
-        <f>BE27+1</f>
+        <f t="shared" si="7"/>
         <v>32</v>
       </c>
       <c r="BG27" s="2">
-        <f>BF27+1</f>
+        <f t="shared" ref="BG27:BY27" si="8">BF27+1</f>
         <v>33</v>
       </c>
       <c r="BH27" s="2">
-        <f>BG27+1</f>
+        <f t="shared" si="8"/>
         <v>34</v>
       </c>
       <c r="BI27" s="2">
-        <f>BH27+1</f>
+        <f t="shared" si="8"/>
         <v>35</v>
       </c>
       <c r="BJ27" s="2">
-        <f>BI27+1</f>
+        <f t="shared" si="8"/>
         <v>36</v>
       </c>
       <c r="BK27" s="2">
-        <f>BJ27+1</f>
+        <f t="shared" si="8"/>
         <v>37</v>
       </c>
       <c r="BL27" s="2">
-        <f>BK27+1</f>
+        <f t="shared" si="8"/>
         <v>38</v>
       </c>
       <c r="BM27" s="2">
-        <f>BL27+1</f>
+        <f t="shared" si="8"/>
         <v>39</v>
       </c>
       <c r="BN27" s="2">
-        <f>BM27+1</f>
+        <f t="shared" si="8"/>
         <v>40</v>
       </c>
       <c r="BO27" s="2">
-        <f>BN27+1</f>
+        <f t="shared" si="8"/>
         <v>41</v>
       </c>
       <c r="BP27" s="2">
-        <f>BO27+1</f>
+        <f t="shared" si="8"/>
         <v>42</v>
       </c>
       <c r="BQ27" s="2">
-        <f>BP27+1</f>
+        <f t="shared" si="8"/>
         <v>43</v>
       </c>
       <c r="BR27" s="2">
-        <f>BQ27+1</f>
+        <f t="shared" si="8"/>
         <v>44</v>
       </c>
       <c r="BS27" s="2">
-        <f>BR27+1</f>
+        <f t="shared" si="8"/>
         <v>45</v>
       </c>
       <c r="BT27" s="2">
-        <f>BS27+1</f>
+        <f t="shared" si="8"/>
         <v>46</v>
       </c>
       <c r="BU27" s="2">
-        <f>BT27+1</f>
+        <f t="shared" si="8"/>
         <v>47</v>
       </c>
       <c r="BV27" s="2">
-        <f>BU27+1</f>
+        <f t="shared" si="8"/>
         <v>48</v>
       </c>
       <c r="BW27" s="2">
-        <f>BV27+1</f>
+        <f t="shared" si="8"/>
         <v>49</v>
       </c>
       <c r="BX27" s="2">
-        <f>BW27+1</f>
+        <f t="shared" si="8"/>
         <v>50</v>
       </c>
       <c r="BY27" s="2">
-        <f>BX27+1</f>
+        <f t="shared" si="8"/>
         <v>51</v>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
         <v>2</v>
       </c>
       <c r="Y30" s="2">
-        <f t="shared" ref="Y30:Y79" si="7">Y29+1</f>
+        <f t="shared" ref="Y30:Y79" si="9">Y29+1</f>
         <v>2</v>
       </c>
       <c r="Z30" s="4" t="str">
@@ -2847,7 +2847,7 @@
         <v>3</v>
       </c>
       <c r="Y31" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="Z31" s="4" t="str">
@@ -2923,7 +2923,7 @@
         <v>4</v>
       </c>
       <c r="Y32" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="Z32" s="4" t="str">
@@ -3002,7 +3002,7 @@
         <v>5</v>
       </c>
       <c r="Y33" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
       <c r="Z33" s="4" t="str">
@@ -3081,7 +3081,7 @@
         <v>6</v>
       </c>
       <c r="Y34" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="Z34" s="4" t="str">
@@ -3163,7 +3163,7 @@
         <v>7</v>
       </c>
       <c r="Y35" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
       <c r="Z35" s="4" t="str">
@@ -3251,7 +3251,7 @@
         <v>8</v>
       </c>
       <c r="Y36" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
       <c r="Z36" s="4" t="str">
@@ -3342,7 +3342,7 @@
         <v>9</v>
       </c>
       <c r="Y37" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
       <c r="Z37" s="4" t="str">
@@ -3436,7 +3436,7 @@
         <v>10</v>
       </c>
       <c r="Y38" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="Z38" s="4" t="str">
@@ -3533,7 +3533,7 @@
         <v>11</v>
       </c>
       <c r="Y39" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="Z39" s="4" t="str">
@@ -3630,7 +3630,7 @@
         <v>12</v>
       </c>
       <c r="Y40" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="Z40" s="4" t="str">
@@ -3733,7 +3733,7 @@
         <v>13</v>
       </c>
       <c r="Y41" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
       <c r="Z41" s="4" t="str">
@@ -3839,7 +3839,7 @@
         <v>14</v>
       </c>
       <c r="Y42" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
       <c r="Z42" s="4" t="str">
@@ -3948,7 +3948,7 @@
         <v>15</v>
       </c>
       <c r="Y43" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>15</v>
       </c>
       <c r="Z43" s="4" t="str">
@@ -4057,7 +4057,7 @@
         <v>16</v>
       </c>
       <c r="Y44" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>16</v>
       </c>
       <c r="Z44" s="4" t="str">
@@ -4169,7 +4169,7 @@
         <v>17</v>
       </c>
       <c r="Y45" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>17</v>
       </c>
       <c r="Z45" s="4" t="str">
@@ -4284,7 +4284,7 @@
         <v>18</v>
       </c>
       <c r="Y46" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>18</v>
       </c>
       <c r="Z46" s="4" t="str">
@@ -4402,7 +4402,7 @@
         <v>19</v>
       </c>
       <c r="Y47" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>19</v>
       </c>
       <c r="Z47" s="4" t="str">
@@ -4523,7 +4523,7 @@
         <v>20</v>
       </c>
       <c r="Y48" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="Z48" s="4" t="str">
@@ -4647,7 +4647,7 @@
         <v>21</v>
       </c>
       <c r="Y49" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>21</v>
       </c>
       <c r="Z49" s="4" t="str">
@@ -4774,7 +4774,7 @@
         <v>22</v>
       </c>
       <c r="Y50" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>22</v>
       </c>
       <c r="Z50" s="4" t="str">
@@ -4904,7 +4904,7 @@
         <v>23</v>
       </c>
       <c r="Y51" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>23</v>
       </c>
       <c r="Z51" s="4" t="str">
@@ -5037,7 +5037,7 @@
         <v>24</v>
       </c>
       <c r="Y52" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>24</v>
       </c>
       <c r="Z52" s="4" t="str">
@@ -5173,7 +5173,7 @@
         <v>25</v>
       </c>
       <c r="Y53" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>25</v>
       </c>
       <c r="Z53" s="4" t="str">
@@ -5312,7 +5312,7 @@
         <v>26</v>
       </c>
       <c r="Y54" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>26</v>
       </c>
       <c r="Z54" s="4" t="str">
@@ -5454,7 +5454,7 @@
         <v>27</v>
       </c>
       <c r="Y55" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>27</v>
       </c>
       <c r="Z55" s="4" t="str">
@@ -5602,7 +5602,7 @@
         <v>28</v>
       </c>
       <c r="Y56" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>28</v>
       </c>
       <c r="Z56" s="4" t="str">
@@ -5753,7 +5753,7 @@
         <v>29</v>
       </c>
       <c r="Y57" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>29</v>
       </c>
       <c r="Z57" s="4" t="str">
@@ -5907,7 +5907,7 @@
         <v>30</v>
       </c>
       <c r="Y58" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>30</v>
       </c>
       <c r="Z58" s="4" t="str">
@@ -6064,7 +6064,7 @@
         <v>31</v>
       </c>
       <c r="Y59" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>31</v>
       </c>
       <c r="Z59" s="4" t="str">
@@ -6221,7 +6221,7 @@
         <v>32</v>
       </c>
       <c r="Y60" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>32</v>
       </c>
       <c r="Z60" s="4" t="str">
@@ -6384,7 +6384,7 @@
         <v>33</v>
       </c>
       <c r="Y61" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>33</v>
       </c>
       <c r="Z61" s="4" t="str">
@@ -6550,7 +6550,7 @@
         <v>34</v>
       </c>
       <c r="Y62" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>34</v>
       </c>
       <c r="Z62" s="4" t="str">
@@ -6719,7 +6719,7 @@
         <v>35</v>
       </c>
       <c r="Y63" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>35</v>
       </c>
       <c r="Z63" s="4" t="str">
@@ -6891,7 +6891,7 @@
         <v>36</v>
       </c>
       <c r="Y64" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>36</v>
       </c>
       <c r="Z64" s="4" t="str">
@@ -7063,7 +7063,7 @@
         <v>37</v>
       </c>
       <c r="Y65" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>37</v>
       </c>
       <c r="Z65" s="4" t="str">
@@ -7238,7 +7238,7 @@
         <v>38</v>
       </c>
       <c r="Y66" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>38</v>
       </c>
       <c r="Z66" s="4" t="str">
@@ -7416,7 +7416,7 @@
         <v>39</v>
       </c>
       <c r="Y67" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>39</v>
       </c>
       <c r="Z67" s="4" t="str">
@@ -7597,7 +7597,7 @@
         <v>40</v>
       </c>
       <c r="Y68" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
       <c r="Z68" s="4" t="str">
@@ -7781,7 +7781,7 @@
         <v>41</v>
       </c>
       <c r="Y69" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>41</v>
       </c>
       <c r="Z69" s="4" t="str">
@@ -7968,7 +7968,7 @@
         <v>42</v>
       </c>
       <c r="Y70" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>42</v>
       </c>
       <c r="Z70" s="4" t="str">
@@ -8158,7 +8158,7 @@
         <v>43</v>
       </c>
       <c r="Y71" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>43</v>
       </c>
       <c r="Z71" s="4" t="str">
@@ -8351,7 +8351,7 @@
         <v>44</v>
       </c>
       <c r="Y72" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>44</v>
       </c>
       <c r="Z72" s="4" t="str">
@@ -8547,7 +8547,7 @@
         <v>45</v>
       </c>
       <c r="Y73" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>45</v>
       </c>
       <c r="Z73" s="4" t="str">
@@ -8746,7 +8746,7 @@
         <v>46</v>
       </c>
       <c r="Y74" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>46</v>
       </c>
       <c r="Z74" s="4" t="str">
@@ -8948,7 +8948,7 @@
         <v>47</v>
       </c>
       <c r="Y75" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>47</v>
       </c>
       <c r="Z75" s="4" t="str">
@@ -9153,7 +9153,7 @@
         <v>48</v>
       </c>
       <c r="Y76" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>48</v>
       </c>
       <c r="Z76" s="4" t="str">
@@ -9361,7 +9361,7 @@
         <v>49</v>
       </c>
       <c r="Y77" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>49</v>
       </c>
       <c r="Z77" s="4" t="str">
@@ -9572,7 +9572,7 @@
         <v>50</v>
       </c>
       <c r="Y78" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>50</v>
       </c>
       <c r="Z78" s="4" t="str">
@@ -9786,7 +9786,7 @@
         <v>51</v>
       </c>
       <c r="Y79" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>51</v>
       </c>
       <c r="Z79" s="4" t="str">
